--- a/hardware/Microduck-HAT-IMU-Shopping-List-20261013.xlsx
+++ b/hardware/Microduck-HAT-IMU-Shopping-List-20261013.xlsx
@@ -15,6 +15,7 @@
     <sheet name="订单匹配依据" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="制作工具与耗材" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="制作成本" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="鸭子本体合计" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2434" uniqueCount="1061">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2529" uniqueCount="1114">
   <si>
     <t xml:space="preserve">Microduck 鸭子用料与制作工具采购清单</t>
   </si>
@@ -2239,52 +2240,10 @@
     <t xml:space="preserve">M2.6*8[200只]镀镍</t>
   </si>
   <si>
-    <t xml:space="preserve">M2×4 薄头内六角平尾自攻螺丝</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304不锈钢 / 薄杯头内六角 / 平尾自攻 / M2×4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">金超官方旗舰店</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2*4(200个)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">与十字盘头是不同头型，按实际安装位置选择；每包数量是备料数量。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2×6 薄头内六角平尾自攻螺丝</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304不锈钢 / 薄杯头内六角 / 平尾自攻 / M2×6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2*6(100个)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2×8 薄头内六角平尾自攻螺丝</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304不锈钢 / 薄杯头内六角 / 平尾自攻 / M2×8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2*8(100个)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2×12 薄头内六角平尾自攻螺丝</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304不锈钢 / 薄杯头内六角 / 平尾自攻 / M2×12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2*12(100个)</t>
-  </si>
-  <si>
     <t xml:space="preserve">相关订单匹配依据</t>
   </si>
   <si>
-    <t xml:space="preserve">源：订单数据.xlsx；仅保留本次采购相关的115条商品记录。</t>
+    <t xml:space="preserve">源：订单数据.xlsx；仅保留本次采购相关的111条商品记录。</t>
   </si>
   <si>
     <t xml:space="preserve">数量是订单拍数，不一定等于器件个数。每拍包装数量由商品款式单独解析。</t>
@@ -2723,21 +2682,6 @@
   </si>
   <si>
     <t xml:space="preserve">鸭子本体用料：ET2216 薄壁轴承</t>
-  </si>
-  <si>
-    <t xml:space="preserve">金超304不锈钢薄头圆柱头内六角平尾自攻螺丝薄杯头螺钉M3M4M5M6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鸭子本体用料：M2×8 薄头内六角平尾自攻螺丝</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鸭子本体用料：M2×12 薄头内六角平尾自攻螺丝</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鸭子本体用料：M2×6 薄头内六角平尾自攻螺丝</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鸭子本体用料：M2×4 薄头内六角平尾自攻螺丝</t>
   </si>
   <si>
     <t xml:space="preserve">飞特HD1910舵机，补充2只（与13只订单合计15只）</t>
@@ -3253,21 +3197,244 @@
   <si>
     <t xml:space="preserve">SN74LVC2G125DCUR
 商品无选项，按商品标题完整型号购买</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鸭子本体采购列表与合计</t>
+  </si>
+  <si>
+    <t xml:space="preserve">历史价格预算，包含下表备料；HAT/IMU各按整板计价，原器件列表不动。不计3D打印、制作工具、焊接清洁耗材。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCB有免费券：已列商品合计</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCB无券：按单张折算合计</t>
+  </si>
+  <si>
+    <t xml:space="preserve">首次整包整批采购：PCB免费</t>
+  </si>
+  <si>
+    <t xml:space="preserve">首次整包整批采购：PCB无券</t>
+  </si>
+  <si>
+    <t xml:space="preserve">数量含备料，螺丝按整包；SH转XH备选线不重复计入。M2×5为原订单0元优惠价。TF卡等未提供价格的项目未计入。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">商品 / 模块</t>
+  </si>
+  <si>
+    <t xml:space="preserve">计价单位</t>
+  </si>
+  <si>
+    <t xml:space="preserve">参考采购数量</t>
+  </si>
+  <si>
+    <t xml:space="preserve">历史单价(元)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">小计(元)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">数量与费用说明</t>
+  </si>
+  <si>
+    <t xml:space="preserve">商品或BOM链接</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAT 整板</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAT-V5，84个板上器件，含PCB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">块</t>
+  </si>
+  <si>
+    <t xml:space="preserve">按单板实际用料分摊，PCB免费券基准；无券每块另加4元。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMU 整板</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMU-TO-DLX-V2，25个板上器件，含PCB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HD-1910-C001；HD-1910-C001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">只</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2GB RAM 无 eMMC 带排针[【Microduck 原版主板】]；2GB RAM / 无eMMC / 带排针</t>
+  </si>
+  <si>
+    <t xml:space="preserve">个</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【NP-F550补光灯专用▲2200mAh】2电+标准双充套裝；沣标 NP-F550 / 2200mAh / 2块电池＋标准双充</t>
+  </si>
+  <si>
+    <t xml:space="preserve">套</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8M 219 摄像头[【适配3W/3E/3A/3C/CM5/4系列】]；IMX219 / 800万像素 / 瑞莎8M 219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VL53L5X V2模块配盖片；VL53L5X V2模块配盖片（商品标题 VL53L5CX）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3525腔体-4Ω3W/喇叭；3525 腔体 / 4Ω 3W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6700开式【轴承钢·精品级】10*15*3MM；6700开式 / 10×15×3mm / 轴承钢精品级</t>
+  </si>
+  <si>
+    <t xml:space="preserve">按订单参考采购数量计入，包含备料；尺寸顺序为内径×外径×宽度；两次订单为3只和2只。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ET2216【精品级】16*22*4MM[轴承钢]；ET2216 / 16×22×4mm / 轴承钢精品级</t>
+  </si>
+  <si>
+    <t xml:space="preserve">按订单参考采购数量计入，包含备料；尺寸顺序为内径×外径×宽度；两次订单为10只和2只。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2*4[200只]镀镍；铁镀镍 / 十字圆头 / 平尾自攻 / M2×4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">包（200个）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每种买1包（200只），包含备料；按打印模型及对应安装位置选择长度；每包数量是备料数量。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2*5[200只]镀镍；铁镀镍 / 十字圆头 / 平尾自攻 / M2×5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每种买1包（200只），包含备料；按打印模型及对应安装位置选择长度；每包数量是备料数量。原订单商品金额为0元（订单优惠），不代表常规售价。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2*6[200只]镀镍；铁镀镍 / 十字圆头 / 平尾自攻 / M2×6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2*8[200只]镀镍；铁镀镍 / 十字圆头 / 平尾自攻 / M2×8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2*12[200只]镀镍；铁镀镍 / 十字圆头 / 平尾自攻 / M2×12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2.6*8[200只]镀镍；铁镀镍 / 十字圆头 / 平尾自攻 / M2.6×8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EH2.5MM 2P胶壳（50个）；EH 2P，配 HAT J1/J2/J9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">包（50个）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EH2.5MM 3P胶壳（50个）；EH 3P，配 HAT J13/J14、IMU J1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EH2.5MM 端子（100个）；EH2.5MM 端子</t>
+  </si>
+  <si>
+    <t xml:space="preserve">包（100个）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2m;1.0-4P转杜邦母（5条）；SH1.0 4P / 20cm / 杜邦母</t>
+  </si>
+  <si>
+    <t xml:space="preserve">包（5个）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200mm;1007/24#;3P;AMP2.0；200mm / 1007 / 24AWG / 3P / AMP2.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">条</t>
+  </si>
+  <si>
+    <t xml:space="preserve">按订单参考采购数量计入，包含备料；用于飞特舵机线束；10cm和20cm按实际走线位置选择。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100mm;1007/24#;3P;AMP2.0；100mm / 1007 / 24AWG / 3P / AMP2.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">按订单参考采购数量计入，包含备料；与20cm线是不同长度选项，数量按实际线束方案准备。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3P胶壳(179228-3)；179228-3 / 3P / 2.0mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">按订单参考采购数量计入，包含备料；每个3P胶壳配3个AMP端子；原订单数量50是购入个数。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">镀锡端子100个；AMP/TE2.0 配套端子 / 100个</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2007WV-3P；A2007WV-3P / 2.0mm / 直插</t>
+  </si>
+  <si>
+    <t xml:space="preserve">按订单参考采购数量计入，包含备料；直插版本，按A2007WV-3P完整型号选购。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">按商品完整型号购买：AMP2.0 3P 弯插板座；A2007WR-3P / 2.0mm / 弯插</t>
+  </si>
+  <si>
+    <t xml:space="preserve">按订单参考采购数量计入，包含备料；弯插版本，按A2007WR-3P完整型号选购。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黑色;3芯;22AWG;1m；黑色 / 3芯 / 22AWG / 1m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">米</t>
+  </si>
+  <si>
+    <t xml:space="preserve">原订单2米×3.63元＋1米×3.52元，合计3米10.78元；单价按两次订单均价。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22AWG(0.33平方)黑色 2米；黑色 / 22AWG / 0.33mm² / 2m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2P;胶壳；XH2.54 / 2P / 胶壳</t>
+  </si>
+  <si>
+    <t xml:space="preserve">按订单参考采购数量计入，包含备料；与XH端子成套使用，按2P胶壳款式购买。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2P;直针；XH2.54 / 2P / 直针</t>
+  </si>
+  <si>
+    <t xml:space="preserve">按订单参考采购数量计入，包含备料；按2P直针款式购买。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2P;XH簧片；XH2.54 / 簧片</t>
+  </si>
+  <si>
+    <t xml:space="preserve">按订单参考采购数量计入，包含备料；按“2P;XH簧片”原选项购买，与XH胶壳成套。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">袋装 164片 彩色 【2倍收缩】；164片 / 彩色 / 2倍收缩</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="13">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0"/>
-    <numFmt numFmtId="166" formatCode="\¥0.00"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="168" formatCode="0.00"/>
-    <numFmt numFmtId="169" formatCode="\¥0.000000"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="_(\$* #,##0_);_(\$* \(#,##0\);_(\$* \-_);_(@_)"/>
+    <numFmt numFmtId="169" formatCode="0%"/>
+    <numFmt numFmtId="170" formatCode="0"/>
+    <numFmt numFmtId="171" formatCode="\¥0.00"/>
+    <numFmt numFmtId="172" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="173" formatCode="0.00"/>
+    <numFmt numFmtId="174" formatCode="\¥0.000000"/>
+    <numFmt numFmtId="175" formatCode="\¥0.00"/>
+    <numFmt numFmtId="176" formatCode="\¥0.0000"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="24">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -3287,6 +3454,18 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3377,6 +3556,51 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF233653"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="18"/>
+      <color rgb="FF233653"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF233653"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF187545"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1565C0"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -3463,7 +3687,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="21">
+  <cellStyleXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3487,155 +3711,214 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="44">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="7" fillId="2" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="3" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="3" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="4" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="4" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="2" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="3" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="3" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="5" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="10" fillId="4" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="6" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="17" fillId="6" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="16" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="14" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="20" fillId="6" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="4" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="22" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="18" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="5" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="22" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="13">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Normal" xfId="20"/>
+    <cellStyle name="Comma" xfId="20"/>
+    <cellStyle name="Comma [0]" xfId="21"/>
+    <cellStyle name="Currency" xfId="22"/>
+    <cellStyle name="Currency [0]" xfId="23"/>
+    <cellStyle name="Normal" xfId="24"/>
+    <cellStyle name="Normal 1" xfId="25"/>
+    <cellStyle name="Percent" xfId="26"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="16">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3695,6 +3978,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF187545"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE8F2FF"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -3774,13 +4065,13 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle count="7" name="TableStyleLight1">
-      <tableStyleElement dxfId="8" type="wholeTable"/>
-      <tableStyleElement dxfId="9" type="firstColumnStripe"/>
-      <tableStyleElement dxfId="10" type="firstRowStripe"/>
-      <tableStyleElement dxfId="11" type="lastColumn"/>
-      <tableStyleElement dxfId="12" type="firstColumn"/>
-      <tableStyleElement dxfId="13" type="headerRow"/>
-      <tableStyleElement dxfId="14" type="totalRow"/>
+      <tableStyleElement dxfId="9" type="wholeTable"/>
+      <tableStyleElement dxfId="10" type="firstColumnStripe"/>
+      <tableStyleElement dxfId="11" type="firstRowStripe"/>
+      <tableStyleElement dxfId="12" type="lastColumn"/>
+      <tableStyleElement dxfId="13" type="firstColumn"/>
+      <tableStyleElement dxfId="14" type="headerRow"/>
+      <tableStyleElement dxfId="15" type="totalRow"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -3891,8 +4182,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DuckAccessories" displayName="DuckAccessories" ref="A6:K43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A6:K43"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DuckAccessories" displayName="DuckAccessories" ref="A6:K39" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A6:K39"/>
   <tableColumns count="11">
     <tableColumn id="1" name="类别"/>
     <tableColumn id="2" name="商品 / 用品"/>
@@ -3911,7 +4202,24 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="HATComponents" displayName="HATComponents" ref="A7:K91" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="DuckTotalItems" displayName="DuckTotalItems" ref="A10:H42" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A10:H42"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="商品 / 模块"/>
+    <tableColumn id="2" name="型号 / 指定款式"/>
+    <tableColumn id="3" name="计价单位"/>
+    <tableColumn id="4" name="参考采购数量"/>
+    <tableColumn id="5" name="历史单价(元)"/>
+    <tableColumn id="6" name="小计(元)"/>
+    <tableColumn id="7" name="数量与费用说明"/>
+    <tableColumn id="8" name="商品或BOM链接"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="HATComponents" displayName="HATComponents" ref="A7:K91" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A7:K91"/>
   <tableColumns count="11">
     <tableColumn id="1" name="位号"/>
@@ -3930,8 +4238,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="IMUComponents" displayName="IMUComponents" ref="A7:K32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="IMUComponents" displayName="IMUComponents" ref="A7:K32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A7:K32"/>
   <tableColumns count="11">
     <tableColumn id="1" name="位号"/>
@@ -3950,9 +4258,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="OrderEvidence" displayName="OrderEvidence" ref="A6:J121" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A6:J121"/>
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="OrderEvidence" displayName="OrderEvidence" ref="A6:J117" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A6:J117"/>
   <tableColumns count="10">
     <tableColumn id="1" name="订单源行"/>
     <tableColumn id="2" name="提交日期"/>
@@ -3969,8 +4277,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Procurement" displayName="Procurement" ref="A8:O54" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Procurement" displayName="Procurement" ref="A8:O54" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A8:O54"/>
   <tableColumns count="15">
     <tableColumn id="1" name="类别"/>
@@ -12314,150 +12622,10 @@
         <v>3.59</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="8" t="s">
-        <v>714</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>737</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>738</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>717</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>739</v>
-      </c>
-      <c r="F40" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=837006412005","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>740</v>
-      </c>
-      <c r="H40" s="1" t="n">
-        <v>200</v>
-      </c>
-      <c r="I40" s="8" t="s">
-        <v>741</v>
-      </c>
-      <c r="J40" s="8" t="n">
-        <v>116</v>
-      </c>
-      <c r="K40" s="18" t="n">
-        <v>4.27</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="8" t="s">
-        <v>714</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>742</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>743</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>717</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>739</v>
-      </c>
-      <c r="F41" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=837006412005","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>744</v>
-      </c>
-      <c r="H41" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I41" s="8" t="s">
-        <v>741</v>
-      </c>
-      <c r="J41" s="8" t="n">
-        <v>115</v>
-      </c>
-      <c r="K41" s="18" t="n">
-        <v>3.03</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="8" t="s">
-        <v>714</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>745</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>746</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>717</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>739</v>
-      </c>
-      <c r="F42" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=837006412005","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>747</v>
-      </c>
-      <c r="H42" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I42" s="8" t="s">
-        <v>741</v>
-      </c>
-      <c r="J42" s="8" t="n">
-        <v>113</v>
-      </c>
-      <c r="K42" s="18" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="8" t="s">
-        <v>714</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>749</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>717</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>739</v>
-      </c>
-      <c r="F43" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=837006412005","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>750</v>
-      </c>
-      <c r="H43" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="I43" s="8" t="s">
-        <v>741</v>
-      </c>
-      <c r="J43" s="8" t="n">
-        <v>114</v>
-      </c>
-      <c r="K43" s="18" t="n">
-        <v>3.52</v>
-      </c>
-    </row>
+    <row r="40" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="42" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="43" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -12477,7 +12645,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J121"/>
+  <dimension ref="A1:J117"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -12505,7 +12673,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>751</v>
+        <v>737</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -12519,7 +12687,7 @@
     </row>
     <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>752</v>
+        <v>738</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -12533,7 +12701,7 @@
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>753</v>
+        <v>739</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -12547,7 +12715,7 @@
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>754</v>
+        <v>740</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -12564,31 +12732,31 @@
         <v>553</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>755</v>
+        <v>741</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>756</v>
+        <v>742</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>757</v>
+        <v>743</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>758</v>
+        <v>744</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>759</v>
+        <v>745</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>760</v>
+        <v>746</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>761</v>
+        <v>747</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>550</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>762</v>
+        <v>748</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12599,13 +12767,13 @@
         <v>46306</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>763</v>
+        <v>749</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>262</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>764</v>
+        <v>750</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>260</v>
@@ -12621,7 +12789,7 @@
         <v>打开商品</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>765</v>
+        <v>751</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12632,13 +12800,13 @@
         <v>46305</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>763</v>
+        <v>749</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>636</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>766</v>
+        <v>752</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>637</v>
@@ -12654,7 +12822,7 @@
         <v>打开商品</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>767</v>
+        <v>753</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12665,13 +12833,13 @@
         <v>46297</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>763</v>
+        <v>749</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>658</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>768</v>
+        <v>754</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>659</v>
@@ -12687,7 +12855,7 @@
         <v>打开商品</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>767</v>
+        <v>753</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12698,16 +12866,16 @@
         <v>46297</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>763</v>
+        <v>749</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>658</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>769</v>
+        <v>755</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>770</v>
+        <v>756</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>10</v>
@@ -12720,7 +12888,7 @@
         <v>打开商品</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>767</v>
+        <v>753</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12731,16 +12899,16 @@
         <v>46293</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>237</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>772</v>
+        <v>758</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>773</v>
+        <v>759</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>1</v>
@@ -12753,7 +12921,7 @@
         <v>打开商品</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>765</v>
+        <v>751</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12764,16 +12932,16 @@
         <v>46293</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>774</v>
+        <v>760</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>775</v>
+        <v>761</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>776</v>
+        <v>762</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>1</v>
@@ -12786,7 +12954,7 @@
         <v>打开商品</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>777</v>
+        <v>763</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12797,13 +12965,13 @@
         <v>46291</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>647</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>778</v>
+        <v>764</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>653</v>
@@ -12819,7 +12987,7 @@
         <v>打开商品</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>767</v>
+        <v>753</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12830,13 +12998,13 @@
         <v>46291</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>647</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>778</v>
+        <v>764</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>648</v>
@@ -12852,7 +13020,7 @@
         <v>打开商品</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>767</v>
+        <v>753</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12863,16 +13031,16 @@
         <v>46290</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>779</v>
+        <v>765</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>780</v>
+        <v>766</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>781</v>
+        <v>767</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>1</v>
@@ -12885,7 +13053,7 @@
         <v>打开商品</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>782</v>
+        <v>768</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12896,13 +13064,13 @@
         <v>46290</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>636</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>783</v>
+        <v>769</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>641</v>
@@ -12918,7 +13086,7 @@
         <v>打开商品</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>767</v>
+        <v>753</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12929,13 +13097,13 @@
         <v>46287</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>591</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>784</v>
+        <v>770</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>592</v>
@@ -12962,16 +13130,16 @@
         <v>46282</v>
       </c>
       <c r="C18" s="8" t="s">
+        <v>757</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>771</v>
       </c>
-      <c r="D18" s="8" t="s">
-        <v>785</v>
-      </c>
       <c r="E18" s="8" t="s">
-        <v>786</v>
+        <v>772</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>787</v>
+        <v>773</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>1</v>
@@ -12984,7 +13152,7 @@
         <v>打开商品</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>788</v>
+        <v>774</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12995,13 +13163,13 @@
         <v>46282</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>27</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>789</v>
+        <v>775</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>33</v>
@@ -13028,13 +13196,13 @@
         <v>46282</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>141</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>163</v>
@@ -13061,13 +13229,13 @@
         <v>46282</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>141</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>142</v>
@@ -13083,7 +13251,7 @@
         <v>打开商品</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>765</v>
+        <v>751</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13094,13 +13262,13 @@
         <v>46282</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>141</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>243</v>
@@ -13127,16 +13295,16 @@
         <v>46279</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>774</v>
+        <v>760</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>791</v>
+        <v>777</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>792</v>
+        <v>778</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>1</v>
@@ -13149,7 +13317,7 @@
         <v>打开商品</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>793</v>
+        <v>779</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13160,13 +13328,13 @@
         <v>46279</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>103</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>586</v>
@@ -13193,13 +13361,13 @@
         <v>46279</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>27</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>789</v>
+        <v>775</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>28</v>
@@ -13215,7 +13383,7 @@
         <v>打开商品</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13226,13 +13394,13 @@
         <v>46279</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>27</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>796</v>
+        <v>782</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>43</v>
@@ -13248,7 +13416,7 @@
         <v>打开商品</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>797</v>
+        <v>783</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13259,13 +13427,13 @@
         <v>46279</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>141</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>142</v>
@@ -13292,13 +13460,13 @@
         <v>46279</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>798</v>
+        <v>784</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>575</v>
@@ -13325,13 +13493,13 @@
         <v>46279</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>798</v>
+        <v>784</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>570</v>
@@ -13358,13 +13526,13 @@
         <v>46279</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>798</v>
+        <v>784</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>580</v>
@@ -13391,13 +13559,13 @@
         <v>46276</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>262</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>764</v>
+        <v>750</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>260</v>
@@ -13424,13 +13592,13 @@
         <v>46276</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>603</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>799</v>
+        <v>785</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>604</v>
@@ -13457,13 +13625,13 @@
         <v>46276</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>133</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>800</v>
+        <v>786</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>134</v>
@@ -13490,13 +13658,13 @@
         <v>46276</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>66</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>801</v>
+        <v>787</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>67</v>
@@ -13523,16 +13691,16 @@
         <v>46276</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>802</v>
+        <v>788</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>803</v>
+        <v>789</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>804</v>
+        <v>790</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>10</v>
@@ -13545,7 +13713,7 @@
         <v>打开商品</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>805</v>
+        <v>791</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13556,13 +13724,13 @@
         <v>46276</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>53</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>806</v>
+        <v>792</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>54</v>
@@ -13589,13 +13757,13 @@
         <v>46275</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>610</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>807</v>
+        <v>793</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>611</v>
@@ -13622,13 +13790,13 @@
         <v>46274</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>226</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>808</v>
+        <v>794</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>598</v>
@@ -13655,16 +13823,16 @@
         <v>46274</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>809</v>
+        <v>795</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>810</v>
+        <v>796</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>811</v>
+        <v>797</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>1</v>
@@ -13677,7 +13845,7 @@
         <v>打开商品</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>812</v>
+        <v>798</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13688,16 +13856,16 @@
         <v>46274</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>813</v>
+        <v>799</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>814</v>
+        <v>800</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>815</v>
+        <v>801</v>
       </c>
       <c r="G40" s="9" t="n">
         <v>1</v>
@@ -13710,7 +13878,7 @@
         <v>打开商品</v>
       </c>
       <c r="J40" s="8" t="s">
-        <v>816</v>
+        <v>802</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13721,16 +13889,16 @@
         <v>46274</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>817</v>
+        <v>803</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>818</v>
+        <v>804</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>819</v>
+        <v>805</v>
       </c>
       <c r="G41" s="9" t="n">
         <v>1</v>
@@ -13743,7 +13911,7 @@
         <v>打开商品</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>820</v>
+        <v>806</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13754,13 +13922,13 @@
         <v>46272</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>798</v>
+        <v>784</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>109</v>
@@ -13787,13 +13955,13 @@
         <v>46272</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>798</v>
+        <v>784</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>92</v>
@@ -13820,13 +13988,13 @@
         <v>46272</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>821</v>
+        <v>807</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>179</v>
@@ -13853,13 +14021,13 @@
         <v>46272</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>72</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>822</v>
+        <v>808</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>128</v>
@@ -13886,13 +14054,13 @@
         <v>46272</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D46" s="8" t="s">
         <v>72</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>823</v>
+        <v>809</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>73</v>
@@ -13919,13 +14087,13 @@
         <v>46272</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>59</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>824</v>
+        <v>810</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>60</v>
@@ -13952,13 +14120,13 @@
         <v>46272</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D48" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>825</v>
+        <v>811</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>85</v>
@@ -13985,13 +14153,13 @@
         <v>46272</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>825</v>
+        <v>811</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>80</v>
@@ -14018,13 +14186,13 @@
         <v>46272</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D50" s="8" t="s">
         <v>115</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>826</v>
+        <v>812</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>116</v>
@@ -14051,13 +14219,13 @@
         <v>46272</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>184</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>827</v>
+        <v>813</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>190</v>
@@ -14084,13 +14252,13 @@
         <v>46272</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>184</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>827</v>
+        <v>813</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>195</v>
@@ -14117,13 +14285,13 @@
         <v>46272</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>184</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>827</v>
+        <v>813</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>185</v>
@@ -14150,13 +14318,13 @@
         <v>46272</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>211</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>828</v>
+        <v>814</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>212</v>
@@ -14183,13 +14351,13 @@
         <v>46272</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>168</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>829</v>
+        <v>815</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>165</v>
@@ -14216,16 +14384,16 @@
         <v>46272</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>830</v>
+        <v>816</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>831</v>
+        <v>817</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>832</v>
+        <v>818</v>
       </c>
       <c r="G56" s="9" t="n">
         <v>1</v>
@@ -14238,7 +14406,7 @@
         <v>打开商品</v>
       </c>
       <c r="J56" s="8" t="s">
-        <v>765</v>
+        <v>751</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14249,13 +14417,13 @@
         <v>46272</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D57" s="8" t="s">
         <v>141</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>153</v>
@@ -14282,13 +14450,13 @@
         <v>46272</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>141</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>158</v>
@@ -14315,16 +14483,16 @@
         <v>46272</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>141</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>833</v>
+        <v>819</v>
       </c>
       <c r="G59" s="9" t="n">
         <v>1</v>
@@ -14337,7 +14505,7 @@
         <v>打开商品</v>
       </c>
       <c r="J59" s="8" t="s">
-        <v>834</v>
+        <v>820</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14348,13 +14516,13 @@
         <v>46272</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D60" s="8" t="s">
         <v>204</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>835</v>
+        <v>821</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>205</v>
@@ -14381,13 +14549,13 @@
         <v>46272</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D61" s="8" t="s">
         <v>103</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>836</v>
+        <v>822</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>104</v>
@@ -14414,13 +14582,13 @@
         <v>46272</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>97</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>837</v>
+        <v>823</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>98</v>
@@ -14447,13 +14615,13 @@
         <v>46272</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>122</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>838</v>
+        <v>824</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>123</v>
@@ -14480,13 +14648,13 @@
         <v>46272</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D64" s="8" t="s">
         <v>27</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>839</v>
+        <v>825</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>38</v>
@@ -14513,16 +14681,16 @@
         <v>46272</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>173</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>840</v>
+        <v>826</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>770</v>
+        <v>756</v>
       </c>
       <c r="G65" s="9" t="n">
         <v>5</v>
@@ -14546,16 +14714,16 @@
         <v>46272</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>841</v>
+        <v>827</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>842</v>
+        <v>828</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>770</v>
+        <v>756</v>
       </c>
       <c r="G66" s="9" t="n">
         <v>5</v>
@@ -14568,7 +14736,7 @@
         <v>打开商品</v>
       </c>
       <c r="J66" s="8" t="s">
-        <v>765</v>
+        <v>751</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14579,13 +14747,13 @@
         <v>46269</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D67" s="8" t="s">
         <v>262</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>764</v>
+        <v>750</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>260</v>
@@ -14601,7 +14769,7 @@
         <v>打开商品</v>
       </c>
       <c r="J67" s="8" t="s">
-        <v>765</v>
+        <v>751</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14612,13 +14780,13 @@
         <v>46269</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>262</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>843</v>
+        <v>829</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>260</v>
@@ -14634,7 +14802,7 @@
         <v>打开商品</v>
       </c>
       <c r="J68" s="8" t="s">
-        <v>765</v>
+        <v>751</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14645,13 +14813,13 @@
         <v>46269</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>257</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>844</v>
+        <v>830</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>260</v>
@@ -14667,7 +14835,7 @@
         <v>打开商品</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>765</v>
+        <v>751</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14678,13 +14846,13 @@
         <v>46269</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D70" s="8" t="s">
         <v>257</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>845</v>
+        <v>831</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>258</v>
@@ -14711,16 +14879,16 @@
         <v>46269</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>846</v>
+        <v>832</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>847</v>
+        <v>833</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>848</v>
+        <v>834</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>1</v>
@@ -14733,7 +14901,7 @@
         <v>打开商品</v>
       </c>
       <c r="J71" s="8" t="s">
-        <v>767</v>
+        <v>753</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14744,13 +14912,13 @@
         <v>46269</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D72" s="8" t="s">
         <v>237</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>849</v>
+        <v>835</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>238</v>
@@ -14777,13 +14945,13 @@
         <v>46269</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>27</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>850</v>
+        <v>836</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>217</v>
@@ -14810,16 +14978,16 @@
         <v>46269</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>851</v>
+        <v>837</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>852</v>
+        <v>838</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>853</v>
+        <v>839</v>
       </c>
       <c r="G74" s="9" t="n">
         <v>1</v>
@@ -14832,7 +15000,7 @@
         <v>打开商品</v>
       </c>
       <c r="J74" s="8" t="s">
-        <v>854</v>
+        <v>840</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14843,13 +15011,13 @@
         <v>46269</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D75" s="8" t="s">
         <v>141</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>148</v>
@@ -14876,13 +15044,13 @@
         <v>46269</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D76" s="8" t="s">
         <v>141</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>142</v>
@@ -14898,7 +15066,7 @@
         <v>打开商品</v>
       </c>
       <c r="J76" s="8" t="s">
-        <v>765</v>
+        <v>751</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14909,13 +15077,13 @@
         <v>46269</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>141</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>248</v>
@@ -14942,13 +15110,13 @@
         <v>46269</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>231</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>855</v>
+        <v>841</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>232</v>
@@ -14975,16 +15143,16 @@
         <v>46269</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>231</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>855</v>
+        <v>841</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>856</v>
+        <v>842</v>
       </c>
       <c r="G79" s="9" t="n">
         <v>1</v>
@@ -14997,7 +15165,7 @@
         <v>打开商品</v>
       </c>
       <c r="J79" s="8" t="s">
-        <v>765</v>
+        <v>751</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15008,16 +15176,16 @@
         <v>46269</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>226</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>857</v>
+        <v>843</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>770</v>
+        <v>756</v>
       </c>
       <c r="G80" s="9" t="n">
         <v>50</v>
@@ -15041,16 +15209,16 @@
         <v>46269</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>271</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>858</v>
+        <v>844</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>770</v>
+        <v>756</v>
       </c>
       <c r="G81" s="9" t="n">
         <v>10</v>
@@ -15074,13 +15242,13 @@
         <v>46269</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>266</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>859</v>
+        <v>845</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>264</v>
@@ -15107,16 +15275,16 @@
         <v>46266</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>226</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>844</v>
+        <v>830</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>770</v>
+        <v>756</v>
       </c>
       <c r="G83" s="9" t="n">
         <v>1</v>
@@ -15129,7 +15297,7 @@
         <v>打开商品</v>
       </c>
       <c r="J83" s="8" t="s">
-        <v>765</v>
+        <v>751</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15140,13 +15308,13 @@
         <v>46258</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D84" s="8" t="s">
         <v>27</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>789</v>
+        <v>775</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>28</v>
@@ -15162,7 +15330,7 @@
         <v>打开商品</v>
       </c>
       <c r="J84" s="8" t="s">
-        <v>765</v>
+        <v>751</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15173,13 +15341,13 @@
         <v>46258</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D85" s="8" t="s">
         <v>168</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>860</v>
+        <v>846</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>197</v>
@@ -15206,13 +15374,13 @@
         <v>46258</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D86" s="8" t="s">
         <v>27</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>796</v>
+        <v>782</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>43</v>
@@ -15228,7 +15396,7 @@
         <v>打开商品</v>
       </c>
       <c r="J86" s="8" t="s">
-        <v>765</v>
+        <v>751</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15239,13 +15407,13 @@
         <v>46258</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D87" s="8" t="s">
         <v>27</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>861</v>
+        <v>847</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>48</v>
@@ -15272,16 +15440,16 @@
         <v>46256</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>862</v>
+        <v>848</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>863</v>
+        <v>849</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>864</v>
+        <v>850</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>865</v>
+        <v>851</v>
       </c>
       <c r="G88" s="9" t="n">
         <v>1</v>
@@ -15294,7 +15462,7 @@
         <v>打开商品</v>
       </c>
       <c r="J88" s="8" t="s">
-        <v>866</v>
+        <v>852</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15305,13 +15473,13 @@
         <v>46254</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D89" s="8" t="s">
         <v>141</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>253</v>
@@ -15338,16 +15506,16 @@
         <v>46253</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>867</v>
+        <v>853</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>868</v>
+        <v>854</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>869</v>
+        <v>855</v>
       </c>
       <c r="G90" s="9" t="n">
         <v>1</v>
@@ -15360,7 +15528,7 @@
         <v>打开商品</v>
       </c>
       <c r="J90" s="8" t="s">
-        <v>870</v>
+        <v>856</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15371,13 +15539,13 @@
         <v>46300.4844444444</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>763</v>
+        <v>749</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>718</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>871</v>
+        <v>857</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>723</v>
@@ -15393,7 +15561,7 @@
         <v>打开订单商品</v>
       </c>
       <c r="J91" s="8" t="s">
-        <v>872</v>
+        <v>858</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15404,13 +15572,13 @@
         <v>46294.9525925926</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D92" s="8" t="s">
         <v>629</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>873</v>
+        <v>859</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>630</v>
@@ -15426,7 +15594,7 @@
         <v>打开订单商品</v>
       </c>
       <c r="J92" s="8" t="s">
-        <v>874</v>
+        <v>860</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15437,13 +15605,13 @@
         <v>46291.7980902778</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D93" s="8" t="s">
         <v>669</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>875</v>
+        <v>861</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>670</v>
@@ -15459,7 +15627,7 @@
         <v>打开订单商品</v>
       </c>
       <c r="J93" s="8" t="s">
-        <v>876</v>
+        <v>862</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15470,13 +15638,13 @@
         <v>46291.7979166667</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D94" s="8" t="s">
         <v>669</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>875</v>
+        <v>861</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>670</v>
@@ -15492,7 +15660,7 @@
         <v>打开订单商品</v>
       </c>
       <c r="J94" s="8" t="s">
-        <v>877</v>
+        <v>863</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15503,13 +15671,13 @@
         <v>46291.0479398148</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D95" s="8" t="s">
         <v>675</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>878</v>
+        <v>864</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>676</v>
@@ -15525,7 +15693,7 @@
         <v>打开订单商品</v>
       </c>
       <c r="J95" s="8" t="s">
-        <v>879</v>
+        <v>865</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15536,13 +15704,13 @@
         <v>46289.0137384259</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D96" s="8" t="s">
         <v>699</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>880</v>
+        <v>866</v>
       </c>
       <c r="F96" s="8" t="s">
         <v>700</v>
@@ -15558,7 +15726,7 @@
         <v>打开订单商品</v>
       </c>
       <c r="J96" s="8" t="s">
-        <v>881</v>
+        <v>867</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15569,16 +15737,16 @@
         <v>46286.4381134259</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>882</v>
+        <v>868</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>883</v>
+        <v>869</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>884</v>
+        <v>870</v>
       </c>
       <c r="G97" s="9" t="n">
         <v>1</v>
@@ -15591,7 +15759,7 @@
         <v>打开订单商品</v>
       </c>
       <c r="J97" s="8" t="s">
-        <v>885</v>
+        <v>871</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15602,16 +15770,16 @@
         <v>46286.4381134259</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>882</v>
+        <v>868</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>883</v>
+        <v>869</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>886</v>
+        <v>872</v>
       </c>
       <c r="G98" s="9" t="n">
         <v>1</v>
@@ -15624,7 +15792,7 @@
         <v>打开订单商品</v>
       </c>
       <c r="J98" s="8" t="s">
-        <v>887</v>
+        <v>873</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15635,13 +15803,13 @@
         <v>46277.8198726852</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D99" s="8" t="s">
         <v>718</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>871</v>
+        <v>857</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>733</v>
@@ -15657,7 +15825,7 @@
         <v>打开订单商品</v>
       </c>
       <c r="J99" s="8" t="s">
-        <v>888</v>
+        <v>874</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15668,13 +15836,13 @@
         <v>46277.8198726852</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D100" s="8" t="s">
         <v>718</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>871</v>
+        <v>857</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>730</v>
@@ -15690,7 +15858,7 @@
         <v>打开订单商品</v>
       </c>
       <c r="J100" s="8" t="s">
-        <v>889</v>
+        <v>875</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15701,13 +15869,13 @@
         <v>46277.8198726852</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D101" s="8" t="s">
         <v>718</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>871</v>
+        <v>857</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>727</v>
@@ -15723,7 +15891,7 @@
         <v>打开订单商品</v>
       </c>
       <c r="J101" s="8" t="s">
-        <v>890</v>
+        <v>876</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15734,13 +15902,13 @@
         <v>46277.8198726852</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D102" s="8" t="s">
         <v>718</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>871</v>
+        <v>857</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>719</v>
@@ -15756,7 +15924,7 @@
         <v>打开订单商品</v>
       </c>
       <c r="J102" s="8" t="s">
-        <v>891</v>
+        <v>877</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15767,13 +15935,13 @@
         <v>46277.8198726852</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D103" s="8" t="s">
         <v>718</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>871</v>
+        <v>857</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>736</v>
@@ -15789,7 +15957,7 @@
         <v>打开订单商品</v>
       </c>
       <c r="J103" s="8" t="s">
-        <v>892</v>
+        <v>878</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15800,13 +15968,13 @@
         <v>46274.8817939815</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D104" s="8" t="s">
         <v>617</v>
       </c>
       <c r="E104" s="8" t="s">
-        <v>893</v>
+        <v>879</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>615</v>
@@ -15822,7 +15990,7 @@
         <v>打开订单商品</v>
       </c>
       <c r="J104" s="8" t="s">
-        <v>894</v>
+        <v>880</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15833,13 +16001,13 @@
         <v>46272.8961458333</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D105" s="8" t="s">
         <v>706</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>895</v>
+        <v>881</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>707</v>
@@ -15855,7 +16023,7 @@
         <v>打开订单商品</v>
       </c>
       <c r="J105" s="8" t="s">
-        <v>896</v>
+        <v>882</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15866,13 +16034,13 @@
         <v>46272.8961458333</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D106" s="8" t="s">
         <v>706</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>897</v>
+        <v>883</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>712</v>
@@ -15888,502 +16056,370 @@
         <v>打开订单商品</v>
       </c>
       <c r="J106" s="8" t="s">
-        <v>898</v>
+        <v>884</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="n">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="B107" s="19" t="n">
-        <v>46272.7650694444</v>
+        <v>46266.8829513889</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>739</v>
+        <v>617</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>899</v>
+        <v>879</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>747</v>
+        <v>615</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H107" s="20" t="n">
-        <v>3.2</v>
+        <v>99</v>
       </c>
       <c r="I107" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=837006412005","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1078248851201","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J107" s="8" t="s">
-        <v>900</v>
+        <v>885</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="n">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="B108" s="19" t="n">
-        <v>46272.7650694444</v>
+        <v>46266.8829513889</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>739</v>
+        <v>617</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>899</v>
+        <v>879</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>750</v>
+        <v>886</v>
       </c>
       <c r="G108" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H108" s="20" t="n">
-        <v>3.52</v>
+        <v>45</v>
       </c>
       <c r="I108" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=837006412005","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1078248851201","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J108" s="8" t="s">
-        <v>901</v>
+        <v>887</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="n">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="B109" s="19" t="n">
-        <v>46272.7650694444</v>
+        <v>46266.6967476852</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>739</v>
+        <v>706</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>899</v>
+        <v>883</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>744</v>
+        <v>712</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H109" s="20" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="I109" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=837006412005","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=733598659967","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J109" s="8" t="s">
-        <v>902</v>
+        <v>888</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="n">
-        <v>116</v>
+        <v>173</v>
       </c>
       <c r="B110" s="19" t="n">
-        <v>46272.7650694444</v>
+        <v>46266.6967476852</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>739</v>
+        <v>706</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>899</v>
+        <v>881</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>740</v>
+        <v>707</v>
       </c>
       <c r="G110" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H110" s="20" t="n">
-        <v>4.27</v>
+        <v>1.94</v>
       </c>
       <c r="I110" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=837006412005","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=625390659071","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J110" s="8" t="s">
-        <v>903</v>
+        <v>889</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="B111" s="19" t="n">
-        <v>46266.8829513889</v>
+        <v>46265.3613773148</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H111" s="20" t="n">
-        <v>99</v>
+        <v>129.99</v>
       </c>
       <c r="I111" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1078248851201","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=768918125679","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J111" s="8" t="s">
-        <v>904</v>
+        <v>891</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="n">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="B112" s="19" t="n">
-        <v>46266.8829513889</v>
+        <v>46259.9707407408</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>617</v>
+        <v>765</v>
       </c>
       <c r="E112" s="8" t="s">
+        <v>892</v>
+      </c>
+      <c r="F112" s="8" t="s">
         <v>893</v>
       </c>
-      <c r="F112" s="8" t="s">
-        <v>905</v>
-      </c>
       <c r="G112" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H112" s="20" t="n">
-        <v>45</v>
+        <v>106.68</v>
       </c>
       <c r="I112" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1078248851201","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=588102758150","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J112" s="8" t="s">
-        <v>906</v>
+        <v>894</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="n">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="B113" s="19" t="n">
-        <v>46266.6967476852</v>
+        <v>46258.6749768519</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>706</v>
+        <v>682</v>
       </c>
       <c r="E113" s="8" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>712</v>
+        <v>683</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H113" s="20" t="n">
-        <v>2.91</v>
+        <v>0.01</v>
       </c>
       <c r="I113" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=733598659967","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=701774753211","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J113" s="8" t="s">
-        <v>907</v>
+        <v>896</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="n">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="B114" s="19" t="n">
-        <v>46266.6967476852</v>
+        <v>46258.6749768519</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D114" s="8" t="s">
-        <v>706</v>
+        <v>682</v>
       </c>
       <c r="E114" s="8" t="s">
         <v>895</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>707</v>
+        <v>688</v>
       </c>
       <c r="G114" s="9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H114" s="20" t="n">
-        <v>1.94</v>
+        <v>0.02</v>
       </c>
       <c r="I114" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=625390659071","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=701774753211","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J114" s="8" t="s">
-        <v>908</v>
+        <v>897</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="n">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="B115" s="19" t="n">
-        <v>46265.3613773148</v>
+        <v>46258.6749768519</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D115" s="8" t="s">
-        <v>610</v>
+        <v>682</v>
       </c>
       <c r="E115" s="8" t="s">
-        <v>909</v>
+        <v>895</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>623</v>
+        <v>693</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H115" s="20" t="n">
-        <v>129.99</v>
+        <v>0.03</v>
       </c>
       <c r="I115" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=768918125679","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=701774753211","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J115" s="8" t="s">
-        <v>910</v>
+        <v>898</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="n">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="B116" s="19" t="n">
-        <v>46259.9707407408</v>
+        <v>46254.6453587963</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D116" s="8" t="s">
-        <v>779</v>
+        <v>849</v>
       </c>
       <c r="E116" s="8" t="s">
-        <v>911</v>
+        <v>850</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>912</v>
+        <v>851</v>
       </c>
       <c r="G116" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H116" s="20" t="n">
-        <v>106.68</v>
+        <v>188</v>
       </c>
       <c r="I116" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=588102758150","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=956985590887","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J116" s="8" t="s">
-        <v>913</v>
+        <v>899</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="n">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="B117" s="19" t="n">
-        <v>46258.6749768519</v>
+        <v>46254.0581481482</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>682</v>
+        <v>900</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>914</v>
+        <v>901</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>683</v>
+        <v>902</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H117" s="20" t="n">
-        <v>0.01</v>
+        <v>4.69</v>
       </c>
       <c r="I117" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=701774753211","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=621018369847","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J117" s="8" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="1" t="n">
-        <v>201</v>
-      </c>
-      <c r="B118" s="19" t="n">
-        <v>46258.6749768519</v>
-      </c>
-      <c r="C118" s="8" t="s">
-        <v>771</v>
-      </c>
-      <c r="D118" s="8" t="s">
-        <v>682</v>
-      </c>
-      <c r="E118" s="8" t="s">
-        <v>914</v>
-      </c>
-      <c r="F118" s="8" t="s">
-        <v>688</v>
-      </c>
-      <c r="G118" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H118" s="20" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I118" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=701774753211","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="J118" s="8" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="1" t="n">
-        <v>202</v>
-      </c>
-      <c r="B119" s="19" t="n">
-        <v>46258.6749768519</v>
-      </c>
-      <c r="C119" s="8" t="s">
-        <v>771</v>
-      </c>
-      <c r="D119" s="8" t="s">
-        <v>682</v>
-      </c>
-      <c r="E119" s="8" t="s">
-        <v>914</v>
-      </c>
-      <c r="F119" s="8" t="s">
-        <v>693</v>
-      </c>
-      <c r="G119" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H119" s="20" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I119" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=701774753211","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="J119" s="8" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="1" t="n">
-        <v>211</v>
-      </c>
-      <c r="B120" s="19" t="n">
-        <v>46254.6453587963</v>
-      </c>
-      <c r="C120" s="8" t="s">
-        <v>771</v>
-      </c>
-      <c r="D120" s="8" t="s">
-        <v>863</v>
-      </c>
-      <c r="E120" s="8" t="s">
-        <v>864</v>
-      </c>
-      <c r="F120" s="8" t="s">
-        <v>865</v>
-      </c>
-      <c r="G120" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H120" s="20" t="n">
-        <v>188</v>
-      </c>
-      <c r="I120" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=956985590887","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="J120" s="8" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="1" t="n">
-        <v>214</v>
-      </c>
-      <c r="B121" s="19" t="n">
-        <v>46254.0581481482</v>
-      </c>
-      <c r="C121" s="8" t="s">
-        <v>771</v>
-      </c>
-      <c r="D121" s="8" t="s">
-        <v>919</v>
-      </c>
-      <c r="E121" s="8" t="s">
-        <v>920</v>
-      </c>
-      <c r="F121" s="8" t="s">
-        <v>921</v>
-      </c>
-      <c r="G121" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H121" s="20" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="I121" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=621018369847","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="J121" s="8" t="s">
-        <v>922</v>
+        <v>903</v>
       </c>
     </row>
   </sheetData>
@@ -16437,7 +16473,7 @@
     </row>
     <row r="2" customFormat="false" ht="27.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="22" t="s">
-        <v>923</v>
+        <v>904</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -16452,7 +16488,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>924</v>
+        <v>905</v>
       </c>
       <c r="B3" s="21"/>
       <c r="C3" s="21"/>
@@ -16467,7 +16503,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>925</v>
+        <v>906</v>
       </c>
       <c r="B4" s="21"/>
       <c r="C4" s="21"/>
@@ -16532,32 +16568,32 @@
     </row>
     <row r="7" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>926</v>
+        <v>907</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>854</v>
+        <v>840</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>927</v>
+        <v>908</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>928</v>
+        <v>909</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>851</v>
+        <v>837</v>
       </c>
       <c r="F7" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=581798084270","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>853</v>
+        <v>839</v>
       </c>
       <c r="H7" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>929</v>
+        <v>910</v>
       </c>
       <c r="J7" s="21" t="n">
         <v>154</v>
@@ -16568,32 +16604,32 @@
     </row>
     <row r="8" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>930</v>
+        <v>911</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>820</v>
+        <v>806</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>931</v>
+        <v>912</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>932</v>
+        <v>913</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>817</v>
+        <v>803</v>
       </c>
       <c r="F8" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=851008959999","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>819</v>
+        <v>805</v>
       </c>
       <c r="H8" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="21" t="s">
-        <v>933</v>
+        <v>914</v>
       </c>
       <c r="J8" s="21" t="n">
         <v>107</v>
@@ -16604,32 +16640,32 @@
     </row>
     <row r="9" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>930</v>
+        <v>911</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>816</v>
+        <v>802</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>934</v>
+        <v>915</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>928</v>
+        <v>909</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>813</v>
+        <v>799</v>
       </c>
       <c r="F9" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=19606507546","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>815</v>
+        <v>801</v>
       </c>
       <c r="H9" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I9" s="21" t="s">
-        <v>935</v>
+        <v>916</v>
       </c>
       <c r="J9" s="21" t="n">
         <v>106</v>
@@ -16640,32 +16676,32 @@
     </row>
     <row r="10" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>930</v>
+        <v>911</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>782</v>
+        <v>768</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>936</v>
+        <v>917</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>937</v>
+        <v>918</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>779</v>
+        <v>765</v>
       </c>
       <c r="F10" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=626569273184","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>781</v>
+        <v>767</v>
       </c>
       <c r="H10" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>938</v>
+        <v>919</v>
       </c>
       <c r="J10" s="21" t="n">
         <v>35</v>
@@ -16676,32 +16712,32 @@
     </row>
     <row r="11" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>939</v>
+        <v>920</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>812</v>
+        <v>798</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>928</v>
+        <v>909</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>809</v>
+        <v>795</v>
       </c>
       <c r="F11" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=979077591318","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>811</v>
+        <v>797</v>
       </c>
       <c r="H11" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I11" s="21" t="s">
-        <v>941</v>
+        <v>922</v>
       </c>
       <c r="J11" s="21" t="n">
         <v>105</v>
@@ -16712,32 +16748,32 @@
     </row>
     <row r="12" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>939</v>
+        <v>920</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>866</v>
+        <v>852</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>942</v>
+        <v>923</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>928</v>
+        <v>909</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>863</v>
+        <v>849</v>
       </c>
       <c r="F12" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=956985590887","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>865</v>
+        <v>851</v>
       </c>
       <c r="H12" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>943</v>
+        <v>924</v>
       </c>
       <c r="J12" s="21" t="n">
         <v>211</v>
@@ -16748,32 +16784,32 @@
     </row>
     <row r="13" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>944</v>
+        <v>925</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>788</v>
+        <v>774</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>945</v>
+        <v>926</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>946</v>
+        <v>927</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="F13" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=566089419587","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>787</v>
+        <v>773</v>
       </c>
       <c r="H13" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I13" s="21" t="s">
-        <v>947</v>
+        <v>928</v>
       </c>
       <c r="J13" s="21" t="n">
         <v>43</v>
@@ -16784,32 +16820,32 @@
     </row>
     <row r="14" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>948</v>
+        <v>929</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>793</v>
+        <v>779</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>949</v>
+        <v>930</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>946</v>
+        <v>927</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>774</v>
+        <v>760</v>
       </c>
       <c r="F14" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=972313702890","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>792</v>
+        <v>778</v>
       </c>
       <c r="H14" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>950</v>
+        <v>931</v>
       </c>
       <c r="J14" s="21" t="n">
         <v>76</v>
@@ -16820,32 +16856,32 @@
     </row>
     <row r="15" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>930</v>
+        <v>911</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>870</v>
+        <v>856</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>951</v>
+        <v>932</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>928</v>
+        <v>909</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>867</v>
+        <v>853</v>
       </c>
       <c r="F15" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=744370287305","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>869</v>
+        <v>855</v>
       </c>
       <c r="H15" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I15" s="21" t="s">
-        <v>952</v>
+        <v>933</v>
       </c>
       <c r="J15" s="21" t="n">
         <v>220</v>
@@ -16856,32 +16892,32 @@
     </row>
     <row r="16" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>953</v>
+        <v>934</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>777</v>
+        <v>763</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>954</v>
+        <v>935</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>928</v>
+        <v>909</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>774</v>
+        <v>760</v>
       </c>
       <c r="F16" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1049340097483","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G16" s="21" t="s">
-        <v>776</v>
+        <v>762</v>
       </c>
       <c r="H16" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I16" s="21" t="s">
-        <v>955</v>
+        <v>936</v>
       </c>
       <c r="J16" s="21" t="n">
         <v>24</v>
@@ -16892,16 +16928,16 @@
     </row>
     <row r="17" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>956</v>
+        <v>937</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>957</v>
+        <v>938</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>958</v>
+        <v>939</v>
       </c>
       <c r="E17" s="21" t="s">
         <v>617</v>
@@ -16911,13 +16947,13 @@
         <v>打开订单商品</v>
       </c>
       <c r="G17" s="21" t="s">
-        <v>905</v>
+        <v>886</v>
       </c>
       <c r="H17" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I17" s="21" t="s">
-        <v>959</v>
+        <v>940</v>
       </c>
       <c r="J17" s="21" t="n">
         <v>169</v>
@@ -16928,32 +16964,32 @@
     </row>
     <row r="18" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>960</v>
+        <v>941</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>961</v>
+        <v>942</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>962</v>
+        <v>943</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>963</v>
+        <v>944</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>779</v>
+        <v>765</v>
       </c>
       <c r="F18" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=588102758150","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G18" s="21" t="s">
-        <v>912</v>
+        <v>893</v>
       </c>
       <c r="H18" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I18" s="21" t="s">
-        <v>964</v>
+        <v>945</v>
       </c>
       <c r="J18" s="21" t="n">
         <v>189</v>
@@ -16964,32 +17000,32 @@
     </row>
     <row r="19" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>965</v>
+        <v>946</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>966</v>
+        <v>947</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>967</v>
+        <v>948</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>968</v>
+        <v>949</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>882</v>
+        <v>868</v>
       </c>
       <c r="F19" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=567201709691","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G19" s="21" t="s">
-        <v>884</v>
+        <v>870</v>
       </c>
       <c r="H19" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>969</v>
+        <v>950</v>
       </c>
       <c r="J19" s="21" t="n">
         <v>39</v>
@@ -17000,32 +17036,32 @@
     </row>
     <row r="20" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>965</v>
+        <v>946</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>970</v>
+        <v>951</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>971</v>
+        <v>952</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>968</v>
+        <v>949</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>882</v>
+        <v>868</v>
       </c>
       <c r="F20" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=567201709691","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G20" s="21" t="s">
-        <v>886</v>
+        <v>872</v>
       </c>
       <c r="H20" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I20" s="21" t="s">
-        <v>972</v>
+        <v>953</v>
       </c>
       <c r="J20" s="21" t="n">
         <v>40</v>
@@ -17036,32 +17072,32 @@
     </row>
     <row r="21" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>930</v>
+        <v>911</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>973</v>
+        <v>954</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>974</v>
+        <v>955</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>975</v>
+        <v>956</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>919</v>
+        <v>900</v>
       </c>
       <c r="F21" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=621018369847","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G21" s="21" t="s">
-        <v>921</v>
+        <v>902</v>
       </c>
       <c r="H21" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I21" s="21" t="s">
-        <v>976</v>
+        <v>957</v>
       </c>
       <c r="J21" s="21" t="n">
         <v>214</v>
@@ -17129,7 +17165,7 @@
     </row>
     <row r="2" customFormat="false" ht="27.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="22" t="s">
-        <v>977</v>
+        <v>958</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -17148,7 +17184,7 @@
     </row>
     <row r="3" customFormat="false" ht="40" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>978</v>
+        <v>959</v>
       </c>
       <c r="B3" s="21"/>
       <c r="C3" s="21"/>
@@ -17194,19 +17230,19 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>979</v>
+        <v>960</v>
       </c>
       <c r="B5" s="27" t="n">
         <v>20</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>980</v>
+        <v>961</v>
       </c>
       <c r="D5" s="27" t="n">
         <v>5</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>981</v>
+        <v>962</v>
       </c>
       <c r="F5" s="27" t="n">
         <v>12</v>
@@ -17240,16 +17276,16 @@
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>982</v>
+        <v>963</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>983</v>
+        <v>964</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>984</v>
+        <v>965</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>985</v>
+        <v>966</v>
       </c>
       <c r="E7" s="21"/>
       <c r="F7" s="21"/>
@@ -17265,7 +17301,7 @@
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>986</v>
+        <v>967</v>
       </c>
       <c r="B8" s="25" t="n">
         <f aca="false">SUM(I29:I72)</f>
@@ -17293,7 +17329,7 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>987</v>
+        <v>968</v>
       </c>
       <c r="B9" s="25" t="n">
         <v>0</v>
@@ -17319,7 +17355,7 @@
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="29" t="s">
-        <v>988</v>
+        <v>969</v>
       </c>
       <c r="B10" s="30" t="n">
         <f aca="false">B8+B9</f>
@@ -17347,7 +17383,7 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>989</v>
+        <v>970</v>
       </c>
       <c r="B11" s="25" t="n">
         <f aca="false">$B$5/$D$5*$B$4</f>
@@ -17375,7 +17411,7 @@
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="29" t="s">
-        <v>990</v>
+        <v>971</v>
       </c>
       <c r="B12" s="30" t="n">
         <f aca="false">B8+B11</f>
@@ -17420,7 +17456,7 @@
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>991</v>
+        <v>972</v>
       </c>
       <c r="B14" s="25"/>
       <c r="C14" s="25"/>
@@ -17439,16 +17475,16 @@
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="s">
-        <v>992</v>
+        <v>973</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>993</v>
+        <v>974</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>994</v>
+        <v>975</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>995</v>
+        <v>976</v>
       </c>
       <c r="E15" s="21"/>
       <c r="F15" s="21"/>
@@ -17464,7 +17500,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>996</v>
+        <v>977</v>
       </c>
       <c r="B16" s="25" t="n">
         <f aca="false">SUM(L29:L72)</f>
@@ -17492,7 +17528,7 @@
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="29" t="s">
-        <v>997</v>
+        <v>978</v>
       </c>
       <c r="B17" s="30" t="n">
         <f aca="false">B16</f>
@@ -17520,7 +17556,7 @@
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>998</v>
+        <v>979</v>
       </c>
       <c r="B18" s="25" t="n">
         <f aca="false">ROUNDUP($B$4/$D$5,0)*$B$5</f>
@@ -17548,7 +17584,7 @@
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="29" t="s">
-        <v>999</v>
+        <v>980</v>
       </c>
       <c r="B19" s="30" t="n">
         <f aca="false">B16+B18</f>
@@ -17593,7 +17629,7 @@
     </row>
     <row r="21" customFormat="false" ht="40" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>1000</v>
+        <v>981</v>
       </c>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
@@ -17612,7 +17648,7 @@
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>1001</v>
+        <v>982</v>
       </c>
       <c r="B22" s="25" t="n">
         <f aca="false">配件与耗材!K19</f>
@@ -17634,7 +17670,7 @@
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="29" t="s">
-        <v>1002</v>
+        <v>983</v>
       </c>
       <c r="B23" s="30" t="n">
         <f aca="false">D10+B22</f>
@@ -17656,7 +17692,7 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="29" t="s">
-        <v>1003</v>
+        <v>984</v>
       </c>
       <c r="B24" s="30" t="n">
         <f aca="false">D12+B22</f>
@@ -17695,7 +17731,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>1004</v>
+        <v>985</v>
       </c>
       <c r="B26" s="21"/>
       <c r="C26" s="21"/>
@@ -17731,43 +17767,43 @@
     </row>
     <row r="28" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="23" t="s">
-        <v>1005</v>
+        <v>986</v>
       </c>
       <c r="B28" s="23" t="s">
         <v>552</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>1006</v>
+        <v>987</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>1007</v>
+        <v>988</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>1008</v>
+        <v>989</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>1009</v>
+        <v>990</v>
       </c>
       <c r="G28" s="23" t="s">
-        <v>1010</v>
+        <v>991</v>
       </c>
       <c r="H28" s="23" t="s">
-        <v>1011</v>
+        <v>992</v>
       </c>
       <c r="I28" s="23" t="s">
-        <v>1012</v>
+        <v>993</v>
       </c>
       <c r="J28" s="23" t="s">
-        <v>1013</v>
+        <v>994</v>
       </c>
       <c r="K28" s="23" t="s">
-        <v>1014</v>
+        <v>995</v>
       </c>
       <c r="L28" s="23" t="s">
-        <v>1015</v>
+        <v>996</v>
       </c>
       <c r="M28" s="23" t="s">
-        <v>1016</v>
+        <v>997</v>
       </c>
       <c r="N28" s="23" t="s">
         <v>550</v>
@@ -17778,7 +17814,7 @@
     </row>
     <row r="29" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>1017</v>
+        <v>998</v>
       </c>
       <c r="B29" s="21" t="n">
         <v>1</v>
@@ -17834,7 +17870,7 @@
     </row>
     <row r="30" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>1018</v>
+        <v>999</v>
       </c>
       <c r="B30" s="21" t="n">
         <v>1</v>
@@ -17890,7 +17926,7 @@
     </row>
     <row r="31" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>1019</v>
+        <v>1000</v>
       </c>
       <c r="B31" s="21" t="n">
         <v>100</v>
@@ -17946,7 +17982,7 @@
     </row>
     <row r="32" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>1020</v>
+        <v>1001</v>
       </c>
       <c r="B32" s="21" t="n">
         <v>100</v>
@@ -18002,7 +18038,7 @@
     </row>
     <row r="33" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>1021</v>
+        <v>1002</v>
       </c>
       <c r="B33" s="21" t="n">
         <v>1</v>
@@ -18058,7 +18094,7 @@
     </row>
     <row r="34" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
-        <v>1022</v>
+        <v>1003</v>
       </c>
       <c r="B34" s="21" t="n">
         <v>100</v>
@@ -18114,7 +18150,7 @@
     </row>
     <row r="35" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
-        <v>1023</v>
+        <v>1004</v>
       </c>
       <c r="B35" s="21" t="n">
         <v>100</v>
@@ -18170,7 +18206,7 @@
     </row>
     <row r="36" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>1024</v>
+        <v>1005</v>
       </c>
       <c r="B36" s="21" t="n">
         <v>20</v>
@@ -18226,7 +18262,7 @@
     </row>
     <row r="37" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
-        <v>1025</v>
+        <v>1006</v>
       </c>
       <c r="B37" s="21" t="n">
         <v>50</v>
@@ -18282,7 +18318,7 @@
     </row>
     <row r="38" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="21" t="s">
-        <v>1026</v>
+        <v>1007</v>
       </c>
       <c r="B38" s="21" t="n">
         <v>100</v>
@@ -18338,7 +18374,7 @@
     </row>
     <row r="39" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="21" t="s">
-        <v>1027</v>
+        <v>1008</v>
       </c>
       <c r="B39" s="21" t="n">
         <v>100</v>
@@ -18394,7 +18430,7 @@
     </row>
     <row r="40" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="21" t="s">
-        <v>1028</v>
+        <v>1009</v>
       </c>
       <c r="B40" s="21" t="n">
         <v>50</v>
@@ -18450,7 +18486,7 @@
     </row>
     <row r="41" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="21" t="s">
-        <v>1029</v>
+        <v>1010</v>
       </c>
       <c r="B41" s="21" t="n">
         <v>2</v>
@@ -18506,7 +18542,7 @@
     </row>
     <row r="42" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="21" t="s">
-        <v>1030</v>
+        <v>1011</v>
       </c>
       <c r="B42" s="21" t="n">
         <v>15</v>
@@ -18562,7 +18598,7 @@
     </row>
     <row r="43" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="21" t="s">
-        <v>1031</v>
+        <v>1012</v>
       </c>
       <c r="B43" s="21" t="n">
         <v>50</v>
@@ -18618,7 +18654,7 @@
     </row>
     <row r="44" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="21" t="s">
-        <v>1032</v>
+        <v>1013</v>
       </c>
       <c r="B44" s="21" t="n">
         <v>10</v>
@@ -18674,7 +18710,7 @@
     </row>
     <row r="45" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="21" t="s">
-        <v>1033</v>
+        <v>1014</v>
       </c>
       <c r="B45" s="21" t="n">
         <v>2</v>
@@ -18730,7 +18766,7 @@
     </row>
     <row r="46" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="21" t="s">
-        <v>1034</v>
+        <v>1015</v>
       </c>
       <c r="B46" s="21" t="n">
         <v>50</v>
@@ -18786,7 +18822,7 @@
     </row>
     <row r="47" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="21" t="s">
-        <v>1035</v>
+        <v>1016</v>
       </c>
       <c r="B47" s="21" t="n">
         <v>20</v>
@@ -18842,7 +18878,7 @@
     </row>
     <row r="48" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="21" t="s">
-        <v>1036</v>
+        <v>1017</v>
       </c>
       <c r="B48" s="21" t="n">
         <v>100</v>
@@ -18898,7 +18934,7 @@
     </row>
     <row r="49" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="21" t="s">
-        <v>1037</v>
+        <v>1018</v>
       </c>
       <c r="B49" s="21" t="n">
         <v>100</v>
@@ -18954,7 +18990,7 @@
     </row>
     <row r="50" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="21" t="s">
-        <v>1038</v>
+        <v>1019</v>
       </c>
       <c r="B50" s="21" t="n">
         <v>100</v>
@@ -19010,7 +19046,7 @@
     </row>
     <row r="51" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="21" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="B51" s="21" t="n">
         <v>100</v>
@@ -19066,7 +19102,7 @@
     </row>
     <row r="52" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="21" t="s">
-        <v>1040</v>
+        <v>1021</v>
       </c>
       <c r="B52" s="21" t="n">
         <v>100</v>
@@ -19122,7 +19158,7 @@
     </row>
     <row r="53" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="21" t="s">
-        <v>1041</v>
+        <v>1022</v>
       </c>
       <c r="B53" s="21" t="n">
         <v>1</v>
@@ -19178,7 +19214,7 @@
     </row>
     <row r="54" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="21" t="s">
-        <v>1042</v>
+        <v>1023</v>
       </c>
       <c r="B54" s="21" t="n">
         <v>1</v>
@@ -19234,7 +19270,7 @@
     </row>
     <row r="55" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="21" t="s">
-        <v>1043</v>
+        <v>1024</v>
       </c>
       <c r="B55" s="21" t="n">
         <v>20</v>
@@ -19290,7 +19326,7 @@
     </row>
     <row r="56" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="21" t="s">
-        <v>1044</v>
+        <v>1025</v>
       </c>
       <c r="B56" s="21" t="n">
         <v>5</v>
@@ -19346,7 +19382,7 @@
     </row>
     <row r="57" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="21" t="s">
-        <v>1045</v>
+        <v>1026</v>
       </c>
       <c r="B57" s="21" t="n">
         <v>5</v>
@@ -19402,7 +19438,7 @@
     </row>
     <row r="58" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="21" t="s">
-        <v>1046</v>
+        <v>1027</v>
       </c>
       <c r="B58" s="21" t="n">
         <v>5</v>
@@ -19458,7 +19494,7 @@
     </row>
     <row r="59" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="21" t="s">
-        <v>1047</v>
+        <v>1028</v>
       </c>
       <c r="B59" s="21" t="n">
         <v>1</v>
@@ -19514,7 +19550,7 @@
     </row>
     <row r="60" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="21" t="s">
-        <v>1048</v>
+        <v>1029</v>
       </c>
       <c r="B60" s="21" t="n">
         <v>1</v>
@@ -19570,7 +19606,7 @@
     </row>
     <row r="61" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="21" t="s">
-        <v>1049</v>
+        <v>1030</v>
       </c>
       <c r="B61" s="21" t="n">
         <v>1</v>
@@ -19626,7 +19662,7 @@
     </row>
     <row r="62" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="21" t="s">
-        <v>1050</v>
+        <v>1031</v>
       </c>
       <c r="B62" s="21" t="n">
         <v>1</v>
@@ -19682,7 +19718,7 @@
     </row>
     <row r="63" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="21" t="s">
-        <v>1051</v>
+        <v>1032</v>
       </c>
       <c r="B63" s="21" t="n">
         <v>1</v>
@@ -19738,7 +19774,7 @@
     </row>
     <row r="64" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="21" t="s">
-        <v>1052</v>
+        <v>1033</v>
       </c>
       <c r="B64" s="21" t="n">
         <v>100</v>
@@ -19794,7 +19830,7 @@
     </row>
     <row r="65" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="21" t="s">
-        <v>1053</v>
+        <v>1034</v>
       </c>
       <c r="B65" s="21" t="n">
         <v>30</v>
@@ -19850,7 +19886,7 @@
     </row>
     <row r="66" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="21" t="s">
-        <v>1054</v>
+        <v>1035</v>
       </c>
       <c r="B66" s="21" t="n">
         <v>100</v>
@@ -19906,7 +19942,7 @@
     </row>
     <row r="67" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="21" t="s">
-        <v>1055</v>
+        <v>1036</v>
       </c>
       <c r="B67" s="21" t="n">
         <v>100</v>
@@ -19962,7 +19998,7 @@
     </row>
     <row r="68" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="21" t="s">
-        <v>1056</v>
+        <v>1037</v>
       </c>
       <c r="B68" s="21" t="n">
         <v>100</v>
@@ -20018,7 +20054,7 @@
     </row>
     <row r="69" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="21" t="s">
-        <v>1057</v>
+        <v>1038</v>
       </c>
       <c r="B69" s="21" t="n">
         <v>1</v>
@@ -20074,7 +20110,7 @@
     </row>
     <row r="70" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="21" t="s">
-        <v>1058</v>
+        <v>1039</v>
       </c>
       <c r="B70" s="21" t="n">
         <v>1</v>
@@ -20130,7 +20166,7 @@
     </row>
     <row r="71" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="21" t="s">
-        <v>1059</v>
+        <v>1040</v>
       </c>
       <c r="B71" s="21" t="n">
         <v>1</v>
@@ -20186,7 +20222,7 @@
     </row>
     <row r="72" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="21" t="s">
-        <v>1060</v>
+        <v>1041</v>
       </c>
       <c r="B72" s="21" t="n">
         <v>1</v>
@@ -20258,4 +20294,1114 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF233653"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H42"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="33"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+    </row>
+    <row r="2" customFormat="false" ht="27.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="34" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+    </row>
+    <row r="3" customFormat="false" ht="40" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="33" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+    </row>
+    <row r="4" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="35" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B4" s="36" t="n">
+        <f aca="false">SUM(F11:F42)</f>
+        <v>2244.28313676336</v>
+      </c>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+    </row>
+    <row r="5" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="35" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B5" s="36" t="n">
+        <f aca="false">B4+(D11+D12)*制作成本!$B$5/制作成本!$D$5</f>
+        <v>2252.28313676336</v>
+      </c>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+    </row>
+    <row r="6" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="35" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B6" s="36" t="n">
+        <f aca="false">B4-F11-F12+制作成本!D16</f>
+        <v>2303.34</v>
+      </c>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+    </row>
+    <row r="7" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="35" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B7" s="36" t="n">
+        <f aca="false">B6+ROUNDUP(D11/制作成本!$D$5,0)*制作成本!$B$5+ROUNDUP(D12/制作成本!$D$5,0)*制作成本!$B$5</f>
+        <v>2343.34</v>
+      </c>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="33"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+    </row>
+    <row r="9" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="33" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
+    </row>
+    <row r="10" customFormat="false" ht="40" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="37" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B10" s="37" t="s">
+        <v>986</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>1054</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="33" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D11" s="38" t="n">
+        <f aca="false">合并采购清单!B4</f>
+        <v>1</v>
+      </c>
+      <c r="E11" s="39" t="n">
+        <f aca="false">SUMPRODUCT(制作成本!F29:F72,制作成本!G29:G72)</f>
+        <v>15.5395050849176</v>
+      </c>
+      <c r="F11" s="40" t="n">
+        <f aca="false">D11*E11</f>
+        <v>15.5395050849176</v>
+      </c>
+      <c r="G11" s="33" t="s">
+        <v>1059</v>
+      </c>
+      <c r="H11" s="41" t="str">
+        <f aca="false">HYPERLINK("https://github.com/kissqy/Microduck-kissqy/blob/main/hardware/README.md#完整位号bom","查看完整BOM")</f>
+        <v>查看完整BOM</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="33" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D12" s="38" t="n">
+        <f aca="false">合并采购清单!D4</f>
+        <v>1</v>
+      </c>
+      <c r="E12" s="39" t="n">
+        <f aca="false">SUMPRODUCT(制作成本!F29:F72,制作成本!H29:H72)</f>
+        <v>12.3336316784379</v>
+      </c>
+      <c r="F12" s="40" t="n">
+        <f aca="false">D12*E12</f>
+        <v>12.3336316784379</v>
+      </c>
+      <c r="G12" s="33" t="s">
+        <v>1059</v>
+      </c>
+      <c r="H12" s="41" t="str">
+        <f aca="false">HYPERLINK("https://github.com/kissqy/Microduck-kissqy/blob/main/hardware/README.md#完整位号bom","查看完整BOM")</f>
+        <v>查看完整BOM</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="33" t="s">
+        <v>614</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D13" s="42" t="n">
+        <v>15</v>
+      </c>
+      <c r="E13" s="39" t="n">
+        <f aca="false">配件与耗材!K17</f>
+        <v>99</v>
+      </c>
+      <c r="F13" s="40" t="n">
+        <f aca="false">D13*E13</f>
+        <v>1485</v>
+      </c>
+      <c r="G13" s="33" t="s">
+        <v>618</v>
+      </c>
+      <c r="H13" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1078248851201","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="33" t="s">
+        <v>607</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D14" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="39" t="n">
+        <f aca="false">配件与耗材!K16</f>
+        <v>309</v>
+      </c>
+      <c r="F14" s="40" t="n">
+        <f aca="false">D14*E14</f>
+        <v>309</v>
+      </c>
+      <c r="G14" s="33" t="s">
+        <v>612</v>
+      </c>
+      <c r="H14" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=763812025816","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D15" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="39" t="n">
+        <f aca="false">配件与耗材!K19</f>
+        <v>84.59</v>
+      </c>
+      <c r="F15" s="40" t="n">
+        <f aca="false">D15*E15</f>
+        <v>84.59</v>
+      </c>
+      <c r="G15" s="33" t="s">
+        <v>631</v>
+      </c>
+      <c r="H15" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=585415365001","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="33" t="s">
+        <v>620</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D16" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="39" t="n">
+        <f aca="false">配件与耗材!K18</f>
+        <v>129.99</v>
+      </c>
+      <c r="F16" s="40" t="n">
+        <f aca="false">D16*E16</f>
+        <v>129.99</v>
+      </c>
+      <c r="G16" s="33" t="s">
+        <v>624</v>
+      </c>
+      <c r="H16" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=768918125679","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="33" t="s">
+        <v>600</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D17" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="39" t="n">
+        <f aca="false">配件与耗材!K15</f>
+        <v>49.5</v>
+      </c>
+      <c r="F17" s="40" t="n">
+        <f aca="false">D17*E17</f>
+        <v>49.5</v>
+      </c>
+      <c r="G17" s="33" t="s">
+        <v>605</v>
+      </c>
+      <c r="H17" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=737603917521","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="33" t="s">
+        <v>595</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D18" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="39" t="n">
+        <f aca="false">配件与耗材!K14</f>
+        <v>3.08</v>
+      </c>
+      <c r="F18" s="40" t="n">
+        <f aca="false">D18*E18</f>
+        <v>3.08</v>
+      </c>
+      <c r="G18" s="33" t="s">
+        <v>599</v>
+      </c>
+      <c r="H18" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=683920556900","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="33" t="s">
+        <v>703</v>
+      </c>
+      <c r="B19" s="33" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D19" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" s="39" t="n">
+        <f aca="false">配件与耗材!K32</f>
+        <v>1.94</v>
+      </c>
+      <c r="F19" s="40" t="n">
+        <f aca="false">D19*E19</f>
+        <v>9.7</v>
+      </c>
+      <c r="G19" s="33" t="s">
+        <v>1072</v>
+      </c>
+      <c r="H19" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=625390659071","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="33" t="s">
+        <v>709</v>
+      </c>
+      <c r="B20" s="33" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D20" s="42" t="n">
+        <v>12</v>
+      </c>
+      <c r="E20" s="39" t="n">
+        <f aca="false">配件与耗材!K33</f>
+        <v>2.91</v>
+      </c>
+      <c r="F20" s="40" t="n">
+        <f aca="false">D20*E20</f>
+        <v>34.92</v>
+      </c>
+      <c r="G20" s="33" t="s">
+        <v>1074</v>
+      </c>
+      <c r="H20" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=733598659967","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="33" t="s">
+        <v>715</v>
+      </c>
+      <c r="B21" s="33" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D21" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="39" t="n">
+        <f aca="false">配件与耗材!K34</f>
+        <v>3.03</v>
+      </c>
+      <c r="F21" s="40" t="n">
+        <f aca="false">D21*E21</f>
+        <v>3.03</v>
+      </c>
+      <c r="G21" s="33" t="s">
+        <v>1077</v>
+      </c>
+      <c r="H21" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="33" t="s">
+        <v>721</v>
+      </c>
+      <c r="B22" s="33" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D22" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="39" t="n">
+        <f aca="false">配件与耗材!K35</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="40" t="n">
+        <f aca="false">D22*E22</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="33" t="s">
+        <v>1079</v>
+      </c>
+      <c r="H22" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="33" t="s">
+        <v>725</v>
+      </c>
+      <c r="B23" s="33" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D23" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="39" t="n">
+        <f aca="false">配件与耗材!K36</f>
+        <v>3.31</v>
+      </c>
+      <c r="F23" s="40" t="n">
+        <f aca="false">D23*E23</f>
+        <v>3.31</v>
+      </c>
+      <c r="G23" s="33" t="s">
+        <v>1077</v>
+      </c>
+      <c r="H23" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="33" t="s">
+        <v>728</v>
+      </c>
+      <c r="B24" s="33" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D24" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="39" t="n">
+        <f aca="false">配件与耗材!K37</f>
+        <v>3.59</v>
+      </c>
+      <c r="F24" s="40" t="n">
+        <f aca="false">D24*E24</f>
+        <v>3.59</v>
+      </c>
+      <c r="G24" s="33" t="s">
+        <v>1077</v>
+      </c>
+      <c r="H24" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="33" t="s">
+        <v>731</v>
+      </c>
+      <c r="B25" s="33" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D25" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="39" t="n">
+        <f aca="false">配件与耗材!K38</f>
+        <v>3.88</v>
+      </c>
+      <c r="F25" s="40" t="n">
+        <f aca="false">D25*E25</f>
+        <v>3.88</v>
+      </c>
+      <c r="G25" s="33" t="s">
+        <v>1077</v>
+      </c>
+      <c r="H25" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="33" t="s">
+        <v>734</v>
+      </c>
+      <c r="B26" s="33" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D26" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="39" t="n">
+        <f aca="false">配件与耗材!K39</f>
+        <v>3.59</v>
+      </c>
+      <c r="F26" s="40" t="n">
+        <f aca="false">D26*E26</f>
+        <v>3.59</v>
+      </c>
+      <c r="G26" s="33" t="s">
+        <v>1077</v>
+      </c>
+      <c r="H26" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="33" t="s">
+        <v>567</v>
+      </c>
+      <c r="B27" s="33" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C27" s="33" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D27" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="39" t="n">
+        <f aca="false">配件与耗材!K9</f>
+        <v>2.2</v>
+      </c>
+      <c r="F27" s="40" t="n">
+        <f aca="false">D27*E27</f>
+        <v>2.2</v>
+      </c>
+      <c r="G27" s="33" t="s">
+        <v>571</v>
+      </c>
+      <c r="H27" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=832569969546","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="33" t="s">
+        <v>572</v>
+      </c>
+      <c r="B28" s="33" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C28" s="33" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D28" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="39" t="n">
+        <f aca="false">配件与耗材!K10</f>
+        <v>2.8</v>
+      </c>
+      <c r="F28" s="40" t="n">
+        <f aca="false">D28*E28</f>
+        <v>2.8</v>
+      </c>
+      <c r="G28" s="33" t="s">
+        <v>576</v>
+      </c>
+      <c r="H28" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=832569969546","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="33" t="s">
+        <v>577</v>
+      </c>
+      <c r="B29" s="33" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D29" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="39" t="n">
+        <f aca="false">配件与耗材!K11</f>
+        <v>3.5</v>
+      </c>
+      <c r="F29" s="40" t="n">
+        <f aca="false">D29*E29</f>
+        <v>3.5</v>
+      </c>
+      <c r="G29" s="33" t="s">
+        <v>581</v>
+      </c>
+      <c r="H29" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=832569969546","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="33" t="s">
+        <v>583</v>
+      </c>
+      <c r="B30" s="33" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D30" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="39" t="n">
+        <f aca="false">配件与耗材!K12</f>
+        <v>4.56</v>
+      </c>
+      <c r="F30" s="40" t="n">
+        <f aca="false">D30*E30</f>
+        <v>4.56</v>
+      </c>
+      <c r="G30" s="33" t="s">
+        <v>587</v>
+      </c>
+      <c r="H30" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=895049863252","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="33" t="s">
+        <v>633</v>
+      </c>
+      <c r="B31" s="33" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C31" s="33" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D31" s="42" t="n">
+        <v>30</v>
+      </c>
+      <c r="E31" s="39" t="n">
+        <f aca="false">配件与耗材!K20</f>
+        <v>0.9</v>
+      </c>
+      <c r="F31" s="40" t="n">
+        <f aca="false">D31*E31</f>
+        <v>27</v>
+      </c>
+      <c r="G31" s="33" t="s">
+        <v>1093</v>
+      </c>
+      <c r="H31" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=825340808235","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="33" t="s">
+        <v>639</v>
+      </c>
+      <c r="B32" s="33" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D32" s="42" t="n">
+        <v>30</v>
+      </c>
+      <c r="E32" s="39" t="n">
+        <f aca="false">配件与耗材!K21</f>
+        <v>0.9</v>
+      </c>
+      <c r="F32" s="40" t="n">
+        <f aca="false">D32*E32</f>
+        <v>27</v>
+      </c>
+      <c r="G32" s="33" t="s">
+        <v>1095</v>
+      </c>
+      <c r="H32" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=825340808235","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="33" t="s">
+        <v>644</v>
+      </c>
+      <c r="B33" s="33" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D33" s="42" t="n">
+        <v>50</v>
+      </c>
+      <c r="E33" s="39" t="n">
+        <f aca="false">配件与耗材!K22</f>
+        <v>0.04</v>
+      </c>
+      <c r="F33" s="40" t="n">
+        <f aca="false">D33*E33</f>
+        <v>2</v>
+      </c>
+      <c r="G33" s="33" t="s">
+        <v>1097</v>
+      </c>
+      <c r="H33" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=891600917698","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="33" t="s">
+        <v>650</v>
+      </c>
+      <c r="B34" s="33" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C34" s="33" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D34" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="39" t="n">
+        <f aca="false">配件与耗材!K23</f>
+        <v>2.68</v>
+      </c>
+      <c r="F34" s="40" t="n">
+        <f aca="false">D34*E34</f>
+        <v>2.68</v>
+      </c>
+      <c r="G34" s="33" t="s">
+        <v>654</v>
+      </c>
+      <c r="H34" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=891600917698","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="33" t="s">
+        <v>655</v>
+      </c>
+      <c r="B35" s="33" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D35" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" s="39" t="n">
+        <f aca="false">配件与耗材!K24</f>
+        <v>0.3</v>
+      </c>
+      <c r="F35" s="40" t="n">
+        <f aca="false">D35*E35</f>
+        <v>3</v>
+      </c>
+      <c r="G35" s="33" t="s">
+        <v>1100</v>
+      </c>
+      <c r="H35" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=598425041338","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="33" t="s">
+        <v>661</v>
+      </c>
+      <c r="B36" s="33" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C36" s="33" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D36" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" s="39" t="n">
+        <f aca="false">配件与耗材!K25</f>
+        <v>0.27</v>
+      </c>
+      <c r="F36" s="40" t="n">
+        <f aca="false">D36*E36</f>
+        <v>2.7</v>
+      </c>
+      <c r="G36" s="33" t="s">
+        <v>1102</v>
+      </c>
+      <c r="H36" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=595594145847","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="33" t="s">
+        <v>666</v>
+      </c>
+      <c r="B37" s="33" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C37" s="33" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D37" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" s="43" t="n">
+        <f aca="false">(订单匹配依据!G93*订单匹配依据!H93+订单匹配依据!G94*订单匹配依据!H94)/(订单匹配依据!G93+订单匹配依据!G94)</f>
+        <v>3.59333333333333</v>
+      </c>
+      <c r="F37" s="40" t="n">
+        <f aca="false">D37*E37</f>
+        <v>10.78</v>
+      </c>
+      <c r="G37" s="33" t="s">
+        <v>1105</v>
+      </c>
+      <c r="H37" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=781764816472","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="33" t="s">
+        <v>672</v>
+      </c>
+      <c r="B38" s="33" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C38" s="33" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D38" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="39" t="n">
+        <f aca="false">配件与耗材!K27</f>
+        <v>3.42</v>
+      </c>
+      <c r="F38" s="40" t="n">
+        <f aca="false">D38*E38</f>
+        <v>3.42</v>
+      </c>
+      <c r="G38" s="33" t="s">
+        <v>677</v>
+      </c>
+      <c r="H38" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=736162720327","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="33" t="s">
+        <v>679</v>
+      </c>
+      <c r="B39" s="33" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C39" s="33" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D39" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" s="39" t="n">
+        <f aca="false">配件与耗材!K28</f>
+        <v>0.01</v>
+      </c>
+      <c r="F39" s="40" t="n">
+        <f aca="false">D39*E39</f>
+        <v>0.1</v>
+      </c>
+      <c r="G39" s="33" t="s">
+        <v>1108</v>
+      </c>
+      <c r="H39" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=701774753211","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="33" t="s">
+        <v>685</v>
+      </c>
+      <c r="B40" s="33" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C40" s="33" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D40" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" s="39" t="n">
+        <f aca="false">配件与耗材!K29</f>
+        <v>0.02</v>
+      </c>
+      <c r="F40" s="40" t="n">
+        <f aca="false">D40*E40</f>
+        <v>0.2</v>
+      </c>
+      <c r="G40" s="33" t="s">
+        <v>1110</v>
+      </c>
+      <c r="H40" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=701774753211","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="33" t="s">
+        <v>690</v>
+      </c>
+      <c r="B41" s="33" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C41" s="33" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D41" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" s="39" t="n">
+        <f aca="false">配件与耗材!K30</f>
+        <v>0.03</v>
+      </c>
+      <c r="F41" s="40" t="n">
+        <f aca="false">D41*E41</f>
+        <v>0.3</v>
+      </c>
+      <c r="G41" s="33" t="s">
+        <v>1112</v>
+      </c>
+      <c r="H41" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=701774753211","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="33" t="s">
+        <v>696</v>
+      </c>
+      <c r="B42" s="33" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C42" s="33" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D42" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="39" t="n">
+        <f aca="false">配件与耗材!K31</f>
+        <v>0.99</v>
+      </c>
+      <c r="F42" s="40" t="n">
+        <f aca="false">D42*E42</f>
+        <v>0.99</v>
+      </c>
+      <c r="G42" s="33" t="s">
+        <v>701</v>
+      </c>
+      <c r="H42" s="41" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=945215173380","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A9:H9"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/hardware/Microduck-HAT-IMU-Shopping-List-20261013.xlsx
+++ b/hardware/Microduck-HAT-IMU-Shopping-List-20261013.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2529" uniqueCount="1114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2469" uniqueCount="1080">
   <si>
     <t xml:space="preserve">Microduck 鸭子用料与制作工具采购清单</t>
   </si>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">鸭子本体用料</t>
   </si>
   <si>
-    <t xml:space="preserve">鸭子本体配套材料。焊接、回流、烧录调试等工具见“制作工具与耗材”工作表。</t>
+    <t xml:space="preserve">鸭子本体配套材料：HAT/IMU接口使用EH，飞特舵机使用AMP2.0。PCB原器件表不动，工具见独立工作表。</t>
   </si>
   <si>
     <t xml:space="preserve">舵机为HD-1910-C001，整机15只；电池按NP-F550的2电＋标准双充套装选购。</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">EH2.5MM 2P胶壳（50个）</t>
   </si>
   <si>
-    <t xml:space="preserve">每只母壳还需2个压接端子；商品称 EH2.5，不混用 XH2.54。</t>
+    <t xml:space="preserve">每只母壳配2个EH压接端子；按EH2.5款式购买，与板上的EH接口配套。</t>
   </si>
   <si>
     <t xml:space="preserve">EH 3P 母壳</t>
@@ -1793,24 +1793,6 @@
     <t xml:space="preserve">用于外部接口转接；每根线的脚序按 HAT J5 与模块核对，不按线色猜。</t>
   </si>
   <si>
-    <t xml:space="preserve">SH1.0 4P 转 XH2.54 线</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SH1.0 4P / 20cm / XH2.54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">与上一条二选一</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ruizhilk旗舰店</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2m;1.0转2.54 4P （2条）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">属于替代转接线方案，不计入板上器件数量。</t>
-  </si>
-  <si>
     <t xml:space="preserve">外接模块</t>
   </si>
   <si>
@@ -2063,57 +2045,6 @@
     <t xml:space="preserve">用于自制接线，按22AWG黑色2米款式购买。</t>
   </si>
   <si>
-    <t xml:space="preserve">XH接插件</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XH2.54 2P 胶壳</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XH2.54 / 2P / 胶壳</t>
-  </si>
-  <si>
-    <t xml:space="preserve">按电池及转接线方案选用</t>
-  </si>
-  <si>
-    <t xml:space="preserve">深圳市腾达升宝电子有限公司</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2P;胶壳</t>
-  </si>
-  <si>
-    <t xml:space="preserve">与XH端子成套使用，按2P胶壳款式购买。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XH2.54 2P 直针座</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XH2.54 / 2P / 直针</t>
-  </si>
-  <si>
-    <t xml:space="preserve">按电池及转接接口方案选用</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2P;直针</t>
-  </si>
-  <si>
-    <t xml:space="preserve">按2P直针款式购买。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XH2.54 压接端子</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XH2.54 / 簧片</t>
-  </si>
-  <si>
-    <t xml:space="preserve">每个接线孔1个端子</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2P;XH簧片</t>
-  </si>
-  <si>
-    <t xml:space="preserve">按“2P;XH簧片”原选项购买，与XH胶壳成套。</t>
-  </si>
-  <si>
     <t xml:space="preserve">线束绝缘</t>
   </si>
   <si>
@@ -2243,7 +2174,7 @@
     <t xml:space="preserve">相关订单匹配依据</t>
   </si>
   <si>
-    <t xml:space="preserve">源：订单数据.xlsx；仅保留本次采购相关的111条商品记录。</t>
+    <t xml:space="preserve">源：订单数据.xlsx；仅保留本次采购相关的107条商品记录。</t>
   </si>
   <si>
     <t xml:space="preserve">数量是订单拍数，不一定等于器件个数。每拍包装数量由商品款式单独解析。</t>
@@ -2339,9 +2270,6 @@
     <t xml:space="preserve">AMP2.0间距2.0 179228 电池端子线 端子连接线 电子线 镍片端子线</t>
   </si>
   <si>
-    <t xml:space="preserve">SH1.0转XH2.54mm间距电子线连接线转接线端子线转换线2P3P4P5P6P</t>
-  </si>
-  <si>
     <t xml:space="preserve">亚润五金专营店</t>
   </si>
   <si>
@@ -2712,18 +2640,6 @@
   </si>
   <si>
     <t xml:space="preserve">制作工具与耗材：安立信937A 数显焊台</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XH2.54MM  直针弯针 连接器 2/3/4/5/6/8/10/11-16P 胶壳插针簧片</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鸭子本体用料：XH2.54 2P 胶壳</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鸭子本体用料：XH2.54 2P 直针座</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鸭子本体用料：XH2.54 压接端子</t>
   </si>
   <si>
     <t xml:space="preserve">制作工具与耗材：恒温加热台</t>
@@ -3202,7 +3118,7 @@
     <t xml:space="preserve">鸭子本体采购列表与合计</t>
   </si>
   <si>
-    <t xml:space="preserve">历史价格预算，包含下表备料；HAT/IMU各按整板计价，原器件列表不动。不计3D打印、制作工具、焊接清洁耗材。</t>
+    <t xml:space="preserve">鸭子本体＋PCB汇总，含参考备料；HAT/IMU各按整板计价，原器件表不动。3D打印、制作工具、焊接清洁耗材不计入。</t>
   </si>
   <si>
     <t xml:space="preserve">PCB有免费券：已列商品合计</t>
@@ -3217,7 +3133,7 @@
     <t xml:space="preserve">首次整包整批采购：PCB无券</t>
   </si>
   <si>
-    <t xml:space="preserve">数量含备料，螺丝按整包；SH转XH备选线不重复计入。M2×5为原订单0元优惠价。TF卡等未提供价格的项目未计入。</t>
+    <t xml:space="preserve">HAT/IMU接口使用EH，舵机线束为AMP2.0。数量含备料，螺丝按整包；M2×5原订单为0元优惠价。TF卡等未提供价格的项目未计入。</t>
   </si>
   <si>
     <t xml:space="preserve">商品 / 模块</t>
@@ -3392,24 +3308,6 @@
   </si>
   <si>
     <t xml:space="preserve">22AWG(0.33平方)黑色 2米；黑色 / 22AWG / 0.33mm² / 2m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2P;胶壳；XH2.54 / 2P / 胶壳</t>
-  </si>
-  <si>
-    <t xml:space="preserve">按订单参考采购数量计入，包含备料；与XH端子成套使用，按2P胶壳款式购买。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2P;直针；XH2.54 / 2P / 直针</t>
-  </si>
-  <si>
-    <t xml:space="preserve">按订单参考采购数量计入，包含备料；按2P直针款式购买。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2P;XH簧片；XH2.54 / 簧片</t>
-  </si>
-  <si>
-    <t xml:space="preserve">按订单参考采购数量计入，包含备料；按“2P;XH簧片”原选项购买，与XH胶壳成套。</t>
   </si>
   <si>
     <t xml:space="preserve">袋装 164片 彩色 【2倍收缩】；164片 / 彩色 / 2倍收缩</t>
@@ -3419,20 +3317,24 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="13">
+  <numFmts count="17">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="_(\$* #,##0_);_(\$* \(#,##0\);_(\$* \-_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="0%"/>
-    <numFmt numFmtId="170" formatCode="0"/>
-    <numFmt numFmtId="171" formatCode="\¥0.00"/>
-    <numFmt numFmtId="172" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="173" formatCode="0.00"/>
-    <numFmt numFmtId="174" formatCode="\¥0.000000"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
+    <numFmt numFmtId="169" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
+    <numFmt numFmtId="170" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
+    <numFmt numFmtId="171" formatCode="_(\$* #,##0_);_(\$* \(#,##0\);_(\$* \-_);_(@_)"/>
+    <numFmt numFmtId="172" formatCode="_(\$* #,##0_);_(\$* \(#,##0\);_(\$* \-_);_(@_)"/>
+    <numFmt numFmtId="173" formatCode="0%"/>
+    <numFmt numFmtId="174" formatCode="0"/>
     <numFmt numFmtId="175" formatCode="\¥0.00"/>
-    <numFmt numFmtId="176" formatCode="\¥0.0000"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="0.00"/>
+    <numFmt numFmtId="178" formatCode="\¥0.000000"/>
+    <numFmt numFmtId="179" formatCode="\¥0.00"/>
+    <numFmt numFmtId="180" formatCode="\¥0.0000"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -3687,7 +3589,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="27">
+  <cellStyleXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3715,6 +3617,10 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3723,187 +3629,192 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="44">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="2" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="174" fontId="7" fillId="2" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="3" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="3" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="174" fontId="7" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="4" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="4" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="2" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="2" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="3" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="3" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="175" fontId="6" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="175" fontId="14" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="10" fillId="4" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="175" fontId="10" fillId="4" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="6" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="17" fillId="6" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="175" fontId="17" fillId="6" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="16" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="175" fontId="16" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="14" fillId="0" borderId="0" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="14" fillId="0" borderId="0" xfId="29" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="30" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="30" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="6" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="0" xfId="30" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="20" fillId="6" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="20" fillId="6" borderId="0" xfId="30" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="4" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="4" borderId="0" xfId="30" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="30" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="22" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="179" fontId="22" fillId="0" borderId="0" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="18" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="179" fontId="18" fillId="0" borderId="0" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="30" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="5" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="5" borderId="0" xfId="30" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="180" fontId="22" fillId="0" borderId="0" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="13">
+  <cellStyles count="19">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
@@ -3911,12 +3822,18 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
     <cellStyle name="Comma" xfId="20"/>
-    <cellStyle name="Comma [0]" xfId="21"/>
-    <cellStyle name="Currency" xfId="22"/>
-    <cellStyle name="Currency [0]" xfId="23"/>
-    <cellStyle name="Normal" xfId="24"/>
-    <cellStyle name="Normal 1" xfId="25"/>
-    <cellStyle name="Percent" xfId="26"/>
+    <cellStyle name="Comma 1" xfId="21"/>
+    <cellStyle name="Comma [0]" xfId="22"/>
+    <cellStyle name="Comma [0] 2" xfId="23"/>
+    <cellStyle name="Currency" xfId="24"/>
+    <cellStyle name="Currency 3" xfId="25"/>
+    <cellStyle name="Currency [0]" xfId="26"/>
+    <cellStyle name="Currency [0] 4" xfId="27"/>
+    <cellStyle name="Normal" xfId="28"/>
+    <cellStyle name="Normal 1" xfId="29"/>
+    <cellStyle name="Normal 5" xfId="30"/>
+    <cellStyle name="Percent" xfId="31"/>
+    <cellStyle name="Percent 6" xfId="32"/>
   </cellStyles>
   <dxfs count="16">
     <dxf>
@@ -4182,8 +4099,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DuckAccessories" displayName="DuckAccessories" ref="A6:K39" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A6:K39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DuckAccessories" displayName="DuckAccessories" ref="A6:K35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A6:K35"/>
   <tableColumns count="11">
     <tableColumn id="1" name="类别"/>
     <tableColumn id="2" name="商品 / 用品"/>
@@ -4202,8 +4119,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="DuckTotalItems" displayName="DuckTotalItems" ref="A10:H42" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A10:H42"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="DuckTotalItems" displayName="DuckTotalItems" ref="A10:H39" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A10:H39"/>
   <tableColumns count="8">
     <tableColumn id="1" name="商品 / 模块"/>
     <tableColumn id="2" name="型号 / 指定款式"/>
@@ -4259,8 +4176,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="OrderEvidence" displayName="OrderEvidence" ref="A6:J117" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A6:J117"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="OrderEvidence" displayName="OrderEvidence" ref="A6:J113" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A6:J113"/>
   <tableColumns count="10">
     <tableColumn id="1" name="订单源行"/>
     <tableColumn id="2" name="提交日期"/>
@@ -11459,8 +11376,8 @@
         <v>559</v>
       </c>
       <c r="F7" s="17" t="str">
-        <f aca="false">HYPERLINK("https://www.jlc.com/","定制打样入口")</f>
-        <v>定制打样入口</v>
+        <f aca="false">HYPERLINK("https://www.jlc.com/","PCB打样入口")</f>
+        <v>PCB打样入口</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>560</v>
@@ -11491,8 +11408,8 @@
         <v>559</v>
       </c>
       <c r="F8" s="17" t="str">
-        <f aca="false">HYPERLINK("https://www.jlc.com/","定制打样入口")</f>
-        <v>定制打样入口</v>
+        <f aca="false">HYPERLINK("https://www.jlc.com/","PCB打样入口")</f>
+        <v>PCB打样入口</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>560</v>
@@ -11652,58 +11569,58 @@
     </row>
     <row r="13" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>591</v>
+        <v>226</v>
       </c>
       <c r="F13" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1021140262048","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=683920556900","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>592</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>593</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>38</v>
+        <v>103</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
+        <v>588</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>594</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="C14" s="8" t="s">
         <v>595</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="D14" s="8" t="s">
         <v>596</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="E14" s="8" t="s">
         <v>597</v>
       </c>
-      <c r="E14" s="8" t="s">
-        <v>226</v>
-      </c>
       <c r="F14" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=683920556900","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=737603917521","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G14" s="8" t="s">
@@ -11716,70 +11633,70 @@
         <v>599</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>3.08</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F15" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=737603917521","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=763812025816","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H15" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>49.5</v>
+        <v>309</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D16" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="F16" s="17" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1078248851201","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+      <c r="G16" s="8" t="s">
         <v>609</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>610</v>
-      </c>
-      <c r="F16" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=763812025816","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>611</v>
       </c>
       <c r="H16" s="1" t="n">
         <v>1</v>
@@ -11788,10 +11705,10 @@
         <v>612</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>309</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11808,14 +11725,14 @@
         <v>616</v>
       </c>
       <c r="E17" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="F17" s="17" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=768918125679","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+      <c r="G17" s="8" t="s">
         <v>617</v>
-      </c>
-      <c r="F17" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1078248851201","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>615</v>
       </c>
       <c r="H17" s="1" t="n">
         <v>1</v>
@@ -11824,10 +11741,10 @@
         <v>618</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>104</v>
+        <v>180</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>99</v>
+        <v>129.99</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11844,67 +11761,67 @@
         <v>622</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>610</v>
+        <v>623</v>
       </c>
       <c r="F18" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=768918125679","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=585415365001","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>180</v>
+        <v>22</v>
       </c>
       <c r="K18" s="18" t="n">
-        <v>129.99</v>
+        <v>84.59</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F19" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=585415365001","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=825340808235","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H19" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="K19" s="18" t="n">
-        <v>84.59</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>633</v>
@@ -11913,26 +11830,26 @@
         <v>634</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="F20" s="17" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=825340808235","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="H20" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="K20" s="18" t="n">
         <v>0.9</v>
@@ -11940,43 +11857,43 @@
     </row>
     <row r="21" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="B21" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>639</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="D21" s="8" t="s">
         <v>640</v>
       </c>
-      <c r="D21" s="8" t="s">
-        <v>635</v>
-      </c>
       <c r="E21" s="8" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="F21" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=825340808235","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=891600917698","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H21" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K21" s="18" t="n">
-        <v>0.9</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>644</v>
@@ -11988,67 +11905,67 @@
         <v>646</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="F22" s="17" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=891600917698","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G22" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="I22" s="8" t="s">
         <v>648</v>
       </c>
-      <c r="H22" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>649</v>
-      </c>
       <c r="J22" s="8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K22" s="18" t="n">
-        <v>0.04</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="B23" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="D23" s="8" t="s">
         <v>651</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="E23" s="8" t="s">
         <v>652</v>
       </c>
-      <c r="E23" s="8" t="s">
-        <v>647</v>
-      </c>
       <c r="F23" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=891600917698","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=598425041338","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>653</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>654</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="K23" s="18" t="n">
-        <v>2.68</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>655</v>
@@ -12057,70 +11974,70 @@
         <v>656</v>
       </c>
       <c r="D24" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="F24" s="17" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=595594145847","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+      <c r="G24" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="H24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="8" t="s">
         <v>658</v>
       </c>
-      <c r="F24" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=598425041338","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="H24" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>660</v>
-      </c>
       <c r="J24" s="8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>643</v>
+        <v>659</v>
       </c>
       <c r="B25" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>661</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="D25" s="8" t="s">
         <v>662</v>
       </c>
-      <c r="D25" s="8" t="s">
-        <v>657</v>
-      </c>
       <c r="E25" s="8" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="F25" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=595594145847","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=781764816472","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H25" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>0.27</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>666</v>
@@ -12135,7 +12052,7 @@
         <v>669</v>
       </c>
       <c r="F26" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=781764816472","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=736162720327","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G26" s="8" t="s">
@@ -12148,480 +12065,340 @@
         <v>671</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>3.63</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="F27" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=736162720327","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=945215173380","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H27" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>3.42</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F28" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=701774753211","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=625390659071","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H28" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>199</v>
+        <v>111</v>
       </c>
       <c r="K28" s="18" t="n">
-        <v>0.01</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F29" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=701774753211","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=733598659967","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H29" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>201</v>
+        <v>112</v>
       </c>
       <c r="K29" s="18" t="n">
-        <v>0.02</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>678</v>
+        <v>691</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>682</v>
+        <v>695</v>
       </c>
       <c r="F30" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=701774753211","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>202</v>
+        <v>88</v>
       </c>
       <c r="K30" s="18" t="n">
-        <v>0.03</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
+        <v>691</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>698</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>699</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>694</v>
+      </c>
+      <c r="E31" s="8" t="s">
         <v>695</v>
       </c>
-      <c r="B31" s="8" t="s">
-        <v>696</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>697</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>698</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>699</v>
-      </c>
       <c r="F31" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=945215173380","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>700</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>701</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="K31" s="18" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
+        <v>691</v>
+      </c>
+      <c r="B32" s="8" t="s">
         <v>702</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="C32" s="8" t="s">
         <v>703</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="D32" s="8" t="s">
+        <v>694</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>695</v>
+      </c>
+      <c r="F32" s="17" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+      <c r="G32" s="8" t="s">
         <v>704</v>
       </c>
-      <c r="D32" s="8" t="s">
-        <v>705</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>706</v>
-      </c>
-      <c r="F32" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=625390659071","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>707</v>
-      </c>
       <c r="H32" s="1" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="K32" s="18" t="n">
-        <v>1.94</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>702</v>
+        <v>691</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>711</v>
+        <v>694</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>706</v>
+        <v>695</v>
       </c>
       <c r="F33" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=733598659967","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>713</v>
+        <v>697</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="K33" s="18" t="n">
-        <v>2.91</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>714</v>
+        <v>691</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>717</v>
+        <v>694</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>718</v>
+        <v>695</v>
       </c>
       <c r="F34" s="17" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
       <c r="H34" s="1" t="n">
         <v>200</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>720</v>
+        <v>697</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K34" s="18" t="n">
-        <v>3.03</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>714</v>
+        <v>691</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>722</v>
+        <v>712</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>717</v>
+        <v>694</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>718</v>
+        <v>695</v>
       </c>
       <c r="F35" s="17" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>723</v>
+        <v>713</v>
       </c>
       <c r="H35" s="1" t="n">
         <v>200</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>724</v>
+        <v>697</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="K35" s="18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="8" t="s">
-        <v>714</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>725</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>726</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>717</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>718</v>
-      </c>
-      <c r="F36" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="H36" s="1" t="n">
-        <v>200</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>720</v>
-      </c>
-      <c r="J36" s="8" t="n">
-        <v>87</v>
-      </c>
-      <c r="K36" s="18" t="n">
-        <v>3.31</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="8" t="s">
-        <v>714</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>728</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>729</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>717</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>718</v>
-      </c>
-      <c r="F37" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>730</v>
-      </c>
-      <c r="H37" s="1" t="n">
-        <v>200</v>
-      </c>
-      <c r="I37" s="8" t="s">
-        <v>720</v>
-      </c>
-      <c r="J37" s="8" t="n">
-        <v>86</v>
-      </c>
-      <c r="K37" s="18" t="n">
         <v>3.59</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="8" t="s">
-        <v>714</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>731</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>732</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>717</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>718</v>
-      </c>
-      <c r="F38" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>733</v>
-      </c>
-      <c r="H38" s="1" t="n">
-        <v>200</v>
-      </c>
-      <c r="I38" s="8" t="s">
-        <v>720</v>
-      </c>
-      <c r="J38" s="8" t="n">
-        <v>85</v>
-      </c>
-      <c r="K38" s="18" t="n">
-        <v>3.88</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="8" t="s">
-        <v>714</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>734</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>735</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>717</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>718</v>
-      </c>
-      <c r="F39" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="H39" s="1" t="n">
-        <v>200</v>
-      </c>
-      <c r="I39" s="8" t="s">
-        <v>720</v>
-      </c>
-      <c r="J39" s="8" t="n">
-        <v>89</v>
-      </c>
-      <c r="K39" s="18" t="n">
-        <v>3.59</v>
-      </c>
-    </row>
+    <row r="36" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="40" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="41" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="42" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -12645,7 +12422,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -12673,7 +12450,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>737</v>
+        <v>714</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -12687,7 +12464,7 @@
     </row>
     <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>738</v>
+        <v>715</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -12701,7 +12478,7 @@
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>739</v>
+        <v>716</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -12715,7 +12492,7 @@
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>740</v>
+        <v>717</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -12732,31 +12509,31 @@
         <v>553</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>741</v>
+        <v>718</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>742</v>
+        <v>719</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>743</v>
+        <v>720</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>744</v>
+        <v>721</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>745</v>
+        <v>722</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>746</v>
+        <v>723</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>747</v>
+        <v>724</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>550</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>748</v>
+        <v>725</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12767,13 +12544,13 @@
         <v>46306</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>749</v>
+        <v>726</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>262</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>750</v>
+        <v>727</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>260</v>
@@ -12789,7 +12566,7 @@
         <v>打开商品</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>751</v>
+        <v>728</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12800,16 +12577,16 @@
         <v>46305</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>749</v>
+        <v>726</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>752</v>
+        <v>729</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>30</v>
@@ -12822,7 +12599,7 @@
         <v>打开商品</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>753</v>
+        <v>730</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12833,16 +12610,16 @@
         <v>46297</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>749</v>
+        <v>726</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>754</v>
+        <v>731</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>10</v>
@@ -12855,7 +12632,7 @@
         <v>打开商品</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>753</v>
+        <v>730</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12866,16 +12643,16 @@
         <v>46297</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>749</v>
+        <v>726</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>755</v>
+        <v>732</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>756</v>
+        <v>733</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>10</v>
@@ -12888,7 +12665,7 @@
         <v>打开商品</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>753</v>
+        <v>730</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12899,16 +12676,16 @@
         <v>46293</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>237</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>758</v>
+        <v>735</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>759</v>
+        <v>736</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>1</v>
@@ -12921,7 +12698,7 @@
         <v>打开商品</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>751</v>
+        <v>728</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12932,16 +12709,16 @@
         <v>46293</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>760</v>
+        <v>737</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>761</v>
+        <v>738</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>762</v>
+        <v>739</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>1</v>
@@ -12954,7 +12731,7 @@
         <v>打开商品</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>763</v>
+        <v>740</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12965,16 +12742,16 @@
         <v>46291</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D13" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="F13" s="8" t="s">
         <v>647</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>764</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>653</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>1</v>
@@ -12987,7 +12764,7 @@
         <v>打开商品</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>753</v>
+        <v>730</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12998,16 +12775,16 @@
         <v>46291</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>764</v>
+        <v>741</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>50</v>
@@ -13020,7 +12797,7 @@
         <v>打开商品</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>753</v>
+        <v>730</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13031,16 +12808,16 @@
         <v>46290</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>765</v>
+        <v>742</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>766</v>
+        <v>743</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>767</v>
+        <v>744</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>1</v>
@@ -13053,7 +12830,7 @@
         <v>打开商品</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>768</v>
+        <v>745</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13064,16 +12841,16 @@
         <v>46290</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>769</v>
+        <v>746</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="G16" s="9" t="n">
         <v>30</v>
@@ -13086,1347 +12863,1347 @@
         <v>打开商品</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>753</v>
+        <v>730</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B17" s="19" t="n">
-        <v>46287</v>
+        <v>46282</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>591</v>
+        <v>747</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>770</v>
+        <v>748</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>592</v>
+        <v>749</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="20" t="n">
-        <v>3.4</v>
+        <v>268</v>
       </c>
       <c r="I17" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1021140262048","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=566089419587","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>588</v>
+        <v>750</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B18" s="19" t="n">
         <v>46282</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>771</v>
+        <v>27</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>773</v>
+        <v>33</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H18" s="20" t="n">
-        <v>268</v>
+        <v>0.06</v>
       </c>
       <c r="I18" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=566089419587","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=630712731066","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>774</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B19" s="19" t="n">
         <v>46282</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>27</v>
+        <v>141</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>775</v>
+        <v>752</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>33</v>
+        <v>163</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H19" s="20" t="n">
-        <v>0.06</v>
+        <v>1.46</v>
       </c>
       <c r="I19" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=630712731066","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>30</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20" s="19" t="n">
         <v>46282</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>141</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>776</v>
+        <v>752</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="G20" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="20" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="I20" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>160</v>
+        <v>728</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B21" s="19" t="n">
         <v>46282</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>141</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>776</v>
+        <v>752</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>142</v>
+        <v>243</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="20" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="I21" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>751</v>
+        <v>240</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="B22" s="19" t="n">
-        <v>46282</v>
+        <v>46279</v>
       </c>
       <c r="C22" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>737</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>753</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>754</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="20" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="I22" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=972313702890","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="B23" s="19" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>756</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>586</v>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="20" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="I23" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=895049863252","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="B24" s="19" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>751</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H24" s="20" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I24" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=630712731066","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>757</v>
       </c>
-      <c r="D22" s="8" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B25" s="19" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I25" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=731471380840","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="E22" s="8" t="s">
-        <v>776</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="G22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="I22" s="10" t="str">
+      <c r="E26" s="8" t="s">
+        <v>752</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="G26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I26" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
         <v>打开商品</v>
       </c>
-      <c r="J22" s="8" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
-        <v>76</v>
-      </c>
-      <c r="B23" s="19" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>760</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>777</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>778</v>
-      </c>
-      <c r="G23" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="20" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="I23" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=972313702890","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
-        <v>77</v>
-      </c>
-      <c r="B24" s="19" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>780</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>586</v>
-      </c>
-      <c r="G24" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="20" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="I24" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=895049863252","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
-        <v>78</v>
-      </c>
-      <c r="B25" s="19" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>775</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G25" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="H25" s="20" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I25" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=630712731066","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="n">
-        <v>79</v>
-      </c>
-      <c r="B26" s="19" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>782</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G26" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="20" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="I26" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=731471380840","打开商品")</f>
-        <v>打开商品</v>
-      </c>
       <c r="J26" s="8" t="s">
-        <v>783</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B27" s="19" t="n">
         <v>46279</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>141</v>
+        <v>91</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>776</v>
+        <v>760</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>142</v>
+        <v>575</v>
       </c>
       <c r="G27" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="20" t="n">
-        <v>1.42</v>
+        <v>2.8</v>
       </c>
       <c r="I27" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=832569969546","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>137</v>
+        <v>572</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B28" s="19" t="n">
         <v>46279</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>784</v>
+        <v>760</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="G28" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="20" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="I28" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=832569969546","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B29" s="19" t="n">
         <v>46279</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>784</v>
+        <v>760</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="20" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="I29" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=832569969546","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>567</v>
+        <v>577</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B30" s="19" t="n">
-        <v>46279</v>
+        <v>46276</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D30" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" s="20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="I30" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=640391703111","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B31" s="19" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>597</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>761</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>598</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="20" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="I31" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=737603917521","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="B32" s="19" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>762</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="G32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=909264246006","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="B33" s="19" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I33" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=793455311175","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="B34" s="19" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>764</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>765</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>766</v>
+      </c>
+      <c r="G34" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H34" s="20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I34" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=582129955778","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B35" s="19" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>768</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I35" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=993202872551","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B36" s="19" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>769</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>605</v>
+      </c>
+      <c r="G36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="20" t="n">
+        <v>309</v>
+      </c>
+      <c r="I36" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=763812025816","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="B37" s="19" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>770</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>592</v>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="20" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="I37" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=683920556900","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B38" s="19" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>771</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>772</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>773</v>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I38" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=979077591318","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="B39" s="19" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>775</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>776</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="G39" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="20" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="I39" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=19606507546","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="B40" s="19" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>780</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>781</v>
+      </c>
+      <c r="G40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I40" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=851008959999","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B41" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D41" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="E30" s="8" t="s">
-        <v>784</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>580</v>
-      </c>
-      <c r="G30" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I30" s="10" t="str">
+      <c r="E41" s="8" t="s">
+        <v>760</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I41" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=832569969546","打开商品")</f>
         <v>打开商品</v>
       </c>
-      <c r="J30" s="8" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="n">
-        <v>91</v>
-      </c>
-      <c r="B31" s="19" t="n">
-        <v>46276</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>750</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="G31" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H31" s="20" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="I31" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=640391703111","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="B32" s="19" t="n">
-        <v>46276</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>603</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>785</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>604</v>
-      </c>
-      <c r="G32" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="20" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="I32" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=737603917521","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="n">
-        <v>93</v>
-      </c>
-      <c r="B33" s="19" t="n">
-        <v>46276</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>786</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="G33" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="I33" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=909264246006","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="B34" s="19" t="n">
-        <v>46276</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>787</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="G34" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I34" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=793455311175","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="B35" s="19" t="n">
-        <v>46276</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>788</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>789</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>790</v>
-      </c>
-      <c r="G35" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H35" s="20" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I35" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=582129955778","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="n">
-        <v>96</v>
-      </c>
-      <c r="B36" s="19" t="n">
-        <v>46276</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>792</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G36" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I36" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=993202872551","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="B37" s="19" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>610</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>793</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>611</v>
-      </c>
-      <c r="G37" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" s="20" t="n">
-        <v>309</v>
-      </c>
-      <c r="I37" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=763812025816","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J37" s="8" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="n">
-        <v>103</v>
-      </c>
-      <c r="B38" s="19" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>794</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>598</v>
-      </c>
-      <c r="G38" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="20" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="I38" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=683920556900","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J38" s="8" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="n">
-        <v>105</v>
-      </c>
-      <c r="B39" s="19" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>795</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>796</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>797</v>
-      </c>
-      <c r="G39" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="20" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="I39" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=979077591318","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J39" s="8" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="n">
+      <c r="J41" s="8" t="s">
         <v>106</v>
-      </c>
-      <c r="B40" s="19" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>799</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>800</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>801</v>
-      </c>
-      <c r="G40" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="20" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I40" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=19606507546","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J40" s="8" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="n">
-        <v>107</v>
-      </c>
-      <c r="B41" s="19" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>803</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>804</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="G41" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="I41" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=851008959999","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J41" s="8" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B42" s="19" t="n">
         <v>46272</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>784</v>
+        <v>760</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="G42" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="20" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="I42" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=832569969546","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B43" s="19" t="n">
         <v>46272</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>91</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="G43" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="20" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="I43" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=832569969546","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=762173333947","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>88</v>
+        <v>176</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B44" s="19" t="n">
         <v>46272</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>807</v>
+        <v>784</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="20" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="I44" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=762173333947","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=944306254140","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>176</v>
+        <v>125</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B45" s="19" t="n">
         <v>46272</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>72</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>808</v>
+        <v>785</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>128</v>
+        <v>73</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="20" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="I45" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=944306254140","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=943185002457","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>125</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B46" s="19" t="n">
         <v>46272</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>809</v>
+        <v>786</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="G46" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="20" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="I46" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=943185002457","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=610558214623","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B47" s="19" t="n">
         <v>46272</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>810</v>
+        <v>787</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H47" s="20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I47" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=610558214623","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=931081429973","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B48" s="19" t="n">
         <v>46272</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D48" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>811</v>
+        <v>787</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="20" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="I48" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=931081429973","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B49" s="19" t="n">
         <v>46272</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>811</v>
+        <v>788</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="20" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="I49" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=931081429973","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=598174251748","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B50" s="19" t="n">
         <v>46272</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>812</v>
+        <v>789</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>116</v>
+        <v>190</v>
       </c>
       <c r="G50" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="20" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="I50" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=598174251748","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=902117985110","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>112</v>
+        <v>187</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B51" s="19" t="n">
         <v>46272</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>184</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>813</v>
+        <v>789</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="G51" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="20" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="I51" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=902117985110","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B52" s="19" t="n">
         <v>46272</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>184</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>813</v>
+        <v>789</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="G52" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="20" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="I52" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=902117985110","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J52" s="8" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B53" s="19" t="n">
         <v>46272</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>813</v>
+        <v>790</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H53" s="20" t="n">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="I53" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=902117985110","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=944053669860","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J53" s="8" t="s">
-        <v>181</v>
+        <v>208</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B54" s="19" t="n">
         <v>46272</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>211</v>
+        <v>168</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>814</v>
+        <v>791</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>212</v>
+        <v>165</v>
       </c>
       <c r="G54" s="9" t="n">
         <v>5</v>
       </c>
       <c r="H54" s="20" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="I54" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=944053669860","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=808484505787","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J54" s="8" t="s">
-        <v>208</v>
+        <v>165</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B55" s="19" t="n">
         <v>46272</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>168</v>
+        <v>792</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>815</v>
+        <v>793</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>165</v>
+        <v>794</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H55" s="20" t="n">
-        <v>1.18</v>
+        <v>3</v>
       </c>
       <c r="I55" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=808484505787","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=857961351344","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J55" s="8" t="s">
-        <v>165</v>
+        <v>728</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B56" s="19" t="n">
         <v>46272</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>816</v>
+        <v>141</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>817</v>
+        <v>752</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>818</v>
+        <v>153</v>
       </c>
       <c r="G56" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H56" s="20" t="n">
-        <v>3</v>
+        <v>1.46</v>
       </c>
       <c r="I56" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=857961351344","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J56" s="8" t="s">
-        <v>751</v>
+        <v>150</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B57" s="19" t="n">
         <v>46272</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D57" s="8" t="s">
         <v>141</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>776</v>
+        <v>752</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G57" s="9" t="n">
         <v>1</v>
@@ -14439,27 +14216,27 @@
         <v>打开商品</v>
       </c>
       <c r="J57" s="8" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B58" s="19" t="n">
         <v>46272</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>141</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>776</v>
+        <v>752</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>158</v>
+        <v>795</v>
       </c>
       <c r="G58" s="9" t="n">
         <v>1</v>
@@ -14472,654 +14249,654 @@
         <v>打开商品</v>
       </c>
       <c r="J58" s="8" t="s">
-        <v>155</v>
+        <v>796</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B59" s="19" t="n">
         <v>46272</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D59" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>797</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="G59" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H59" s="20" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I59" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1013388982214","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J59" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="n">
+        <v>139</v>
+      </c>
+      <c r="B60" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G60" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" s="20" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I60" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=920058690376","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J60" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B61" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>799</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="G61" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" s="20" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="I61" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=533725557959","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J61" s="8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="n">
         <v>141</v>
       </c>
-      <c r="E59" s="8" t="s">
-        <v>776</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>819</v>
-      </c>
-      <c r="G59" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H59" s="20" t="n">
+      <c r="B62" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>800</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="G62" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" s="20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I62" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=996702312391","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J62" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="B63" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>801</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G63" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I63" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1005108810412","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J63" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="B64" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>802</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>733</v>
+      </c>
+      <c r="G64" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H64" s="20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I64" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=908248360601","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J64" s="8" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B65" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>803</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>733</v>
+      </c>
+      <c r="G65" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H65" s="20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I65" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=708737648760","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J65" s="8" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="B66" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="G66" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" s="20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I66" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=640391703111","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J66" s="8" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B67" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="G67" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" s="20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I67" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1062189210190","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J67" s="8" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="B68" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="G68" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" s="20" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="I68" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1028742717053","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J68" s="8" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B69" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="G69" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H69" s="20" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="I69" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=726808419708","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J69" s="8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="1" t="n">
+        <v>151</v>
+      </c>
+      <c r="B70" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="G70" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I70" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=602152415662","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J70" s="8" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B71" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>811</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="G71" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" s="20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="I71" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=606816197525","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J71" s="8" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="n">
+        <v>153</v>
+      </c>
+      <c r="B72" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>812</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="G72" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H72" s="20" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I72" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=977236759812","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J72" s="8" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="n">
+        <v>154</v>
+      </c>
+      <c r="B73" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>814</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>815</v>
+      </c>
+      <c r="G73" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="20" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="I73" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=581798084270","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J73" s="8" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="n">
+        <v>155</v>
+      </c>
+      <c r="B74" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>752</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="G74" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="20" t="n">
         <v>1.46</v>
       </c>
-      <c r="I59" s="10" t="str">
+      <c r="I74" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
         <v>打开商品</v>
       </c>
-      <c r="J59" s="8" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="n">
-        <v>137</v>
-      </c>
-      <c r="B60" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D60" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>821</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="G60" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H60" s="20" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="I60" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1013388982214","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J60" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="n">
-        <v>139</v>
-      </c>
-      <c r="B61" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D61" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>822</v>
-      </c>
-      <c r="F61" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="G61" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H61" s="20" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="I61" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=920058690376","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J61" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="n">
-        <v>140</v>
-      </c>
-      <c r="B62" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>823</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="G62" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H62" s="20" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="I62" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=533725557959","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J62" s="8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="n">
-        <v>141</v>
-      </c>
-      <c r="B63" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>824</v>
-      </c>
-      <c r="F63" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="G63" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H63" s="20" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="I63" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=996702312391","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J63" s="8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="n">
-        <v>142</v>
-      </c>
-      <c r="B64" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D64" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>825</v>
-      </c>
-      <c r="F64" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G64" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H64" s="20" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="I64" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1005108810412","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J64" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="n">
-        <v>143</v>
-      </c>
-      <c r="B65" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>826</v>
-      </c>
-      <c r="F65" s="8" t="s">
-        <v>756</v>
-      </c>
-      <c r="G65" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H65" s="20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="I65" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=908248360601","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J65" s="8" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="n">
+      <c r="J74" s="8" t="s">
         <v>144</v>
-      </c>
-      <c r="B66" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D66" s="8" t="s">
-        <v>827</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>828</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>756</v>
-      </c>
-      <c r="G66" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H66" s="20" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="I66" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=708737648760","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J66" s="8" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="n">
-        <v>147</v>
-      </c>
-      <c r="B67" s="19" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>750</v>
-      </c>
-      <c r="F67" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="G67" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H67" s="20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I67" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=640391703111","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J67" s="8" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="n">
-        <v>148</v>
-      </c>
-      <c r="B68" s="19" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>829</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="G68" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H68" s="20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I68" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1062189210190","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J68" s="8" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="n">
-        <v>149</v>
-      </c>
-      <c r="B69" s="19" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D69" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>830</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="G69" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H69" s="20" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="I69" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1028742717053","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J69" s="8" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="n">
-        <v>150</v>
-      </c>
-      <c r="B70" s="19" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D70" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>831</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="G70" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H70" s="20" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="I70" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=726808419708","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J70" s="8" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="n">
-        <v>151</v>
-      </c>
-      <c r="B71" s="19" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D71" s="8" t="s">
-        <v>832</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>833</v>
-      </c>
-      <c r="F71" s="8" t="s">
-        <v>834</v>
-      </c>
-      <c r="G71" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H71" s="20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="I71" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=602152415662","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J71" s="8" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="n">
-        <v>152</v>
-      </c>
-      <c r="B72" s="19" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D72" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>835</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="G72" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H72" s="20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="I72" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=606816197525","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J72" s="8" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="n">
-        <v>153</v>
-      </c>
-      <c r="B73" s="19" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D73" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>836</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="G73" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="H73" s="20" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I73" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=977236759812","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J73" s="8" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="n">
-        <v>154</v>
-      </c>
-      <c r="B74" s="19" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>837</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>838</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>839</v>
-      </c>
-      <c r="G74" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H74" s="20" t="n">
-        <v>9.84</v>
-      </c>
-      <c r="I74" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=581798084270","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J74" s="8" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B75" s="19" t="n">
         <v>46269</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D75" s="8" t="s">
         <v>141</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>776</v>
+        <v>752</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="G75" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H75" s="20" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="I75" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J75" s="8" t="s">
-        <v>144</v>
+        <v>728</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B76" s="19" t="n">
         <v>46269</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D76" s="8" t="s">
         <v>141</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>776</v>
+        <v>752</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>142</v>
+        <v>248</v>
       </c>
       <c r="G76" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H76" s="20" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="I76" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J76" s="8" t="s">
-        <v>751</v>
+        <v>245</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B77" s="19" t="n">
         <v>46269</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>141</v>
+        <v>231</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>776</v>
+        <v>817</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H77" s="20" t="n">
-        <v>1.46</v>
+        <v>1.8</v>
       </c>
       <c r="I77" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1025817117811","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J77" s="8" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B78" s="19" t="n">
         <v>46269</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>231</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>841</v>
+        <v>817</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>232</v>
+        <v>818</v>
       </c>
       <c r="G78" s="9" t="n">
         <v>1</v>
@@ -15132,519 +14909,519 @@
         <v>打开商品</v>
       </c>
       <c r="J78" s="8" t="s">
-        <v>228</v>
+        <v>728</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B79" s="19" t="n">
         <v>46269</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>841</v>
+        <v>819</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>842</v>
+        <v>733</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H79" s="20" t="n">
-        <v>1.8</v>
+        <v>0.06</v>
       </c>
       <c r="I79" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1025817117811","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=891785167202","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J79" s="8" t="s">
-        <v>751</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B80" s="19" t="n">
         <v>46269</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>226</v>
+        <v>271</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>843</v>
+        <v>820</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>756</v>
+        <v>733</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H80" s="20" t="n">
-        <v>0.06</v>
+        <v>0.43</v>
       </c>
       <c r="I80" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=891785167202","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=705642638300","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J80" s="8" t="s">
-        <v>224</v>
+        <v>268</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B81" s="19" t="n">
         <v>46269</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>844</v>
+        <v>821</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>756</v>
+        <v>264</v>
       </c>
       <c r="G81" s="9" t="n">
         <v>10</v>
       </c>
       <c r="H81" s="20" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="I81" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=705642638300","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=747094785928","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J81" s="8" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="n">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="B82" s="19" t="n">
-        <v>46269</v>
+        <v>46266</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>266</v>
+        <v>226</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>845</v>
+        <v>806</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>264</v>
+        <v>733</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H82" s="20" t="n">
-        <v>0.47</v>
+        <v>21.17</v>
       </c>
       <c r="I82" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=747094785928","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1027587805193","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J82" s="8" t="s">
-        <v>264</v>
+        <v>728</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="n">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="B83" s="19" t="n">
-        <v>46266</v>
+        <v>46258</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>226</v>
+        <v>27</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>830</v>
+        <v>751</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>756</v>
+        <v>28</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H83" s="20" t="n">
-        <v>21.17</v>
+        <v>0.03</v>
       </c>
       <c r="I83" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1027587805193","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=630712731066","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J83" s="8" t="s">
-        <v>751</v>
+        <v>728</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="n">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B84" s="19" t="n">
         <v>46258</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>27</v>
+        <v>168</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>28</v>
+        <v>197</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="H84" s="20" t="n">
-        <v>0.03</v>
+        <v>1.28</v>
       </c>
       <c r="I84" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=630712731066","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=969642590399","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J84" s="8" t="s">
-        <v>751</v>
+        <v>197</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B85" s="19" t="n">
         <v>46258</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>168</v>
+        <v>27</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>846</v>
+        <v>758</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>197</v>
+        <v>43</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H85" s="20" t="n">
-        <v>1.28</v>
+        <v>1.98</v>
       </c>
       <c r="I85" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=969642590399","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=731471380840","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J85" s="8" t="s">
-        <v>197</v>
+        <v>728</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B86" s="19" t="n">
         <v>46258</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D86" s="8" t="s">
         <v>27</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>782</v>
+        <v>823</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H86" s="20" t="n">
-        <v>1.98</v>
+        <v>0.12</v>
       </c>
       <c r="I86" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=731471380840","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=730407108775","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J86" s="8" t="s">
-        <v>751</v>
+        <v>45</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B87" s="19" t="n">
-        <v>46258</v>
+        <v>46256</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>757</v>
+        <v>824</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>27</v>
+        <v>825</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>847</v>
+        <v>826</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>48</v>
+        <v>827</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H87" s="20" t="n">
-        <v>0.12</v>
+        <v>169</v>
       </c>
       <c r="I87" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=730407108775","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=956985590887","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J87" s="8" t="s">
-        <v>45</v>
+        <v>828</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B88" s="19" t="n">
-        <v>46256</v>
+        <v>46254</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>848</v>
+        <v>734</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>849</v>
+        <v>141</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>850</v>
+        <v>752</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>851</v>
+        <v>253</v>
       </c>
       <c r="G88" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H88" s="20" t="n">
-        <v>169</v>
+        <v>1.44</v>
       </c>
       <c r="I88" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=956985590887","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J88" s="8" t="s">
-        <v>852</v>
+        <v>250</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B89" s="19" t="n">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>141</v>
+        <v>829</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>776</v>
+        <v>830</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>253</v>
+        <v>831</v>
       </c>
       <c r="G89" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H89" s="20" t="n">
-        <v>1.44</v>
+        <v>3.28</v>
       </c>
       <c r="I89" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=744370287305","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J89" s="8" t="s">
-        <v>250</v>
+        <v>832</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="n">
-        <v>220</v>
+        <v>12</v>
       </c>
       <c r="B90" s="19" t="n">
-        <v>46253</v>
+        <v>46300.4844444444</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>757</v>
+        <v>726</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>853</v>
+        <v>695</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>854</v>
+        <v>833</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>855</v>
+        <v>700</v>
       </c>
       <c r="G90" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H90" s="20" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="I90" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=744370287305","打开商品")</f>
-        <v>打开商品</v>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
+        <v>打开订单商品</v>
       </c>
       <c r="J90" s="8" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B91" s="19" t="n">
-        <v>46300.4844444444</v>
+        <v>46294.9525925926</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>749</v>
+        <v>734</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>718</v>
+        <v>623</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>857</v>
+        <v>835</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>723</v>
+        <v>624</v>
       </c>
       <c r="G91" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H91" s="20" t="n">
-        <v>0</v>
+        <v>84.59</v>
       </c>
       <c r="I91" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=585415365001","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J91" s="8" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B92" s="19" t="n">
-        <v>46294.9525925926</v>
+        <v>46291.7980902778</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>629</v>
+        <v>663</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>859</v>
+        <v>837</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>630</v>
+        <v>664</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H92" s="20" t="n">
-        <v>84.59</v>
+        <v>3.63</v>
       </c>
       <c r="I92" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=585415365001","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=781764816472","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J92" s="8" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B93" s="19" t="n">
-        <v>46291.7980902778</v>
+        <v>46291.7979166667</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>861</v>
+        <v>837</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H93" s="20" t="n">
-        <v>3.63</v>
+        <v>3.52</v>
       </c>
       <c r="I93" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=781764816472","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J93" s="8" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B94" s="19" t="n">
-        <v>46291.7979166667</v>
+        <v>46291.0479398148</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D94" s="8" t="s">
         <v>669</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>861</v>
+        <v>840</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>670</v>
@@ -15653,773 +15430,641 @@
         <v>1</v>
       </c>
       <c r="H94" s="20" t="n">
-        <v>3.52</v>
+        <v>3.42</v>
       </c>
       <c r="I94" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=781764816472","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=736162720327","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J94" s="8" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B95" s="19" t="n">
-        <v>46291.0479398148</v>
+        <v>46289.0137384259</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>864</v>
+        <v>842</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="G95" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H95" s="20" t="n">
-        <v>3.42</v>
+        <v>0.99</v>
       </c>
       <c r="I95" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=736162720327","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=945215173380","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J95" s="8" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B96" s="19" t="n">
-        <v>46289.0137384259</v>
+        <v>46286.4381134259</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>699</v>
+        <v>844</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>866</v>
+        <v>845</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>700</v>
+        <v>846</v>
       </c>
       <c r="G96" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>0.99</v>
+        <v>3.63</v>
       </c>
       <c r="I96" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=945215173380","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=567201709691","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J96" s="8" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B97" s="19" t="n">
         <v>46286.4381134259</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>868</v>
+        <v>844</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>869</v>
+        <v>845</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>870</v>
+        <v>848</v>
       </c>
       <c r="G97" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H97" s="20" t="n">
-        <v>3.63</v>
+        <v>3.3</v>
       </c>
       <c r="I97" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=567201709691","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J97" s="8" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="B98" s="19" t="n">
-        <v>46286.4381134259</v>
+        <v>46277.8198726852</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>868</v>
+        <v>695</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>869</v>
+        <v>833</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>872</v>
+        <v>710</v>
       </c>
       <c r="G98" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H98" s="20" t="n">
-        <v>3.3</v>
+        <v>3.88</v>
       </c>
       <c r="I98" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=567201709691","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J98" s="8" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B99" s="19" t="n">
         <v>46277.8198726852</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>718</v>
+        <v>695</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>857</v>
+        <v>833</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>733</v>
+        <v>707</v>
       </c>
       <c r="G99" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H99" s="20" t="n">
-        <v>3.88</v>
+        <v>3.59</v>
       </c>
       <c r="I99" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J99" s="8" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B100" s="19" t="n">
         <v>46277.8198726852</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>718</v>
+        <v>695</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>857</v>
+        <v>833</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>730</v>
+        <v>704</v>
       </c>
       <c r="G100" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>3.59</v>
+        <v>3.31</v>
       </c>
       <c r="I100" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J100" s="8" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B101" s="19" t="n">
         <v>46277.8198726852</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>718</v>
+        <v>695</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>857</v>
+        <v>833</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>727</v>
+        <v>696</v>
       </c>
       <c r="G101" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H101" s="20" t="n">
-        <v>3.31</v>
+        <v>3.03</v>
       </c>
       <c r="I101" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J101" s="8" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B102" s="19" t="n">
         <v>46277.8198726852</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>718</v>
+        <v>695</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>857</v>
+        <v>833</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="G102" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H102" s="20" t="n">
-        <v>3.03</v>
+        <v>3.59</v>
       </c>
       <c r="I102" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J102" s="8" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="n">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B103" s="19" t="n">
-        <v>46277.8198726852</v>
+        <v>46274.8817939815</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>718</v>
+        <v>611</v>
       </c>
       <c r="E103" s="8" t="s">
+        <v>855</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>609</v>
+      </c>
+      <c r="G103" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="H103" s="20" t="n">
+        <v>99</v>
+      </c>
+      <c r="I103" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1078248851201","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+      <c r="J103" s="8" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="B104" s="19" t="n">
+        <v>46272.8961458333</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="D104" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="E104" s="8" t="s">
         <v>857</v>
       </c>
-      <c r="F103" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="G103" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H103" s="20" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="I103" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="J103" s="8" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="1" t="n">
-        <v>104</v>
-      </c>
-      <c r="B104" s="19" t="n">
-        <v>46274.8817939815</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D104" s="8" t="s">
-        <v>617</v>
-      </c>
-      <c r="E104" s="8" t="s">
-        <v>879</v>
-      </c>
       <c r="F104" s="8" t="s">
-        <v>615</v>
+        <v>684</v>
       </c>
       <c r="G104" s="9" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H104" s="20" t="n">
-        <v>99</v>
+        <v>1.94</v>
       </c>
       <c r="I104" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1078248851201","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=625390659071","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J104" s="8" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B105" s="19" t="n">
         <v>46272.8961458333</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>706</v>
+        <v>683</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>881</v>
+        <v>859</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>707</v>
+        <v>689</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H105" s="20" t="n">
-        <v>1.94</v>
+        <v>2.91</v>
       </c>
       <c r="I105" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=625390659071","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=733598659967","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J105" s="8" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="n">
-        <v>112</v>
+        <v>168</v>
       </c>
       <c r="B106" s="19" t="n">
-        <v>46272.8961458333</v>
+        <v>46266.8829513889</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>706</v>
+        <v>611</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>883</v>
+        <v>855</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>712</v>
+        <v>609</v>
       </c>
       <c r="G106" s="9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H106" s="20" t="n">
-        <v>2.91</v>
+        <v>99</v>
       </c>
       <c r="I106" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=733598659967","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1078248851201","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J106" s="8" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B107" s="19" t="n">
         <v>46266.8829513889</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>879</v>
+        <v>855</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>615</v>
+        <v>862</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H107" s="20" t="n">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="I107" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1078248851201","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J107" s="8" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B108" s="19" t="n">
-        <v>46266.8829513889</v>
+        <v>46266.6967476852</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>617</v>
+        <v>683</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>879</v>
+        <v>859</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>886</v>
+        <v>689</v>
       </c>
       <c r="G108" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H108" s="20" t="n">
-        <v>45</v>
+        <v>2.91</v>
       </c>
       <c r="I108" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1078248851201","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=733598659967","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J108" s="8" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B109" s="19" t="n">
         <v>46266.6967476852</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>706</v>
+        <v>683</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>883</v>
+        <v>857</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>712</v>
+        <v>684</v>
       </c>
       <c r="G109" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H109" s="20" t="n">
-        <v>2.91</v>
+        <v>1.94</v>
       </c>
       <c r="I109" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=733598659967","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=625390659071","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J109" s="8" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B110" s="19" t="n">
-        <v>46266.6967476852</v>
+        <v>46265.3613773148</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>706</v>
+        <v>604</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>881</v>
+        <v>866</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>707</v>
+        <v>617</v>
       </c>
       <c r="G110" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H110" s="20" t="n">
-        <v>1.94</v>
+        <v>129.99</v>
       </c>
       <c r="I110" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=625390659071","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=768918125679","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J110" s="8" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B111" s="19" t="n">
-        <v>46265.3613773148</v>
+        <v>46259.9707407408</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>610</v>
+        <v>742</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>890</v>
+        <v>868</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>623</v>
+        <v>869</v>
       </c>
       <c r="G111" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H111" s="20" t="n">
-        <v>129.99</v>
+        <v>106.68</v>
       </c>
       <c r="I111" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=768918125679","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=588102758150","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J111" s="8" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="n">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="B112" s="19" t="n">
-        <v>46259.9707407408</v>
+        <v>46254.6453587963</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>765</v>
+        <v>825</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>892</v>
+        <v>826</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>893</v>
+        <v>827</v>
       </c>
       <c r="G112" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H112" s="20" t="n">
-        <v>106.68</v>
+        <v>188</v>
       </c>
       <c r="I112" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=588102758150","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=956985590887","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J112" s="8" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="n">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="B113" s="19" t="n">
-        <v>46258.6749768519</v>
+        <v>46254.0581481482</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>682</v>
+        <v>872</v>
       </c>
       <c r="E113" s="8" t="s">
-        <v>895</v>
+        <v>873</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>683</v>
+        <v>874</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H113" s="20" t="n">
-        <v>0.01</v>
+        <v>4.69</v>
       </c>
       <c r="I113" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=701774753211","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=621018369847","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J113" s="8" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="1" t="n">
-        <v>201</v>
-      </c>
-      <c r="B114" s="19" t="n">
-        <v>46258.6749768519</v>
-      </c>
-      <c r="C114" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D114" s="8" t="s">
-        <v>682</v>
-      </c>
-      <c r="E114" s="8" t="s">
-        <v>895</v>
-      </c>
-      <c r="F114" s="8" t="s">
-        <v>688</v>
-      </c>
-      <c r="G114" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H114" s="20" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I114" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=701774753211","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="J114" s="8" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="1" t="n">
-        <v>202</v>
-      </c>
-      <c r="B115" s="19" t="n">
-        <v>46258.6749768519</v>
-      </c>
-      <c r="C115" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D115" s="8" t="s">
-        <v>682</v>
-      </c>
-      <c r="E115" s="8" t="s">
-        <v>895</v>
-      </c>
-      <c r="F115" s="8" t="s">
-        <v>693</v>
-      </c>
-      <c r="G115" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H115" s="20" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I115" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=701774753211","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="J115" s="8" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="1" t="n">
-        <v>211</v>
-      </c>
-      <c r="B116" s="19" t="n">
-        <v>46254.6453587963</v>
-      </c>
-      <c r="C116" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D116" s="8" t="s">
-        <v>849</v>
-      </c>
-      <c r="E116" s="8" t="s">
-        <v>850</v>
-      </c>
-      <c r="F116" s="8" t="s">
-        <v>851</v>
-      </c>
-      <c r="G116" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H116" s="20" t="n">
-        <v>188</v>
-      </c>
-      <c r="I116" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=956985590887","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="J116" s="8" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="1" t="n">
-        <v>214</v>
-      </c>
-      <c r="B117" s="19" t="n">
-        <v>46254.0581481482</v>
-      </c>
-      <c r="C117" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="D117" s="8" t="s">
-        <v>900</v>
-      </c>
-      <c r="E117" s="8" t="s">
-        <v>901</v>
-      </c>
-      <c r="F117" s="8" t="s">
-        <v>902</v>
-      </c>
-      <c r="G117" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H117" s="20" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="I117" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=621018369847","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="J117" s="8" t="s">
-        <v>903</v>
+        <v>875</v>
       </c>
     </row>
   </sheetData>
@@ -16473,7 +16118,7 @@
     </row>
     <row r="2" customFormat="false" ht="27.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="22" t="s">
-        <v>904</v>
+        <v>876</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -16488,7 +16133,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>905</v>
+        <v>877</v>
       </c>
       <c r="B3" s="21"/>
       <c r="C3" s="21"/>
@@ -16503,7 +16148,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>906</v>
+        <v>878</v>
       </c>
       <c r="B4" s="21"/>
       <c r="C4" s="21"/>
@@ -16568,32 +16213,32 @@
     </row>
     <row r="7" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>907</v>
+        <v>879</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>840</v>
+        <v>816</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>908</v>
+        <v>880</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>909</v>
+        <v>881</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>837</v>
+        <v>813</v>
       </c>
       <c r="F7" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=581798084270","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>839</v>
+        <v>815</v>
       </c>
       <c r="H7" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>910</v>
+        <v>882</v>
       </c>
       <c r="J7" s="21" t="n">
         <v>154</v>
@@ -16604,32 +16249,32 @@
     </row>
     <row r="8" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>911</v>
+        <v>883</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>806</v>
+        <v>782</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>912</v>
+        <v>884</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>913</v>
+        <v>885</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>803</v>
+        <v>779</v>
       </c>
       <c r="F8" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=851008959999","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>805</v>
+        <v>781</v>
       </c>
       <c r="H8" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="21" t="s">
-        <v>914</v>
+        <v>886</v>
       </c>
       <c r="J8" s="21" t="n">
         <v>107</v>
@@ -16640,32 +16285,32 @@
     </row>
     <row r="9" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>911</v>
+        <v>883</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>802</v>
+        <v>778</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>915</v>
+        <v>887</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>909</v>
+        <v>881</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>799</v>
+        <v>775</v>
       </c>
       <c r="F9" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=19606507546","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>801</v>
+        <v>777</v>
       </c>
       <c r="H9" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I9" s="21" t="s">
-        <v>916</v>
+        <v>888</v>
       </c>
       <c r="J9" s="21" t="n">
         <v>106</v>
@@ -16676,32 +16321,32 @@
     </row>
     <row r="10" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>911</v>
+        <v>883</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>768</v>
+        <v>745</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>917</v>
+        <v>889</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>918</v>
+        <v>890</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>765</v>
+        <v>742</v>
       </c>
       <c r="F10" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=626569273184","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>767</v>
+        <v>744</v>
       </c>
       <c r="H10" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>919</v>
+        <v>891</v>
       </c>
       <c r="J10" s="21" t="n">
         <v>35</v>
@@ -16712,32 +16357,32 @@
     </row>
     <row r="11" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>920</v>
+        <v>892</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>798</v>
+        <v>774</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>921</v>
+        <v>893</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>909</v>
+        <v>881</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>795</v>
+        <v>771</v>
       </c>
       <c r="F11" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=979077591318","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>797</v>
+        <v>773</v>
       </c>
       <c r="H11" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I11" s="21" t="s">
-        <v>922</v>
+        <v>894</v>
       </c>
       <c r="J11" s="21" t="n">
         <v>105</v>
@@ -16748,32 +16393,32 @@
     </row>
     <row r="12" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>920</v>
+        <v>892</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>852</v>
+        <v>828</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>923</v>
+        <v>895</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>909</v>
+        <v>881</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>849</v>
+        <v>825</v>
       </c>
       <c r="F12" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=956985590887","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>851</v>
+        <v>827</v>
       </c>
       <c r="H12" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>924</v>
+        <v>896</v>
       </c>
       <c r="J12" s="21" t="n">
         <v>211</v>
@@ -16784,32 +16429,32 @@
     </row>
     <row r="13" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>925</v>
+        <v>897</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>774</v>
+        <v>750</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>926</v>
+        <v>898</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>927</v>
+        <v>899</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>771</v>
+        <v>747</v>
       </c>
       <c r="F13" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=566089419587","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>773</v>
+        <v>749</v>
       </c>
       <c r="H13" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I13" s="21" t="s">
-        <v>928</v>
+        <v>900</v>
       </c>
       <c r="J13" s="21" t="n">
         <v>43</v>
@@ -16820,32 +16465,32 @@
     </row>
     <row r="14" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>929</v>
+        <v>901</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>779</v>
+        <v>755</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>930</v>
+        <v>902</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>927</v>
+        <v>899</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>760</v>
+        <v>737</v>
       </c>
       <c r="F14" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=972313702890","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>778</v>
+        <v>754</v>
       </c>
       <c r="H14" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>931</v>
+        <v>903</v>
       </c>
       <c r="J14" s="21" t="n">
         <v>76</v>
@@ -16856,32 +16501,32 @@
     </row>
     <row r="15" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>911</v>
+        <v>883</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>856</v>
+        <v>832</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>932</v>
+        <v>904</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>909</v>
+        <v>881</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>853</v>
+        <v>829</v>
       </c>
       <c r="F15" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=744370287305","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>855</v>
+        <v>831</v>
       </c>
       <c r="H15" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I15" s="21" t="s">
-        <v>933</v>
+        <v>905</v>
       </c>
       <c r="J15" s="21" t="n">
         <v>220</v>
@@ -16892,32 +16537,32 @@
     </row>
     <row r="16" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>934</v>
+        <v>906</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>763</v>
+        <v>740</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>935</v>
+        <v>907</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>909</v>
+        <v>881</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>760</v>
+        <v>737</v>
       </c>
       <c r="F16" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1049340097483","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G16" s="21" t="s">
-        <v>762</v>
+        <v>739</v>
       </c>
       <c r="H16" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I16" s="21" t="s">
-        <v>936</v>
+        <v>908</v>
       </c>
       <c r="J16" s="21" t="n">
         <v>24</v>
@@ -16928,32 +16573,32 @@
     </row>
     <row r="17" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>937</v>
+        <v>909</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>938</v>
+        <v>910</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>886</v>
+        <v>862</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>939</v>
+        <v>911</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="F17" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1078248851201","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G17" s="21" t="s">
-        <v>886</v>
+        <v>862</v>
       </c>
       <c r="H17" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I17" s="21" t="s">
-        <v>940</v>
+        <v>912</v>
       </c>
       <c r="J17" s="21" t="n">
         <v>169</v>
@@ -16964,32 +16609,32 @@
     </row>
     <row r="18" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>941</v>
+        <v>913</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>942</v>
+        <v>914</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>943</v>
+        <v>915</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>944</v>
+        <v>916</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>765</v>
+        <v>742</v>
       </c>
       <c r="F18" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=588102758150","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G18" s="21" t="s">
-        <v>893</v>
+        <v>869</v>
       </c>
       <c r="H18" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I18" s="21" t="s">
-        <v>945</v>
+        <v>917</v>
       </c>
       <c r="J18" s="21" t="n">
         <v>189</v>
@@ -17000,32 +16645,32 @@
     </row>
     <row r="19" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>946</v>
+        <v>918</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>947</v>
+        <v>919</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>948</v>
+        <v>920</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>949</v>
+        <v>921</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>868</v>
+        <v>844</v>
       </c>
       <c r="F19" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=567201709691","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G19" s="21" t="s">
-        <v>870</v>
+        <v>846</v>
       </c>
       <c r="H19" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>950</v>
+        <v>922</v>
       </c>
       <c r="J19" s="21" t="n">
         <v>39</v>
@@ -17036,32 +16681,32 @@
     </row>
     <row r="20" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>946</v>
+        <v>918</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>951</v>
+        <v>923</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>952</v>
+        <v>924</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>949</v>
+        <v>921</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>868</v>
+        <v>844</v>
       </c>
       <c r="F20" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=567201709691","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G20" s="21" t="s">
-        <v>872</v>
+        <v>848</v>
       </c>
       <c r="H20" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I20" s="21" t="s">
-        <v>953</v>
+        <v>925</v>
       </c>
       <c r="J20" s="21" t="n">
         <v>40</v>
@@ -17072,32 +16717,32 @@
     </row>
     <row r="21" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>911</v>
+        <v>883</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>954</v>
+        <v>926</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>955</v>
+        <v>927</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>956</v>
+        <v>928</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>900</v>
+        <v>872</v>
       </c>
       <c r="F21" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=621018369847","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G21" s="21" t="s">
-        <v>902</v>
+        <v>874</v>
       </c>
       <c r="H21" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I21" s="21" t="s">
-        <v>957</v>
+        <v>929</v>
       </c>
       <c r="J21" s="21" t="n">
         <v>214</v>
@@ -17165,7 +16810,7 @@
     </row>
     <row r="2" customFormat="false" ht="27.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="22" t="s">
-        <v>958</v>
+        <v>930</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -17184,7 +16829,7 @@
     </row>
     <row r="3" customFormat="false" ht="40" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>959</v>
+        <v>931</v>
       </c>
       <c r="B3" s="21"/>
       <c r="C3" s="21"/>
@@ -17230,19 +16875,19 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>960</v>
+        <v>932</v>
       </c>
       <c r="B5" s="27" t="n">
         <v>20</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>961</v>
+        <v>933</v>
       </c>
       <c r="D5" s="27" t="n">
         <v>5</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>962</v>
+        <v>934</v>
       </c>
       <c r="F5" s="27" t="n">
         <v>12</v>
@@ -17276,16 +16921,16 @@
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>963</v>
+        <v>935</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>964</v>
+        <v>936</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>965</v>
+        <v>937</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>966</v>
+        <v>938</v>
       </c>
       <c r="E7" s="21"/>
       <c r="F7" s="21"/>
@@ -17301,7 +16946,7 @@
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>967</v>
+        <v>939</v>
       </c>
       <c r="B8" s="25" t="n">
         <f aca="false">SUM(I29:I72)</f>
@@ -17329,7 +16974,7 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>968</v>
+        <v>940</v>
       </c>
       <c r="B9" s="25" t="n">
         <v>0</v>
@@ -17355,7 +17000,7 @@
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="29" t="s">
-        <v>969</v>
+        <v>941</v>
       </c>
       <c r="B10" s="30" t="n">
         <f aca="false">B8+B9</f>
@@ -17383,7 +17028,7 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>970</v>
+        <v>942</v>
       </c>
       <c r="B11" s="25" t="n">
         <f aca="false">$B$5/$D$5*$B$4</f>
@@ -17411,7 +17056,7 @@
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="29" t="s">
-        <v>971</v>
+        <v>943</v>
       </c>
       <c r="B12" s="30" t="n">
         <f aca="false">B8+B11</f>
@@ -17456,7 +17101,7 @@
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>972</v>
+        <v>944</v>
       </c>
       <c r="B14" s="25"/>
       <c r="C14" s="25"/>
@@ -17475,16 +17120,16 @@
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="s">
-        <v>973</v>
+        <v>945</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>974</v>
+        <v>946</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>975</v>
+        <v>947</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>976</v>
+        <v>948</v>
       </c>
       <c r="E15" s="21"/>
       <c r="F15" s="21"/>
@@ -17500,7 +17145,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>977</v>
+        <v>949</v>
       </c>
       <c r="B16" s="25" t="n">
         <f aca="false">SUM(L29:L72)</f>
@@ -17528,7 +17173,7 @@
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="29" t="s">
-        <v>978</v>
+        <v>950</v>
       </c>
       <c r="B17" s="30" t="n">
         <f aca="false">B16</f>
@@ -17556,7 +17201,7 @@
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>979</v>
+        <v>951</v>
       </c>
       <c r="B18" s="25" t="n">
         <f aca="false">ROUNDUP($B$4/$D$5,0)*$B$5</f>
@@ -17584,7 +17229,7 @@
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="29" t="s">
-        <v>980</v>
+        <v>952</v>
       </c>
       <c r="B19" s="30" t="n">
         <f aca="false">B16+B18</f>
@@ -17629,7 +17274,7 @@
     </row>
     <row r="21" customFormat="false" ht="40" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>981</v>
+        <v>953</v>
       </c>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
@@ -17648,10 +17293,10 @@
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>982</v>
+        <v>954</v>
       </c>
       <c r="B22" s="25" t="n">
-        <f aca="false">配件与耗材!K19</f>
+        <f aca="false">配件与耗材!K18</f>
         <v>84.59</v>
       </c>
       <c r="C22" s="25"/>
@@ -17670,7 +17315,7 @@
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="29" t="s">
-        <v>983</v>
+        <v>955</v>
       </c>
       <c r="B23" s="30" t="n">
         <f aca="false">D10+B22</f>
@@ -17692,7 +17337,7 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="29" t="s">
-        <v>984</v>
+        <v>956</v>
       </c>
       <c r="B24" s="30" t="n">
         <f aca="false">D12+B22</f>
@@ -17731,7 +17376,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>985</v>
+        <v>957</v>
       </c>
       <c r="B26" s="21"/>
       <c r="C26" s="21"/>
@@ -17767,43 +17412,43 @@
     </row>
     <row r="28" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="23" t="s">
-        <v>986</v>
+        <v>958</v>
       </c>
       <c r="B28" s="23" t="s">
         <v>552</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>987</v>
+        <v>959</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>988</v>
+        <v>960</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>989</v>
+        <v>961</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>990</v>
+        <v>962</v>
       </c>
       <c r="G28" s="23" t="s">
-        <v>991</v>
+        <v>963</v>
       </c>
       <c r="H28" s="23" t="s">
-        <v>992</v>
+        <v>964</v>
       </c>
       <c r="I28" s="23" t="s">
-        <v>993</v>
+        <v>965</v>
       </c>
       <c r="J28" s="23" t="s">
-        <v>994</v>
+        <v>966</v>
       </c>
       <c r="K28" s="23" t="s">
-        <v>995</v>
+        <v>967</v>
       </c>
       <c r="L28" s="23" t="s">
-        <v>996</v>
+        <v>968</v>
       </c>
       <c r="M28" s="23" t="s">
-        <v>997</v>
+        <v>969</v>
       </c>
       <c r="N28" s="23" t="s">
         <v>550</v>
@@ -17814,7 +17459,7 @@
     </row>
     <row r="29" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>998</v>
+        <v>970</v>
       </c>
       <c r="B29" s="21" t="n">
         <v>1</v>
@@ -17870,7 +17515,7 @@
     </row>
     <row r="30" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>999</v>
+        <v>971</v>
       </c>
       <c r="B30" s="21" t="n">
         <v>1</v>
@@ -17926,7 +17571,7 @@
     </row>
     <row r="31" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>1000</v>
+        <v>972</v>
       </c>
       <c r="B31" s="21" t="n">
         <v>100</v>
@@ -17982,7 +17627,7 @@
     </row>
     <row r="32" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>1001</v>
+        <v>973</v>
       </c>
       <c r="B32" s="21" t="n">
         <v>100</v>
@@ -18038,7 +17683,7 @@
     </row>
     <row r="33" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>1002</v>
+        <v>974</v>
       </c>
       <c r="B33" s="21" t="n">
         <v>1</v>
@@ -18094,7 +17739,7 @@
     </row>
     <row r="34" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
-        <v>1003</v>
+        <v>975</v>
       </c>
       <c r="B34" s="21" t="n">
         <v>100</v>
@@ -18150,7 +17795,7 @@
     </row>
     <row r="35" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
-        <v>1004</v>
+        <v>976</v>
       </c>
       <c r="B35" s="21" t="n">
         <v>100</v>
@@ -18206,7 +17851,7 @@
     </row>
     <row r="36" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>1005</v>
+        <v>977</v>
       </c>
       <c r="B36" s="21" t="n">
         <v>20</v>
@@ -18262,7 +17907,7 @@
     </row>
     <row r="37" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
-        <v>1006</v>
+        <v>978</v>
       </c>
       <c r="B37" s="21" t="n">
         <v>50</v>
@@ -18318,7 +17963,7 @@
     </row>
     <row r="38" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="21" t="s">
-        <v>1007</v>
+        <v>979</v>
       </c>
       <c r="B38" s="21" t="n">
         <v>100</v>
@@ -18374,7 +18019,7 @@
     </row>
     <row r="39" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="21" t="s">
-        <v>1008</v>
+        <v>980</v>
       </c>
       <c r="B39" s="21" t="n">
         <v>100</v>
@@ -18430,7 +18075,7 @@
     </row>
     <row r="40" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="21" t="s">
-        <v>1009</v>
+        <v>981</v>
       </c>
       <c r="B40" s="21" t="n">
         <v>50</v>
@@ -18486,7 +18131,7 @@
     </row>
     <row r="41" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="21" t="s">
-        <v>1010</v>
+        <v>982</v>
       </c>
       <c r="B41" s="21" t="n">
         <v>2</v>
@@ -18542,7 +18187,7 @@
     </row>
     <row r="42" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="21" t="s">
-        <v>1011</v>
+        <v>983</v>
       </c>
       <c r="B42" s="21" t="n">
         <v>15</v>
@@ -18598,7 +18243,7 @@
     </row>
     <row r="43" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="21" t="s">
-        <v>1012</v>
+        <v>984</v>
       </c>
       <c r="B43" s="21" t="n">
         <v>50</v>
@@ -18654,7 +18299,7 @@
     </row>
     <row r="44" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="21" t="s">
-        <v>1013</v>
+        <v>985</v>
       </c>
       <c r="B44" s="21" t="n">
         <v>10</v>
@@ -18710,7 +18355,7 @@
     </row>
     <row r="45" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="21" t="s">
-        <v>1014</v>
+        <v>986</v>
       </c>
       <c r="B45" s="21" t="n">
         <v>2</v>
@@ -18766,7 +18411,7 @@
     </row>
     <row r="46" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="21" t="s">
-        <v>1015</v>
+        <v>987</v>
       </c>
       <c r="B46" s="21" t="n">
         <v>50</v>
@@ -18822,7 +18467,7 @@
     </row>
     <row r="47" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="21" t="s">
-        <v>1016</v>
+        <v>988</v>
       </c>
       <c r="B47" s="21" t="n">
         <v>20</v>
@@ -18878,7 +18523,7 @@
     </row>
     <row r="48" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="21" t="s">
-        <v>1017</v>
+        <v>989</v>
       </c>
       <c r="B48" s="21" t="n">
         <v>100</v>
@@ -18934,7 +18579,7 @@
     </row>
     <row r="49" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="21" t="s">
-        <v>1018</v>
+        <v>990</v>
       </c>
       <c r="B49" s="21" t="n">
         <v>100</v>
@@ -18990,7 +18635,7 @@
     </row>
     <row r="50" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="21" t="s">
-        <v>1019</v>
+        <v>991</v>
       </c>
       <c r="B50" s="21" t="n">
         <v>100</v>
@@ -19046,7 +18691,7 @@
     </row>
     <row r="51" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="21" t="s">
-        <v>1020</v>
+        <v>992</v>
       </c>
       <c r="B51" s="21" t="n">
         <v>100</v>
@@ -19102,7 +18747,7 @@
     </row>
     <row r="52" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="21" t="s">
-        <v>1021</v>
+        <v>993</v>
       </c>
       <c r="B52" s="21" t="n">
         <v>100</v>
@@ -19158,7 +18803,7 @@
     </row>
     <row r="53" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="21" t="s">
-        <v>1022</v>
+        <v>994</v>
       </c>
       <c r="B53" s="21" t="n">
         <v>1</v>
@@ -19214,7 +18859,7 @@
     </row>
     <row r="54" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="21" t="s">
-        <v>1023</v>
+        <v>995</v>
       </c>
       <c r="B54" s="21" t="n">
         <v>1</v>
@@ -19270,7 +18915,7 @@
     </row>
     <row r="55" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="21" t="s">
-        <v>1024</v>
+        <v>996</v>
       </c>
       <c r="B55" s="21" t="n">
         <v>20</v>
@@ -19326,7 +18971,7 @@
     </row>
     <row r="56" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="21" t="s">
-        <v>1025</v>
+        <v>997</v>
       </c>
       <c r="B56" s="21" t="n">
         <v>5</v>
@@ -19382,7 +19027,7 @@
     </row>
     <row r="57" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="21" t="s">
-        <v>1026</v>
+        <v>998</v>
       </c>
       <c r="B57" s="21" t="n">
         <v>5</v>
@@ -19438,7 +19083,7 @@
     </row>
     <row r="58" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="21" t="s">
-        <v>1027</v>
+        <v>999</v>
       </c>
       <c r="B58" s="21" t="n">
         <v>5</v>
@@ -19494,7 +19139,7 @@
     </row>
     <row r="59" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="21" t="s">
-        <v>1028</v>
+        <v>1000</v>
       </c>
       <c r="B59" s="21" t="n">
         <v>1</v>
@@ -19550,7 +19195,7 @@
     </row>
     <row r="60" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="21" t="s">
-        <v>1029</v>
+        <v>1001</v>
       </c>
       <c r="B60" s="21" t="n">
         <v>1</v>
@@ -19606,7 +19251,7 @@
     </row>
     <row r="61" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="21" t="s">
-        <v>1030</v>
+        <v>1002</v>
       </c>
       <c r="B61" s="21" t="n">
         <v>1</v>
@@ -19662,7 +19307,7 @@
     </row>
     <row r="62" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="21" t="s">
-        <v>1031</v>
+        <v>1003</v>
       </c>
       <c r="B62" s="21" t="n">
         <v>1</v>
@@ -19718,7 +19363,7 @@
     </row>
     <row r="63" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="21" t="s">
-        <v>1032</v>
+        <v>1004</v>
       </c>
       <c r="B63" s="21" t="n">
         <v>1</v>
@@ -19774,7 +19419,7 @@
     </row>
     <row r="64" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="21" t="s">
-        <v>1033</v>
+        <v>1005</v>
       </c>
       <c r="B64" s="21" t="n">
         <v>100</v>
@@ -19830,7 +19475,7 @@
     </row>
     <row r="65" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="21" t="s">
-        <v>1034</v>
+        <v>1006</v>
       </c>
       <c r="B65" s="21" t="n">
         <v>30</v>
@@ -19886,7 +19531,7 @@
     </row>
     <row r="66" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="21" t="s">
-        <v>1035</v>
+        <v>1007</v>
       </c>
       <c r="B66" s="21" t="n">
         <v>100</v>
@@ -19942,7 +19587,7 @@
     </row>
     <row r="67" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="21" t="s">
-        <v>1036</v>
+        <v>1008</v>
       </c>
       <c r="B67" s="21" t="n">
         <v>100</v>
@@ -19998,7 +19643,7 @@
     </row>
     <row r="68" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="21" t="s">
-        <v>1037</v>
+        <v>1009</v>
       </c>
       <c r="B68" s="21" t="n">
         <v>100</v>
@@ -20054,7 +19699,7 @@
     </row>
     <row r="69" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="21" t="s">
-        <v>1038</v>
+        <v>1010</v>
       </c>
       <c r="B69" s="21" t="n">
         <v>1</v>
@@ -20110,7 +19755,7 @@
     </row>
     <row r="70" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="21" t="s">
-        <v>1039</v>
+        <v>1011</v>
       </c>
       <c r="B70" s="21" t="n">
         <v>1</v>
@@ -20166,7 +19811,7 @@
     </row>
     <row r="71" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="21" t="s">
-        <v>1040</v>
+        <v>1012</v>
       </c>
       <c r="B71" s="21" t="n">
         <v>1</v>
@@ -20222,7 +19867,7 @@
     </row>
     <row r="72" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="21" t="s">
-        <v>1041</v>
+        <v>1013</v>
       </c>
       <c r="B72" s="21" t="n">
         <v>1</v>
@@ -20327,7 +19972,7 @@
     </row>
     <row r="2" customFormat="false" ht="27.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="34" t="s">
-        <v>1042</v>
+        <v>1014</v>
       </c>
       <c r="B2" s="34"/>
       <c r="C2" s="34"/>
@@ -20339,7 +19984,7 @@
     </row>
     <row r="3" customFormat="false" ht="40" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="33" t="s">
-        <v>1043</v>
+        <v>1015</v>
       </c>
       <c r="B3" s="33"/>
       <c r="C3" s="33"/>
@@ -20351,11 +19996,11 @@
     </row>
     <row r="4" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="35" t="s">
-        <v>1044</v>
+        <v>1016</v>
       </c>
       <c r="B4" s="36" t="n">
-        <f aca="false">SUM(F11:F42)</f>
-        <v>2244.28313676336</v>
+        <f aca="false">SUM(F11:F39)</f>
+        <v>2243.68313676336</v>
       </c>
       <c r="C4" s="33"/>
       <c r="D4" s="33"/>
@@ -20366,11 +20011,11 @@
     </row>
     <row r="5" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="35" t="s">
-        <v>1045</v>
+        <v>1017</v>
       </c>
       <c r="B5" s="36" t="n">
         <f aca="false">B4+(D11+D12)*制作成本!$B$5/制作成本!$D$5</f>
-        <v>2252.28313676336</v>
+        <v>2251.68313676336</v>
       </c>
       <c r="C5" s="33"/>
       <c r="D5" s="33"/>
@@ -20381,11 +20026,11 @@
     </row>
     <row r="6" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="35" t="s">
-        <v>1046</v>
+        <v>1018</v>
       </c>
       <c r="B6" s="36" t="n">
         <f aca="false">B4-F11-F12+制作成本!D16</f>
-        <v>2303.34</v>
+        <v>2302.74</v>
       </c>
       <c r="C6" s="33"/>
       <c r="D6" s="33"/>
@@ -20396,11 +20041,11 @@
     </row>
     <row r="7" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="35" t="s">
-        <v>1047</v>
+        <v>1019</v>
       </c>
       <c r="B7" s="36" t="n">
         <f aca="false">B6+ROUNDUP(D11/制作成本!$D$5,0)*制作成本!$B$5+ROUNDUP(D12/制作成本!$D$5,0)*制作成本!$B$5</f>
-        <v>2343.34</v>
+        <v>2342.74</v>
       </c>
       <c r="C7" s="33"/>
       <c r="D7" s="33"/>
@@ -20421,7 +20066,7 @@
     </row>
     <row r="9" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>1048</v>
+        <v>1020</v>
       </c>
       <c r="B9" s="33"/>
       <c r="C9" s="33"/>
@@ -20433,39 +20078,39 @@
     </row>
     <row r="10" customFormat="false" ht="40" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="37" t="s">
-        <v>1049</v>
+        <v>1021</v>
       </c>
       <c r="B10" s="37" t="s">
-        <v>986</v>
+        <v>958</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>1050</v>
+        <v>1022</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>1051</v>
+        <v>1023</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>1052</v>
+        <v>1024</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>1053</v>
+        <v>1025</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>1054</v>
+        <v>1026</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>1055</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>1056</v>
+        <v>1028</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>1057</v>
+        <v>1029</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>1058</v>
+        <v>1030</v>
       </c>
       <c r="D11" s="38" t="n">
         <f aca="false">合并采购清单!B4</f>
@@ -20480,7 +20125,7 @@
         <v>15.5395050849176</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>1059</v>
+        <v>1031</v>
       </c>
       <c r="H11" s="41" t="str">
         <f aca="false">HYPERLINK("https://github.com/kissqy/Microduck-kissqy/blob/main/hardware/README.md#完整位号bom","查看完整BOM")</f>
@@ -20489,13 +20134,13 @@
     </row>
     <row r="12" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="s">
-        <v>1060</v>
+        <v>1032</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>1061</v>
+        <v>1033</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>1058</v>
+        <v>1030</v>
       </c>
       <c r="D12" s="38" t="n">
         <f aca="false">合并采购清单!D4</f>
@@ -20510,7 +20155,7 @@
         <v>12.3336316784379</v>
       </c>
       <c r="G12" s="33" t="s">
-        <v>1059</v>
+        <v>1031</v>
       </c>
       <c r="H12" s="41" t="str">
         <f aca="false">HYPERLINK("https://github.com/kissqy/Microduck-kissqy/blob/main/hardware/README.md#完整位号bom","查看完整BOM")</f>
@@ -20519,19 +20164,19 @@
     </row>
     <row r="13" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>1062</v>
+        <v>1034</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>1063</v>
+        <v>1035</v>
       </c>
       <c r="D13" s="42" t="n">
         <v>15</v>
       </c>
       <c r="E13" s="39" t="n">
-        <f aca="false">配件与耗材!K17</f>
+        <f aca="false">配件与耗材!K16</f>
         <v>99</v>
       </c>
       <c r="F13" s="40" t="n">
@@ -20539,7 +20184,7 @@
         <v>1485</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="H13" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1078248851201","打开订单商品")</f>
@@ -20548,19 +20193,19 @@
     </row>
     <row r="14" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>1064</v>
+        <v>1036</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>1065</v>
+        <v>1037</v>
       </c>
       <c r="D14" s="42" t="n">
         <v>1</v>
       </c>
       <c r="E14" s="39" t="n">
-        <f aca="false">配件与耗材!K16</f>
+        <f aca="false">配件与耗材!K15</f>
         <v>309</v>
       </c>
       <c r="F14" s="40" t="n">
@@ -20568,7 +20213,7 @@
         <v>309</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="H14" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=763812025816","打开订单商品")</f>
@@ -20577,19 +20222,19 @@
     </row>
     <row r="15" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>1066</v>
+        <v>1038</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>1067</v>
+        <v>1039</v>
       </c>
       <c r="D15" s="42" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="39" t="n">
-        <f aca="false">配件与耗材!K19</f>
+        <f aca="false">配件与耗材!K18</f>
         <v>84.59</v>
       </c>
       <c r="F15" s="40" t="n">
@@ -20597,7 +20242,7 @@
         <v>84.59</v>
       </c>
       <c r="G15" s="33" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="H15" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=585415365001","打开订单商品")</f>
@@ -20606,19 +20251,19 @@
     </row>
     <row r="16" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="33" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>1068</v>
+        <v>1040</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>1065</v>
+        <v>1037</v>
       </c>
       <c r="D16" s="42" t="n">
         <v>1</v>
       </c>
       <c r="E16" s="39" t="n">
-        <f aca="false">配件与耗材!K18</f>
+        <f aca="false">配件与耗材!K17</f>
         <v>129.99</v>
       </c>
       <c r="F16" s="40" t="n">
@@ -20626,7 +20271,7 @@
         <v>129.99</v>
       </c>
       <c r="G16" s="33" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="H16" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=768918125679","打开订单商品")</f>
@@ -20635,19 +20280,19 @@
     </row>
     <row r="17" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="33" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>1069</v>
+        <v>1041</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>1065</v>
+        <v>1037</v>
       </c>
       <c r="D17" s="42" t="n">
         <v>1</v>
       </c>
       <c r="E17" s="39" t="n">
-        <f aca="false">配件与耗材!K15</f>
+        <f aca="false">配件与耗材!K14</f>
         <v>49.5</v>
       </c>
       <c r="F17" s="40" t="n">
@@ -20655,7 +20300,7 @@
         <v>49.5</v>
       </c>
       <c r="G17" s="33" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="H17" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=737603917521","打开订单商品")</f>
@@ -20664,19 +20309,19 @@
     </row>
     <row r="18" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="33" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>1070</v>
+        <v>1042</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>1065</v>
+        <v>1037</v>
       </c>
       <c r="D18" s="42" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="39" t="n">
-        <f aca="false">配件与耗材!K14</f>
+        <f aca="false">配件与耗材!K13</f>
         <v>3.08</v>
       </c>
       <c r="F18" s="40" t="n">
@@ -20684,7 +20329,7 @@
         <v>3.08</v>
       </c>
       <c r="G18" s="33" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="H18" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=683920556900","打开订单商品")</f>
@@ -20693,19 +20338,19 @@
     </row>
     <row r="19" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="33" t="s">
-        <v>703</v>
+        <v>680</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>1071</v>
+        <v>1043</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>1063</v>
+        <v>1035</v>
       </c>
       <c r="D19" s="42" t="n">
         <v>5</v>
       </c>
       <c r="E19" s="39" t="n">
-        <f aca="false">配件与耗材!K32</f>
+        <f aca="false">配件与耗材!K28</f>
         <v>1.94</v>
       </c>
       <c r="F19" s="40" t="n">
@@ -20713,7 +20358,7 @@
         <v>9.7</v>
       </c>
       <c r="G19" s="33" t="s">
-        <v>1072</v>
+        <v>1044</v>
       </c>
       <c r="H19" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=625390659071","打开订单商品")</f>
@@ -20722,19 +20367,19 @@
     </row>
     <row r="20" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="33" t="s">
-        <v>709</v>
+        <v>686</v>
       </c>
       <c r="B20" s="33" t="s">
-        <v>1073</v>
+        <v>1045</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>1063</v>
+        <v>1035</v>
       </c>
       <c r="D20" s="42" t="n">
         <v>12</v>
       </c>
       <c r="E20" s="39" t="n">
-        <f aca="false">配件与耗材!K33</f>
+        <f aca="false">配件与耗材!K29</f>
         <v>2.91</v>
       </c>
       <c r="F20" s="40" t="n">
@@ -20742,7 +20387,7 @@
         <v>34.92</v>
       </c>
       <c r="G20" s="33" t="s">
-        <v>1074</v>
+        <v>1046</v>
       </c>
       <c r="H20" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=733598659967","打开订单商品")</f>
@@ -20751,19 +20396,19 @@
     </row>
     <row r="21" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="33" t="s">
-        <v>715</v>
+        <v>692</v>
       </c>
       <c r="B21" s="33" t="s">
-        <v>1075</v>
+        <v>1047</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>1076</v>
+        <v>1048</v>
       </c>
       <c r="D21" s="42" t="n">
         <v>1</v>
       </c>
       <c r="E21" s="39" t="n">
-        <f aca="false">配件与耗材!K34</f>
+        <f aca="false">配件与耗材!K30</f>
         <v>3.03</v>
       </c>
       <c r="F21" s="40" t="n">
@@ -20771,7 +20416,7 @@
         <v>3.03</v>
       </c>
       <c r="G21" s="33" t="s">
-        <v>1077</v>
+        <v>1049</v>
       </c>
       <c r="H21" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
@@ -20780,19 +20425,19 @@
     </row>
     <row r="22" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="33" t="s">
-        <v>721</v>
+        <v>698</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>1078</v>
+        <v>1050</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>1076</v>
+        <v>1048</v>
       </c>
       <c r="D22" s="42" t="n">
         <v>1</v>
       </c>
       <c r="E22" s="39" t="n">
-        <f aca="false">配件与耗材!K35</f>
+        <f aca="false">配件与耗材!K31</f>
         <v>0</v>
       </c>
       <c r="F22" s="40" t="n">
@@ -20800,7 +20445,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="33" t="s">
-        <v>1079</v>
+        <v>1051</v>
       </c>
       <c r="H22" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
@@ -20809,19 +20454,19 @@
     </row>
     <row r="23" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="33" t="s">
-        <v>725</v>
+        <v>702</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>1080</v>
+        <v>1052</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>1076</v>
+        <v>1048</v>
       </c>
       <c r="D23" s="42" t="n">
         <v>1</v>
       </c>
       <c r="E23" s="39" t="n">
-        <f aca="false">配件与耗材!K36</f>
+        <f aca="false">配件与耗材!K32</f>
         <v>3.31</v>
       </c>
       <c r="F23" s="40" t="n">
@@ -20829,7 +20474,7 @@
         <v>3.31</v>
       </c>
       <c r="G23" s="33" t="s">
-        <v>1077</v>
+        <v>1049</v>
       </c>
       <c r="H23" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
@@ -20838,19 +20483,19 @@
     </row>
     <row r="24" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="33" t="s">
-        <v>728</v>
+        <v>705</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>1081</v>
+        <v>1053</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>1076</v>
+        <v>1048</v>
       </c>
       <c r="D24" s="42" t="n">
         <v>1</v>
       </c>
       <c r="E24" s="39" t="n">
-        <f aca="false">配件与耗材!K37</f>
+        <f aca="false">配件与耗材!K33</f>
         <v>3.59</v>
       </c>
       <c r="F24" s="40" t="n">
@@ -20858,7 +20503,7 @@
         <v>3.59</v>
       </c>
       <c r="G24" s="33" t="s">
-        <v>1077</v>
+        <v>1049</v>
       </c>
       <c r="H24" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
@@ -20867,19 +20512,19 @@
     </row>
     <row r="25" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="33" t="s">
-        <v>731</v>
+        <v>708</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>1082</v>
+        <v>1054</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>1076</v>
+        <v>1048</v>
       </c>
       <c r="D25" s="42" t="n">
         <v>1</v>
       </c>
       <c r="E25" s="39" t="n">
-        <f aca="false">配件与耗材!K38</f>
+        <f aca="false">配件与耗材!K34</f>
         <v>3.88</v>
       </c>
       <c r="F25" s="40" t="n">
@@ -20887,7 +20532,7 @@
         <v>3.88</v>
       </c>
       <c r="G25" s="33" t="s">
-        <v>1077</v>
+        <v>1049</v>
       </c>
       <c r="H25" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
@@ -20896,19 +20541,19 @@
     </row>
     <row r="26" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="33" t="s">
-        <v>734</v>
+        <v>711</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>1083</v>
+        <v>1055</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>1076</v>
+        <v>1048</v>
       </c>
       <c r="D26" s="42" t="n">
         <v>1</v>
       </c>
       <c r="E26" s="39" t="n">
-        <f aca="false">配件与耗材!K39</f>
+        <f aca="false">配件与耗材!K35</f>
         <v>3.59</v>
       </c>
       <c r="F26" s="40" t="n">
@@ -20916,7 +20561,7 @@
         <v>3.59</v>
       </c>
       <c r="G26" s="33" t="s">
-        <v>1077</v>
+        <v>1049</v>
       </c>
       <c r="H26" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
@@ -20928,10 +20573,10 @@
         <v>567</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>1084</v>
+        <v>1056</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>1085</v>
+        <v>1057</v>
       </c>
       <c r="D27" s="42" t="n">
         <v>1</v>
@@ -20957,10 +20602,10 @@
         <v>572</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>1086</v>
+        <v>1058</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>1085</v>
+        <v>1057</v>
       </c>
       <c r="D28" s="42" t="n">
         <v>1</v>
@@ -20986,10 +20631,10 @@
         <v>577</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>1087</v>
+        <v>1059</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>1088</v>
+        <v>1060</v>
       </c>
       <c r="D29" s="42" t="n">
         <v>1</v>
@@ -21015,10 +20660,10 @@
         <v>583</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>1089</v>
+        <v>1061</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>1090</v>
+        <v>1062</v>
       </c>
       <c r="D30" s="42" t="n">
         <v>1</v>
@@ -21041,19 +20686,19 @@
     </row>
     <row r="31" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="33" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="B31" s="33" t="s">
-        <v>1091</v>
+        <v>1063</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>1092</v>
+        <v>1064</v>
       </c>
       <c r="D31" s="42" t="n">
         <v>30</v>
       </c>
       <c r="E31" s="39" t="n">
-        <f aca="false">配件与耗材!K20</f>
+        <f aca="false">配件与耗材!K19</f>
         <v>0.9</v>
       </c>
       <c r="F31" s="40" t="n">
@@ -21061,7 +20706,7 @@
         <v>27</v>
       </c>
       <c r="G31" s="33" t="s">
-        <v>1093</v>
+        <v>1065</v>
       </c>
       <c r="H31" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=825340808235","打开订单商品")</f>
@@ -21070,19 +20715,19 @@
     </row>
     <row r="32" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="33" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>1094</v>
+        <v>1066</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>1092</v>
+        <v>1064</v>
       </c>
       <c r="D32" s="42" t="n">
         <v>30</v>
       </c>
       <c r="E32" s="39" t="n">
-        <f aca="false">配件与耗材!K21</f>
+        <f aca="false">配件与耗材!K20</f>
         <v>0.9</v>
       </c>
       <c r="F32" s="40" t="n">
@@ -21090,7 +20735,7 @@
         <v>27</v>
       </c>
       <c r="G32" s="33" t="s">
-        <v>1095</v>
+        <v>1067</v>
       </c>
       <c r="H32" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=825340808235","打开订单商品")</f>
@@ -21099,19 +20744,19 @@
     </row>
     <row r="33" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="33" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>1096</v>
+        <v>1068</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>1065</v>
+        <v>1037</v>
       </c>
       <c r="D33" s="42" t="n">
         <v>50</v>
       </c>
       <c r="E33" s="39" t="n">
-        <f aca="false">配件与耗材!K22</f>
+        <f aca="false">配件与耗材!K21</f>
         <v>0.04</v>
       </c>
       <c r="F33" s="40" t="n">
@@ -21119,7 +20764,7 @@
         <v>2</v>
       </c>
       <c r="G33" s="33" t="s">
-        <v>1097</v>
+        <v>1069</v>
       </c>
       <c r="H33" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=891600917698","打开订单商品")</f>
@@ -21128,19 +20773,19 @@
     </row>
     <row r="34" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="33" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>1098</v>
+        <v>1070</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>1088</v>
+        <v>1060</v>
       </c>
       <c r="D34" s="42" t="n">
         <v>1</v>
       </c>
       <c r="E34" s="39" t="n">
-        <f aca="false">配件与耗材!K23</f>
+        <f aca="false">配件与耗材!K22</f>
         <v>2.68</v>
       </c>
       <c r="F34" s="40" t="n">
@@ -21148,7 +20793,7 @@
         <v>2.68</v>
       </c>
       <c r="G34" s="33" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="H34" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=891600917698","打开订单商品")</f>
@@ -21157,19 +20802,19 @@
     </row>
     <row r="35" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="33" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="B35" s="33" t="s">
-        <v>1099</v>
+        <v>1071</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>1065</v>
+        <v>1037</v>
       </c>
       <c r="D35" s="42" t="n">
         <v>10</v>
       </c>
       <c r="E35" s="39" t="n">
-        <f aca="false">配件与耗材!K24</f>
+        <f aca="false">配件与耗材!K23</f>
         <v>0.3</v>
       </c>
       <c r="F35" s="40" t="n">
@@ -21177,7 +20822,7 @@
         <v>3</v>
       </c>
       <c r="G35" s="33" t="s">
-        <v>1100</v>
+        <v>1072</v>
       </c>
       <c r="H35" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=598425041338","打开订单商品")</f>
@@ -21186,19 +20831,19 @@
     </row>
     <row r="36" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="33" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="B36" s="33" t="s">
-        <v>1101</v>
+        <v>1073</v>
       </c>
       <c r="C36" s="33" t="s">
-        <v>1065</v>
+        <v>1037</v>
       </c>
       <c r="D36" s="42" t="n">
         <v>10</v>
       </c>
       <c r="E36" s="39" t="n">
-        <f aca="false">配件与耗材!K25</f>
+        <f aca="false">配件与耗材!K24</f>
         <v>0.27</v>
       </c>
       <c r="F36" s="40" t="n">
@@ -21206,7 +20851,7 @@
         <v>2.7</v>
       </c>
       <c r="G36" s="33" t="s">
-        <v>1102</v>
+        <v>1074</v>
       </c>
       <c r="H36" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=595594145847","打开订单商品")</f>
@@ -21215,19 +20860,19 @@
     </row>
     <row r="37" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="33" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="B37" s="33" t="s">
-        <v>1103</v>
+        <v>1075</v>
       </c>
       <c r="C37" s="33" t="s">
-        <v>1104</v>
+        <v>1076</v>
       </c>
       <c r="D37" s="42" t="n">
         <v>3</v>
       </c>
       <c r="E37" s="43" t="n">
-        <f aca="false">(订单匹配依据!G93*订单匹配依据!H93+订单匹配依据!G94*订单匹配依据!H94)/(订单匹配依据!G93+订单匹配依据!G94)</f>
+        <f aca="false">(订单匹配依据!G92*订单匹配依据!H92+订单匹配依据!G93*订单匹配依据!H93)/(订单匹配依据!G92+订单匹配依据!G93)</f>
         <v>3.59333333333333</v>
       </c>
       <c r="F37" s="40" t="n">
@@ -21235,7 +20880,7 @@
         <v>10.78</v>
       </c>
       <c r="G37" s="33" t="s">
-        <v>1105</v>
+        <v>1077</v>
       </c>
       <c r="H37" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=781764816472","打开订单商品")</f>
@@ -21244,19 +20889,19 @@
     </row>
     <row r="38" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="33" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="B38" s="33" t="s">
-        <v>1106</v>
+        <v>1078</v>
       </c>
       <c r="C38" s="33" t="s">
-        <v>1065</v>
+        <v>1037</v>
       </c>
       <c r="D38" s="42" t="n">
         <v>1</v>
       </c>
       <c r="E38" s="39" t="n">
-        <f aca="false">配件与耗材!K27</f>
+        <f aca="false">配件与耗材!K26</f>
         <v>3.42</v>
       </c>
       <c r="F38" s="40" t="n">
@@ -21264,7 +20909,7 @@
         <v>3.42</v>
       </c>
       <c r="G38" s="33" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="H38" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=736162720327","打开订单商品")</f>
@@ -21273,120 +20918,36 @@
     </row>
     <row r="39" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="33" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="B39" s="33" t="s">
-        <v>1107</v>
+        <v>1079</v>
       </c>
       <c r="C39" s="33" t="s">
-        <v>1065</v>
+        <v>1037</v>
       </c>
       <c r="D39" s="42" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E39" s="39" t="n">
-        <f aca="false">配件与耗材!K28</f>
-        <v>0.01</v>
+        <f aca="false">配件与耗材!K27</f>
+        <v>0.99</v>
       </c>
       <c r="F39" s="40" t="n">
         <f aca="false">D39*E39</f>
-        <v>0.1</v>
+        <v>0.99</v>
       </c>
       <c r="G39" s="33" t="s">
-        <v>1108</v>
+        <v>678</v>
       </c>
       <c r="H39" s="41" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=701774753211","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="33" t="s">
-        <v>685</v>
-      </c>
-      <c r="B40" s="33" t="s">
-        <v>1109</v>
-      </c>
-      <c r="C40" s="33" t="s">
-        <v>1065</v>
-      </c>
-      <c r="D40" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" s="39" t="n">
-        <f aca="false">配件与耗材!K29</f>
-        <v>0.02</v>
-      </c>
-      <c r="F40" s="40" t="n">
-        <f aca="false">D40*E40</f>
-        <v>0.2</v>
-      </c>
-      <c r="G40" s="33" t="s">
-        <v>1110</v>
-      </c>
-      <c r="H40" s="41" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=701774753211","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="33" t="s">
-        <v>690</v>
-      </c>
-      <c r="B41" s="33" t="s">
-        <v>1111</v>
-      </c>
-      <c r="C41" s="33" t="s">
-        <v>1065</v>
-      </c>
-      <c r="D41" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" s="39" t="n">
-        <f aca="false">配件与耗材!K30</f>
-        <v>0.03</v>
-      </c>
-      <c r="F41" s="40" t="n">
-        <f aca="false">D41*E41</f>
-        <v>0.3</v>
-      </c>
-      <c r="G41" s="33" t="s">
-        <v>1112</v>
-      </c>
-      <c r="H41" s="41" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=701774753211","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="33" t="s">
-        <v>696</v>
-      </c>
-      <c r="B42" s="33" t="s">
-        <v>1113</v>
-      </c>
-      <c r="C42" s="33" t="s">
-        <v>1065</v>
-      </c>
-      <c r="D42" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="39" t="n">
-        <f aca="false">配件与耗材!K31</f>
-        <v>0.99</v>
-      </c>
-      <c r="F42" s="40" t="n">
-        <f aca="false">D42*E42</f>
-        <v>0.99</v>
-      </c>
-      <c r="G42" s="33" t="s">
-        <v>701</v>
-      </c>
-      <c r="H42" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=945215173380","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
     </row>
+    <row r="40" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="42" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>

--- a/hardware/Microduck-HAT-IMU-Shopping-List-20261013.xlsx
+++ b/hardware/Microduck-HAT-IMU-Shopping-List-20261013.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2470" uniqueCount="1082">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2406" uniqueCount="1050">
   <si>
     <t xml:space="preserve">Microduck 鸭子用料与制作工具采购清单</t>
   </si>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">鸭子本体用料</t>
   </si>
   <si>
-    <t xml:space="preserve">鸭子本体配套材料：HAT/IMU接口使用EH，飞特舵机使用AMP2.0。PCB原器件表不动，工具见独立工作表。</t>
+    <t xml:space="preserve">鸭子本体配套材料：HAT/IMU接口使用EH，飞特舵机使用AMP2.0成品线（10cm、20cm）。PCB原器件表不动，工具见独立工作表。</t>
   </si>
   <si>
     <t xml:space="preserve">舵机为HD-1910-C001，整机15只；电池按NP-F550的2电＋标准双充套装选购。</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">EH2.5MM 端子（100个）</t>
   </si>
   <si>
-    <t xml:space="preserve">与 EH 母壳成套；不用 AMP2.0 端子替代。</t>
+    <t xml:space="preserve">与EH母壳成套使用，按EH2.5MM端子款式购买。</t>
   </si>
   <si>
     <t xml:space="preserve">信号线</t>
@@ -1946,72 +1946,6 @@
     <t xml:space="preserve">与20cm线是不同长度选项，数量按实际线束方案准备。</t>
   </si>
   <si>
-    <t xml:space="preserve">AMP接插件</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMP2.0 3P 胶壳</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179228-3 / 3P / 2.0mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">按自制线束准备；原订单50个</t>
-  </si>
-  <si>
-    <t xml:space="preserve">智基电子</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3P胶壳(179228-3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">每个3P胶壳配3个AMP端子；原订单数量50是购入个数。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMP2.0 镀锡端子</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMP/TE2.0 配套端子 / 100个</t>
-  </si>
-  <si>
-    <t xml:space="preserve">按自制线束准备</t>
-  </si>
-  <si>
-    <t xml:space="preserve">镀锡端子100个</t>
-  </si>
-  <si>
-    <t xml:space="preserve">与179228-3胶壳成套使用。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMP2.0 3P 直插板座</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A2007WV-3P / 2.0mm / 直插</t>
-  </si>
-  <si>
-    <t xml:space="preserve">制作对应AMP转接接口时选用</t>
-  </si>
-  <si>
-    <t xml:space="preserve">深圳市加特信科技</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A2007WV-3P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">直插版本，按A2007WV-3P完整型号选购。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMP2.0 3P 弯插板座</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A2007WR-3P / 2.0mm / 弯插</t>
-  </si>
-  <si>
-    <t xml:space="preserve">按商品完整型号购买：AMP2.0 3P 弯插板座</t>
-  </si>
-  <si>
-    <t xml:space="preserve">弯插版本，按A2007WR-3P完整型号选购。</t>
-  </si>
-  <si>
     <t xml:space="preserve">线材</t>
   </si>
   <si>
@@ -2180,7 +2114,7 @@
     <t xml:space="preserve">相关订单匹配依据</t>
   </si>
   <si>
-    <t xml:space="preserve">源：订单数据.xlsx；仅保留本次采购相关的107条商品记录。</t>
+    <t xml:space="preserve">源：订单数据.xlsx；仅保留本次采购相关的103条商品记录。</t>
   </si>
   <si>
     <t xml:space="preserve">数量是订单拍数，不一定等于器件个数。每拍包装数量由商品款式单独解析。</t>
@@ -2228,220 +2162,211 @@
     <t xml:space="preserve">其他接口体系，按对应连接方案使用</t>
   </si>
   <si>
-    <t xml:space="preserve">A2007WV-3P/4P/5P/6P CJT/长江连接器原装 2.0mm 直插针座连接器</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A2007WR-3P CJT/长江连接器AMP2.0mm间距弯插 线对板 针座连接器</t>
+    <t xml:space="preserve">交易成功</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54MM间距 双排贴片排母 2*3/4/5/6/8/10/15/20/40P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2*20P=5只</t>
+  </si>
+  <si>
+    <t xml:space="preserve">凯特森工具</t>
+  </si>
+  <si>
+    <t xml:space="preserve">精密清洗套装纳米清洁海绵高效吸附洗板水手机主板芯片维修强去污</t>
+  </si>
+  <si>
+    <t xml:space="preserve">海绵清洗剂实惠组合</t>
+  </si>
+  <si>
+    <t xml:space="preserve">洗板清洁套装</t>
+  </si>
+  <si>
+    <t xml:space="preserve">安立信旗舰店</t>
+  </si>
+  <si>
+    <t xml:space="preserve">安立信锡浆贴片焊接锡膏手机维修环保无铅高中低温焊锡膏针筒锡泥</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183℃中温有铅锡膏30G/支(常用款)  【送推杆/针头】</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183℃ 有铅锡膏针筒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMP2.0间距2.0 179228 电池端子线 端子连接线 电子线 镍片端子线</t>
+  </si>
+  <si>
+    <t xml:space="preserve">亚润五金专营店</t>
+  </si>
+  <si>
+    <t xml:space="preserve">白光BK701D热风枪焊台二合一锡焊电烙铁数显恒温风枪可调温拆焊台</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SBK701D旋钮款（气泵式/收藏送2支烙铁头）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">热风枪焊台</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0603/1608贴片电容 1u1.5u2.2u3.3u4.7u6.8u10u15u22u33u47uF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0603 0805 1206贴片电阻 10R 100R 1K 2K 4.7K 10K 100K 1M 欧 1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22R/22欧;0603 1%（100个）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH1之前调试的22Ω电阻订单，当前采购采用原村田PTC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">无铅环保吸锡带焊盘清洁维修残留除锡渣吸锡线PCB电路板手机主板</t>
+  </si>
+  <si>
+    <t xml:space="preserve">原装吸锡〖宽1.5mm长1.5米〗[X-100型1515]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">吸锡带</t>
+  </si>
+  <si>
+    <t xml:space="preserve">信容芯 SH1.0转杜邦公/杜邦母2P3P4P5P6P7P8P9P10P 28AWG渡锡铜线</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC0603KRX5R9BB105, CL10A105KB8NNNC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0603/1608贴片电容 100n120n150n180n220n270nF 104 154 224 274K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC0603KRX7R9BB104, CL10B104JB8NNNC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EH2.5MM直针插座 弯针 胶壳 间距2.54MM接插件 2P 3P 4P 5P 6P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VL53L5X V2 TOF宽视场飞行时间多区域激光测距传感器模块VL53L5CX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SI2300 2301 2302 2303 2304 2305 2306 2307 2308 2312DS 2309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全新原装BAT54SW BAT54S SOT-323 丝印44t 肖特基贴片三极管 20只</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTC热敏电阻 0603 100R 47R 33R 220R 470R 过电流热保护RPG18BB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH1原村田PRG18BB101MB1RB，100Ω PTC；当前采购款式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0402 0603 0805 1206 1210贴片电容22UF 226K 226P X5R 10% 50V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">瑞莎 Radxa 迷你主板 ZERO 3W RK3566 四核CPU WiFi6 Microduck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3525腔体-4Ω3W/8Ω2W BOX蓝牙音响扬声器安防喇叭 带1.25端子</t>
+  </si>
+  <si>
+    <t xml:space="preserve">阔筹旗舰店</t>
+  </si>
+  <si>
+    <t xml:space="preserve">防静电润轴镊子机械键盘短接镊子尖头弯头圆头精密电子元器件焊接</t>
+  </si>
+  <si>
+    <t xml:space="preserve">防静电ESD-10【短尖头】</t>
+  </si>
+  <si>
+    <t xml:space="preserve">防静电镊子</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中山市宝工电子有限公司</t>
+  </si>
+  <si>
+    <t xml:space="preserve">厂家直销 有铅锡膏 6337锡膏 SMT贴片锡浆 LED锡膏 焊锡膏183℃</t>
+  </si>
+  <si>
+    <t xml:space="preserve">手机维修焊锡膏50g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183℃ 有铅锡膏</t>
+  </si>
+  <si>
+    <t xml:space="preserve">皓越科技smt激光钢网</t>
+  </si>
+  <si>
+    <t xml:space="preserve">手帖打样SMT钢网精密制造PCB模板贴片锡膏红胶LED钢网小钢片</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10*10cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">定制贴片钢网</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XC6206P182MR 丝印65K5 SOT-23 1.8V 300MA 贴片稳压芯片 (20个)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMBT3904 1AM  MMBT3906 2A SOT-23贴片晶体功率三极管NPN PNP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOD-323稳压管BZT52C5V1S 2.4V3.3V4.7V5.1V10V12V15V24V30V33V47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0603 10NF 50V 100V 250V 10% 103K X7R材质 1608贴片陶瓷电容</t>
+  </si>
+  <si>
+    <t xml:space="preserve">贴片磁珠 0402 0603 0805 1206 0R/30R/60R/100R/600R/1K 全系列</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一体成型贴片功率电感0420/0520/0630/0650/1040/1265/1770/0850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全新SN74LVC1G14 17 08 04 02 07 00 32 66 125 126DBVR SOT23-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMD322550327050有源晶振4M8M12M16M20M24M25M27M30M32M40M50M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">原装正品 PAM8406DR 封装SOP16 音频放大器芯片</t>
+  </si>
+  <si>
+    <t xml:space="preserve">深圳优盛电子科技</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100只包邮贴片电容0402 0603 0805 1206 1210 100NF 104K 1UF-106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10UF (106) 精度10%;0603=100个;10V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150R/150欧;0603 1%（100个）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">旧 HAT R33 的150Ω电阻，当前采购用0Ω</t>
+  </si>
+  <si>
+    <t xml:space="preserve">原装正品 LM5050MKX-1/NOPB SOT-23-6 OR-ing FET控制器芯片</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SH1.0mm间距立贴/卧贴2P3P4P5P6P7P8P9P10P12P贴片式插头转接头</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54MM 单排母 双排母 SMT贴片双排母 2/3/4/5/6/7/8/9/10/20-40P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2718/3722/3729上进音降噪硅mini麦克风贴片SMD咪头模拟信号 MEMS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0603贴片高频电容 220p240p270p300p330p360p390p430pF NPO/COG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全新原装 TLV320AIC3104IRHBR 丝印AC3104I VQFN-32 解码器芯片</t>
   </si>
   <si>
     <t xml:space="preserve">暂无</t>
-  </si>
-  <si>
-    <t xml:space="preserve">交易成功</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54MM间距 双排贴片排母 2*3/4/5/6/8/10/15/20/40P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2*20P=5只</t>
-  </si>
-  <si>
-    <t xml:space="preserve">凯特森工具</t>
-  </si>
-  <si>
-    <t xml:space="preserve">精密清洗套装纳米清洁海绵高效吸附洗板水手机主板芯片维修强去污</t>
-  </si>
-  <si>
-    <t xml:space="preserve">海绵清洗剂实惠组合</t>
-  </si>
-  <si>
-    <t xml:space="preserve">洗板清洁套装</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMP/TE2.0国产现货179228-2 179228-3 179228-4 A2007H-4P AMP2.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">安立信旗舰店</t>
-  </si>
-  <si>
-    <t xml:space="preserve">安立信锡浆贴片焊接锡膏手机维修环保无铅高中低温焊锡膏针筒锡泥</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183℃中温有铅锡膏30G/支(常用款)  【送推杆/针头】</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183℃ 有铅锡膏针筒</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMP2.0间距2.0 179228 电池端子线 端子连接线 电子线 镍片端子线</t>
-  </si>
-  <si>
-    <t xml:space="preserve">亚润五金专营店</t>
-  </si>
-  <si>
-    <t xml:space="preserve">白光BK701D热风枪焊台二合一锡焊电烙铁数显恒温风枪可调温拆焊台</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SBK701D旋钮款（气泵式/收藏送2支烙铁头）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">热风枪焊台</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0603/1608贴片电容 1u1.5u2.2u3.3u4.7u6.8u10u15u22u33u47uF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0603 0805 1206贴片电阻 10R 100R 1K 2K 4.7K 10K 100K 1M 欧 1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22R/22欧;0603 1%（100个）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TH1之前调试的22Ω电阻订单，当前采购采用原村田PTC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">无铅环保吸锡带焊盘清洁维修残留除锡渣吸锡线PCB电路板手机主板</t>
-  </si>
-  <si>
-    <t xml:space="preserve">原装吸锡〖宽1.5mm长1.5米〗[X-100型1515]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">吸锡带</t>
-  </si>
-  <si>
-    <t xml:space="preserve">信容芯 SH1.0转杜邦公/杜邦母2P3P4P5P6P7P8P9P10P 28AWG渡锡铜线</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CC0603KRX5R9BB105, CL10A105KB8NNNC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0603/1608贴片电容 100n120n150n180n220n270nF 104 154 224 274K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CC0603KRX7R9BB104, CL10B104JB8NNNC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EH2.5MM直针插座 弯针 胶壳 间距2.54MM接插件 2P 3P 4P 5P 6P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VL53L5X V2 TOF宽视场飞行时间多区域激光测距传感器模块VL53L5CX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SI2300 2301 2302 2303 2304 2305 2306 2307 2308 2312DS 2309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">全新原装BAT54SW BAT54S SOT-323 丝印44t 肖特基贴片三极管 20只</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTC热敏电阻 0603 100R 47R 33R 220R 470R 过电流热保护RPG18BB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TH1原村田PRG18BB101MB1RB，100Ω PTC；当前采购款式</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0402 0603 0805 1206 1210贴片电容22UF 226K 226P X5R 10% 50V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">瑞莎 Radxa 迷你主板 ZERO 3W RK3566 四核CPU WiFi6 Microduck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3525腔体-4Ω3W/8Ω2W BOX蓝牙音响扬声器安防喇叭 带1.25端子</t>
-  </si>
-  <si>
-    <t xml:space="preserve">阔筹旗舰店</t>
-  </si>
-  <si>
-    <t xml:space="preserve">防静电润轴镊子机械键盘短接镊子尖头弯头圆头精密电子元器件焊接</t>
-  </si>
-  <si>
-    <t xml:space="preserve">防静电ESD-10【短尖头】</t>
-  </si>
-  <si>
-    <t xml:space="preserve">防静电镊子</t>
-  </si>
-  <si>
-    <t xml:space="preserve">中山市宝工电子有限公司</t>
-  </si>
-  <si>
-    <t xml:space="preserve">厂家直销 有铅锡膏 6337锡膏 SMT贴片锡浆 LED锡膏 焊锡膏183℃</t>
-  </si>
-  <si>
-    <t xml:space="preserve">手机维修焊锡膏50g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183℃ 有铅锡膏</t>
-  </si>
-  <si>
-    <t xml:space="preserve">皓越科技smt激光钢网</t>
-  </si>
-  <si>
-    <t xml:space="preserve">手帖打样SMT钢网精密制造PCB模板贴片锡膏红胶LED钢网小钢片</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10*10cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">定制贴片钢网</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XC6206P182MR 丝印65K5 SOT-23 1.8V 300MA 贴片稳压芯片 (20个)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MMBT3904 1AM  MMBT3906 2A SOT-23贴片晶体功率三极管NPN PNP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOD-323稳压管BZT52C5V1S 2.4V3.3V4.7V5.1V10V12V15V24V30V33V47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0603 10NF 50V 100V 250V 10% 103K X7R材质 1608贴片陶瓷电容</t>
-  </si>
-  <si>
-    <t xml:space="preserve">贴片磁珠 0402 0603 0805 1206 0R/30R/60R/100R/600R/1K 全系列</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一体成型贴片功率电感0420/0520/0630/0650/1040/1265/1770/0850</t>
-  </si>
-  <si>
-    <t xml:space="preserve">全新SN74LVC1G14 17 08 04 02 07 00 32 66 125 126DBVR SOT23-5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMD322550327050有源晶振4M8M12M16M20M24M25M27M30M32M40M50M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">原装正品 PAM8406DR 封装SOP16 音频放大器芯片</t>
-  </si>
-  <si>
-    <t xml:space="preserve">深圳优盛电子科技</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100只包邮贴片电容0402 0603 0805 1206 1210 100NF 104K 1UF-106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10UF (106) 精度10%;0603=100个;10V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150R/150欧;0603 1%（100个）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">旧 HAT R33 的150Ω电阻，当前采购用0Ω</t>
-  </si>
-  <si>
-    <t xml:space="preserve">原装正品 LM5050MKX-1/NOPB SOT-23-6 OR-ing FET控制器芯片</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SH1.0mm间距立贴/卧贴2P3P4P5P6P7P8P9P10P12P贴片式插头转接头</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54MM 单排母 双排母 SMT贴片双排母 2/3/4/5/6/7/8/9/10/20-40P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2718/3722/3729上进音降噪硅mini麦克风贴片SMD咪头模拟信号 MEMS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0603贴片高频电容 220p240p270p300p330p360p390p430pF NPO/COG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">全新原装 TLV320AIC3104IRHBR 丝印AC3104I VQFN-32 解码器芯片</t>
   </si>
   <si>
     <t xml:space="preserve">深圳市豪芯微电子 只做原装</t>
@@ -3139,7 +3064,7 @@
     <t xml:space="preserve">首次整包整批采购：PCB无券</t>
   </si>
   <si>
-    <t xml:space="preserve">HAT/IMU接口使用EH，舵机线束为AMP2.0。数量含备料，螺丝按整包；M2×5原订单为0元优惠价。TF卡等未提供价格的项目未计入。</t>
+    <t xml:space="preserve">HAT/IMU接口使用EH，舵机使用AMP2.0成品线（10cm、20cm）。数量含备料，螺丝按整包；M2×5原订单为0元优惠价。TF卡等未提供价格的项目未计入。</t>
   </si>
   <si>
     <t xml:space="preserve">商品 / 模块</t>
@@ -3281,27 +3206,6 @@
   </si>
   <si>
     <t xml:space="preserve">按订单参考采购数量计入，包含备料；与20cm线是不同长度选项，数量按实际线束方案准备。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3P胶壳(179228-3)；179228-3 / 3P / 2.0mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">按订单参考采购数量计入，包含备料；每个3P胶壳配3个AMP端子；原订单数量50是购入个数。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">镀锡端子100个；AMP/TE2.0 配套端子 / 100个</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A2007WV-3P；A2007WV-3P / 2.0mm / 直插</t>
-  </si>
-  <si>
-    <t xml:space="preserve">按订单参考采购数量计入，包含备料；直插版本，按A2007WV-3P完整型号选购。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">按商品完整型号购买：AMP2.0 3P 弯插板座；A2007WR-3P / 2.0mm / 弯插</t>
-  </si>
-  <si>
-    <t xml:space="preserve">按订单参考采购数量计入，包含备料；弯插版本，按A2007WR-3P完整型号选购。</t>
   </si>
   <si>
     <t xml:space="preserve">黑色;3芯;22AWG;1m；黑色 / 3芯 / 22AWG / 1m</t>
@@ -3323,7 +3227,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="16">
+  <numFmts count="17">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
@@ -3339,7 +3243,8 @@
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="0.00"/>
     <numFmt numFmtId="178" formatCode="\¥0.000000"/>
-    <numFmt numFmtId="179" formatCode="\¥0.0000"/>
+    <numFmt numFmtId="179" formatCode="\¥0.00"/>
+    <numFmt numFmtId="180" formatCode="\¥0.0000"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -3594,7 +3499,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="39">
+  <cellStyleXfs count="45">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3621,13 +3526,17 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="171" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -3646,6 +3555,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
@@ -3655,180 +3569,180 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="7" fillId="2" borderId="0" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="174" fontId="7" fillId="2" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="3" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="3" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="7" fillId="0" borderId="0" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="174" fontId="7" fillId="0" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="4" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="4" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="2" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="2" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="3" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="3" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="175" fontId="6" fillId="0" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="14" fillId="0" borderId="0" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="175" fontId="14" fillId="0" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="0" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="10" fillId="4" borderId="0" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="175" fontId="10" fillId="4" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="6" borderId="0" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="17" fillId="6" borderId="0" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="175" fontId="17" fillId="6" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="16" fillId="0" borderId="0" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="175" fontId="16" fillId="0" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="0" xfId="33" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="178" fontId="14" fillId="0" borderId="0" xfId="37" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="34" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="38" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="34" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="38" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="6" borderId="0" xfId="34" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="0" xfId="38" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="20" fillId="6" borderId="0" xfId="34" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="175" fontId="20" fillId="6" borderId="0" xfId="38" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="4" borderId="0" xfId="34" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="4" borderId="0" xfId="38" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="34" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="38" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="22" fillId="0" borderId="0" xfId="35" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="179" fontId="22" fillId="0" borderId="0" xfId="36" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="18" fillId="0" borderId="0" xfId="35" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="179" fontId="18" fillId="0" borderId="0" xfId="36" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="34" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="38" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="5" borderId="0" xfId="34" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="23" fillId="5" borderId="0" xfId="38" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="179" fontId="22" fillId="0" borderId="0" xfId="35" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="180" fontId="22" fillId="0" borderId="0" xfId="36" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="25">
+  <cellStyles count="31">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
@@ -3838,22 +3752,28 @@
     <cellStyle name="Comma" xfId="20"/>
     <cellStyle name="Comma 1" xfId="21"/>
     <cellStyle name="Comma 2" xfId="22"/>
-    <cellStyle name="Comma [0]" xfId="23"/>
-    <cellStyle name="Comma [0] 2" xfId="24"/>
-    <cellStyle name="Comma [0] 3" xfId="25"/>
-    <cellStyle name="Currency" xfId="26"/>
-    <cellStyle name="Currency 3" xfId="27"/>
-    <cellStyle name="Currency 4" xfId="28"/>
-    <cellStyle name="Currency [0]" xfId="29"/>
-    <cellStyle name="Currency [0] 4" xfId="30"/>
-    <cellStyle name="Currency [0] 5" xfId="31"/>
-    <cellStyle name="Normal" xfId="32"/>
-    <cellStyle name="Normal 1" xfId="33"/>
-    <cellStyle name="Normal 5" xfId="34"/>
-    <cellStyle name="Normal 6" xfId="35"/>
-    <cellStyle name="Percent" xfId="36"/>
-    <cellStyle name="Percent 6" xfId="37"/>
-    <cellStyle name="Percent 7" xfId="38"/>
+    <cellStyle name="Comma 3" xfId="23"/>
+    <cellStyle name="Comma [0]" xfId="24"/>
+    <cellStyle name="Comma [0] 2" xfId="25"/>
+    <cellStyle name="Comma [0] 3" xfId="26"/>
+    <cellStyle name="Comma [0] 4" xfId="27"/>
+    <cellStyle name="Currency" xfId="28"/>
+    <cellStyle name="Currency 3" xfId="29"/>
+    <cellStyle name="Currency 4" xfId="30"/>
+    <cellStyle name="Currency 5" xfId="31"/>
+    <cellStyle name="Currency [0]" xfId="32"/>
+    <cellStyle name="Currency [0] 4" xfId="33"/>
+    <cellStyle name="Currency [0] 5" xfId="34"/>
+    <cellStyle name="Currency [0] 6" xfId="35"/>
+    <cellStyle name="Normal" xfId="36"/>
+    <cellStyle name="Normal 1" xfId="37"/>
+    <cellStyle name="Normal 5" xfId="38"/>
+    <cellStyle name="Normal 6" xfId="39"/>
+    <cellStyle name="Normal 7" xfId="40"/>
+    <cellStyle name="Percent" xfId="41"/>
+    <cellStyle name="Percent 6" xfId="42"/>
+    <cellStyle name="Percent 7" xfId="43"/>
+    <cellStyle name="Percent 8" xfId="44"/>
   </cellStyles>
   <dxfs count="16">
     <dxf>
@@ -4119,8 +4039,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DuckAccessories" displayName="DuckAccessories" ref="A6:K35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A6:K35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DuckAccessories" displayName="DuckAccessories" ref="A6:K31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A6:K31"/>
   <tableColumns count="11">
     <tableColumn id="1" name="类别"/>
     <tableColumn id="2" name="商品 / 用品"/>
@@ -4139,8 +4059,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="DuckTotalItems" displayName="DuckTotalItems" ref="A10:H39" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A10:H39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="DuckTotalItems" displayName="DuckTotalItems" ref="A10:H35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A10:H35"/>
   <tableColumns count="8">
     <tableColumn id="1" name="商品 / 模块"/>
     <tableColumn id="2" name="型号 / 指定款式"/>
@@ -4196,8 +4116,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="OrderEvidence" displayName="OrderEvidence" ref="A6:J113" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A6:J113"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="OrderEvidence" displayName="OrderEvidence" ref="A6:J109" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A6:J109"/>
   <tableColumns count="10">
     <tableColumn id="1" name="订单源行"/>
     <tableColumn id="2" name="提交日期"/>
@@ -11897,7 +11817,7 @@
         <v>643</v>
       </c>
       <c r="F21" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=891600917698","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=781764816472","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G21" s="8" t="s">
@@ -11910,10 +11830,10 @@
         <v>645</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K21" s="18" t="n">
-        <v>0.04</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11930,211 +11850,211 @@
         <v>648</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="F22" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=891600917698","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=736162720327","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K22" s="18" t="n">
-        <v>2.68</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>639</v>
+        <v>652</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="F23" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=598425041338","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=945215173380","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="H23" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="K23" s="18" t="n">
-        <v>0.3</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>639</v>
+        <v>659</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>653</v>
+        <v>662</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>654</v>
+        <v>663</v>
       </c>
       <c r="F24" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=595594145847","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=625390659071","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="H24" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>0.27</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="C25" s="8" t="s">
+        <v>667</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>668</v>
+      </c>
+      <c r="E25" s="8" t="s">
         <v>663</v>
       </c>
-      <c r="D25" s="8" t="s">
-        <v>664</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>665</v>
-      </c>
       <c r="F25" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=781764816472","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=733598659967","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="H25" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>29</v>
+        <v>112</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>3.63</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>661</v>
+        <v>671</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="F26" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=736162720327","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>3.42</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>678</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>674</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="E27" s="8" t="s">
         <v>675</v>
       </c>
-      <c r="C27" s="8" t="s">
-        <v>676</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>677</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>678</v>
-      </c>
       <c r="F27" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=945215173380","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>682</v>
@@ -12143,283 +12063,143 @@
         <v>683</v>
       </c>
       <c r="D28" s="8" t="s">
+        <v>674</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="F28" s="17" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+      <c r="G28" s="8" t="s">
         <v>684</v>
       </c>
-      <c r="E28" s="8" t="s">
-        <v>685</v>
-      </c>
-      <c r="F28" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=625390659071","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>686</v>
-      </c>
       <c r="H28" s="1" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="K28" s="18" t="n">
-        <v>1.94</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>690</v>
+        <v>674</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="F29" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=733598659967","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>692</v>
+        <v>677</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="K29" s="18" t="n">
-        <v>2.91</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>693</v>
+        <v>671</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>696</v>
+        <v>674</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>697</v>
+        <v>675</v>
       </c>
       <c r="F30" s="17" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="H30" s="1" t="n">
         <v>200</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>699</v>
+        <v>677</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K30" s="18" t="n">
-        <v>3.03</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>693</v>
+        <v>671</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>700</v>
+        <v>691</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>701</v>
+        <v>692</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>696</v>
+        <v>674</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>697</v>
+        <v>675</v>
       </c>
       <c r="F31" s="17" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>702</v>
+        <v>693</v>
       </c>
       <c r="H31" s="1" t="n">
         <v>200</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>703</v>
+        <v>677</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="K31" s="18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="s">
-        <v>693</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>704</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>705</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>696</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>697</v>
-      </c>
-      <c r="F32" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>706</v>
-      </c>
-      <c r="H32" s="1" t="n">
-        <v>200</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>699</v>
-      </c>
-      <c r="J32" s="8" t="n">
-        <v>87</v>
-      </c>
-      <c r="K32" s="18" t="n">
-        <v>3.31</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8" t="s">
-        <v>693</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>707</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>708</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>696</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>697</v>
-      </c>
-      <c r="F33" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>709</v>
-      </c>
-      <c r="H33" s="1" t="n">
-        <v>200</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>699</v>
-      </c>
-      <c r="J33" s="8" t="n">
-        <v>86</v>
-      </c>
-      <c r="K33" s="18" t="n">
         <v>3.59</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8" t="s">
-        <v>693</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>710</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>711</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>696</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>697</v>
-      </c>
-      <c r="F34" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>712</v>
-      </c>
-      <c r="H34" s="1" t="n">
-        <v>200</v>
-      </c>
-      <c r="I34" s="8" t="s">
-        <v>699</v>
-      </c>
-      <c r="J34" s="8" t="n">
-        <v>85</v>
-      </c>
-      <c r="K34" s="18" t="n">
-        <v>3.88</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="8" t="s">
-        <v>693</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>713</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>714</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>696</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>697</v>
-      </c>
-      <c r="F35" s="17" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>715</v>
-      </c>
-      <c r="H35" s="1" t="n">
-        <v>200</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>699</v>
-      </c>
-      <c r="J35" s="8" t="n">
-        <v>89</v>
-      </c>
-      <c r="K35" s="18" t="n">
-        <v>3.59</v>
-      </c>
-    </row>
+    <row r="32" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="34" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="35" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="36" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="37" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="38" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -12475,7 +12255,7 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>716</v>
+        <v>694</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -12489,7 +12269,7 @@
     </row>
     <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>717</v>
+        <v>695</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -12503,7 +12283,7 @@
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>718</v>
+        <v>696</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -12517,7 +12297,7 @@
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>719</v>
+        <v>697</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -12534,31 +12314,31 @@
         <v>555</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>720</v>
+        <v>698</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>721</v>
+        <v>699</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>722</v>
+        <v>700</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>723</v>
+        <v>701</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>724</v>
+        <v>702</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>725</v>
+        <v>703</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>726</v>
+        <v>704</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>552</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>727</v>
+        <v>705</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12569,13 +12349,13 @@
         <v>46306</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>728</v>
+        <v>706</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>264</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>729</v>
+        <v>707</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>262</v>
@@ -12591,7 +12371,7 @@
         <v>打开商品</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>730</v>
+        <v>708</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12602,13 +12382,13 @@
         <v>46305</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>728</v>
+        <v>706</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>632</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>731</v>
+        <v>709</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>633</v>
@@ -12624,3474 +12404,3346 @@
         <v>打开商品</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>732</v>
+        <v>710</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B9" s="19" t="n">
-        <v>46297</v>
+        <v>46293</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>728</v>
+        <v>711</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>654</v>
+        <v>239</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>733</v>
+        <v>712</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>655</v>
+        <v>713</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H9" s="20" t="n">
-        <v>0.3</v>
+        <v>9.1</v>
       </c>
       <c r="I9" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=598425041338","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=606745016341","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>732</v>
+        <v>708</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B10" s="19" t="n">
-        <v>46297</v>
+        <v>46293</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>728</v>
+        <v>711</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>654</v>
+        <v>714</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>734</v>
+        <v>715</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>735</v>
+        <v>716</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H10" s="20" t="n">
-        <v>0.27</v>
+        <v>14.16</v>
       </c>
       <c r="I10" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=595594145847","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1049340097483","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>732</v>
+        <v>717</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B11" s="19" t="n">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>239</v>
+        <v>718</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>737</v>
+        <v>719</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>738</v>
+        <v>720</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="20" t="n">
-        <v>9.1</v>
+        <v>13.8</v>
       </c>
       <c r="I11" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=606745016341","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=626569273184","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>730</v>
+        <v>721</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B12" s="19" t="n">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>739</v>
+        <v>632</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>740</v>
+        <v>722</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>741</v>
+        <v>637</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H12" s="20" t="n">
-        <v>14.16</v>
+        <v>0.9</v>
       </c>
       <c r="I12" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1049340097483","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=825340808235","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>742</v>
+        <v>710</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B13" s="19" t="n">
-        <v>46291</v>
+        <v>46282</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>643</v>
+        <v>723</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>743</v>
+        <v>724</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>649</v>
+        <v>725</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="20" t="n">
-        <v>2.68</v>
+        <v>268</v>
       </c>
       <c r="I13" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=891600917698","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=566089419587","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B14" s="19" t="n">
-        <v>46291</v>
+        <v>46282</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>643</v>
+        <v>27</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>743</v>
+        <v>727</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>644</v>
+        <v>33</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>50</v>
       </c>
       <c r="H14" s="20" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="I14" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=891600917698","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=630712731066","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>732</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="B15" s="19" t="n">
-        <v>46290</v>
+        <v>46282</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>744</v>
+        <v>141</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>745</v>
+        <v>728</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>746</v>
+        <v>729</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="20" t="n">
-        <v>13.8</v>
+        <v>1.46</v>
       </c>
       <c r="I15" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=626569273184","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>747</v>
+        <v>730</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B16" s="19" t="n">
-        <v>46290</v>
+        <v>46282</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>632</v>
+        <v>141</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>748</v>
+        <v>728</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>637</v>
+        <v>142</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H16" s="20" t="n">
-        <v>0.9</v>
+        <v>1.42</v>
       </c>
       <c r="I16" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=825340808235","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>732</v>
+        <v>708</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B17" s="19" t="n">
         <v>46282</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>749</v>
+        <v>141</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>750</v>
+        <v>728</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>751</v>
+        <v>245</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="20" t="n">
-        <v>268</v>
+        <v>1.46</v>
       </c>
       <c r="I17" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=566089419587","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>752</v>
+        <v>242</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="B18" s="19" t="n">
-        <v>46282</v>
+        <v>46279</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D18" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>731</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>732</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="20" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="I18" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=972313702890","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="B19" s="19" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>588</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="20" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="I19" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=895049863252","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="8" t="s">
-        <v>753</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G18" s="9" t="n">
-        <v>50</v>
-      </c>
-      <c r="H18" s="20" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I18" s="10" t="str">
+      <c r="E20" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H20" s="20" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I20" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=630712731066","打开商品")</f>
         <v>打开商品</v>
       </c>
-      <c r="J18" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="B19" s="19" t="n">
-        <v>46282</v>
-      </c>
-      <c r="C19" s="8" t="s">
+      <c r="J20" s="8" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="8" t="s">
         <v>736</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="F21" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I21" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=731471380840","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B22" s="19" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D22" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="E19" s="8" t="s">
-        <v>754</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>755</v>
-      </c>
-      <c r="G19" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="I19" s="10" t="str">
+      <c r="E22" s="8" t="s">
+        <v>728</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I22" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
         <v>打开商品</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="J22" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="n">
+        <v>81</v>
+      </c>
+      <c r="B23" s="19" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I23" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=832569969546","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="B24" s="19" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>572</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I24" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=832569969546","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="n">
+        <v>83</v>
+      </c>
+      <c r="B25" s="19" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>582</v>
+      </c>
+      <c r="G25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I25" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=832569969546","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="G26" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="I26" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=640391703111","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B27" s="19" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>599</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>739</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>600</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="20" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="I27" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=737603917521","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="B28" s="19" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>740</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="G28" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=909264246006","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="B29" s="19" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I29" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=793455311175","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="B30" s="19" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>742</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H30" s="20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I30" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=582129955778","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B31" s="19" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>744</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I31" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=993202872551","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B32" s="19" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>745</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>607</v>
+      </c>
+      <c r="G32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="20" t="n">
+        <v>309</v>
+      </c>
+      <c r="I32" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=763812025816","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="B33" s="19" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>746</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>594</v>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="20" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="I33" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=683920556900","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B34" s="19" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>747</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>748</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>749</v>
+      </c>
+      <c r="G34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I34" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=979077591318","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="B35" s="19" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>751</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>752</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>753</v>
+      </c>
+      <c r="G35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="20" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="I35" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=19606507546","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="B36" s="19" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>755</v>
+      </c>
+      <c r="E36" s="8" t="s">
         <v>756</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
-        <v>53</v>
-      </c>
-      <c r="B20" s="19" t="n">
-        <v>46282</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D20" s="8" t="s">
+      <c r="F36" s="8" t="s">
+        <v>757</v>
+      </c>
+      <c r="G36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I36" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=851008959999","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B37" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I37" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=832569969546","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B38" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I38" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=832569969546","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B39" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>759</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="G39" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I39" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=762173333947","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="B40" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>760</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="G40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="20" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I40" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=944306254140","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="B41" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>761</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I41" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=943185002457","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B42" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>762</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G42" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=610558214623","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="B43" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G43" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I43" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=931081429973","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="B44" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G44" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I44" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=931081429973","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="B45" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>764</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="G45" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=598174251748","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B46" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>765</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="G46" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I46" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=902117985110","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="B47" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>765</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="G47" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I47" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=902117985110","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J47" s="8" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="B48" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>765</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="G48" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I48" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=902117985110","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="B49" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>766</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="G49" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H49" s="20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I49" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=944053669860","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J49" s="8" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B50" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>767</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="G50" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H50" s="20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="I50" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=808484505787","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="n">
+        <v>133</v>
+      </c>
+      <c r="B51" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>768</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>769</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>770</v>
+      </c>
+      <c r="G51" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I51" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=857961351344","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="n">
+        <v>134</v>
+      </c>
+      <c r="B52" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D52" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="E20" s="8" t="s">
-        <v>754</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="G20" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="I20" s="10" t="str">
+      <c r="E52" s="8" t="s">
+        <v>728</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="G52" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I52" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
         <v>打开商品</v>
       </c>
-      <c r="J20" s="8" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
-        <v>56</v>
-      </c>
-      <c r="B21" s="19" t="n">
-        <v>46282</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D21" s="8" t="s">
+      <c r="J52" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="B53" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D53" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="E21" s="8" t="s">
-        <v>754</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="G21" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="20" t="n">
+      <c r="E53" s="8" t="s">
+        <v>728</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="G53" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="20" t="n">
         <v>1.46</v>
       </c>
-      <c r="I21" s="10" t="str">
+      <c r="I53" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
         <v>打开商品</v>
       </c>
-      <c r="J21" s="8" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
-        <v>76</v>
-      </c>
-      <c r="B22" s="19" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>739</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="G22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="20" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="I22" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=972313702890","打开商品")</f>
+      <c r="J53" s="8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B54" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>728</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>771</v>
+      </c>
+      <c r="G54" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I54" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
         <v>打开商品</v>
       </c>
-      <c r="J22" s="8" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
-        <v>77</v>
-      </c>
-      <c r="B23" s="19" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D23" s="8" t="s">
+      <c r="J54" s="8" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B55" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>773</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="G55" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H55" s="20" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I55" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1013388982214","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="n">
+        <v>139</v>
+      </c>
+      <c r="B56" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D56" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="E23" s="8" t="s">
-        <v>760</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>588</v>
-      </c>
-      <c r="G23" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="20" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="I23" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=895049863252","打开商品")</f>
+      <c r="E56" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G56" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="20" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I56" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=920058690376","打开商品")</f>
         <v>打开商品</v>
       </c>
-      <c r="J23" s="8" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
-        <v>78</v>
-      </c>
-      <c r="B24" s="19" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D24" s="8" t="s">
+      <c r="J56" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B57" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>775</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="G57" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" s="20" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="I57" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=533725557959","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J57" s="8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="n">
+        <v>141</v>
+      </c>
+      <c r="B58" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>776</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="G58" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" s="20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I58" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=996702312391","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J58" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="B59" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D59" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E24" s="8" t="s">
-        <v>753</v>
-      </c>
-      <c r="F24" s="8" t="s">
+      <c r="E59" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G59" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" s="20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I59" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1005108810412","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J59" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="B60" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>778</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="G60" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H60" s="20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I60" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=908248360601","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J60" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B61" s="19" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>780</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>781</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="G61" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H61" s="20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I61" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=708737648760","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J61" s="8" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="B62" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="G62" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" s="20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I62" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=640391703111","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J62" s="8" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B63" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>782</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="G63" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I63" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1062189210190","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J63" s="8" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="B64" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>783</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="G64" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" s="20" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="I64" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1028742717053","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J64" s="8" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B65" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>784</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="G65" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H65" s="20" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="I65" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=726808419708","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J65" s="8" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="n">
+        <v>151</v>
+      </c>
+      <c r="B66" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>785</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>786</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>787</v>
+      </c>
+      <c r="G66" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" s="20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I66" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=602152415662","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J66" s="8" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B67" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>788</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="G67" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" s="20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="I67" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=606816197525","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J67" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="n">
+        <v>153</v>
+      </c>
+      <c r="B68" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>789</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="G68" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H68" s="20" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I68" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=977236759812","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J68" s="8" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="n">
+        <v>154</v>
+      </c>
+      <c r="B69" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>790</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>791</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>792</v>
+      </c>
+      <c r="G69" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" s="20" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="I69" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=581798084270","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J69" s="8" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="1" t="n">
+        <v>155</v>
+      </c>
+      <c r="B70" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>728</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="G70" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I70" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J70" s="8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="n">
+        <v>156</v>
+      </c>
+      <c r="B71" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>728</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="G71" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" s="20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I71" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J71" s="8" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="n">
+        <v>157</v>
+      </c>
+      <c r="B72" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>728</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="G72" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" s="20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I72" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J72" s="8" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="n">
+        <v>158</v>
+      </c>
+      <c r="B73" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>794</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="G73" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I73" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1025817117811","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J73" s="8" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="n">
+        <v>159</v>
+      </c>
+      <c r="B74" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>794</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>795</v>
+      </c>
+      <c r="G74" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I74" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1025817117811","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J74" s="8" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B75" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>796</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="G75" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="H75" s="20" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I75" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=891785167202","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J75" s="8" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="n">
+        <v>161</v>
+      </c>
+      <c r="B76" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>797</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="G76" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H76" s="20" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I76" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=705642638300","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J76" s="8" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="B77" s="19" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G77" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H77" s="20" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="I77" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=747094785928","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J77" s="8" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="n">
+        <v>178</v>
+      </c>
+      <c r="B78" s="19" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>783</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="G78" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" s="20" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="I78" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1027587805193","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J78" s="8" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="n">
+        <v>196</v>
+      </c>
+      <c r="B79" s="19" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="F79" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G24" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="H24" s="20" t="n">
+      <c r="G79" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="H79" s="20" t="n">
         <v>0.03</v>
       </c>
-      <c r="I24" s="10" t="str">
+      <c r="I79" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=630712731066","打开商品")</f>
         <v>打开商品</v>
       </c>
-      <c r="J24" s="8" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
-        <v>79</v>
-      </c>
-      <c r="B25" s="19" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C25" s="8" t="s">
+      <c r="J79" s="8" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1" t="n">
+        <v>203</v>
+      </c>
+      <c r="B80" s="19" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>799</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="G80" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H80" s="20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I80" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=969642590399","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J80" s="8" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="n">
+        <v>205</v>
+      </c>
+      <c r="B81" s="19" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E81" s="8" t="s">
         <v>736</v>
       </c>
-      <c r="D25" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>762</v>
-      </c>
-      <c r="F25" s="8" t="s">
+      <c r="F81" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G25" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="20" t="n">
+      <c r="G81" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="20" t="n">
         <v>1.98</v>
       </c>
-      <c r="I25" s="10" t="str">
+      <c r="I81" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=731471380840","打开商品")</f>
         <v>打开商品</v>
       </c>
-      <c r="J25" s="8" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="n">
-        <v>80</v>
-      </c>
-      <c r="B26" s="19" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D26" s="8" t="s">
+      <c r="J81" s="8" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="n">
+        <v>206</v>
+      </c>
+      <c r="B82" s="19" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>800</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G82" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H82" s="20" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I82" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=730407108775","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J82" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="n">
+        <v>209</v>
+      </c>
+      <c r="B83" s="19" t="n">
+        <v>46256</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>801</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>802</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>803</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="G83" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" s="20" t="n">
+        <v>169</v>
+      </c>
+      <c r="I83" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=956985590887","打开商品")</f>
+        <v>打开商品</v>
+      </c>
+      <c r="J83" s="8" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="n">
+        <v>213</v>
+      </c>
+      <c r="B84" s="19" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="D84" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="E26" s="8" t="s">
-        <v>754</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="G26" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="I26" s="10" t="str">
+      <c r="E84" s="8" t="s">
+        <v>728</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="G84" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" s="20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I84" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
         <v>打开商品</v>
       </c>
-      <c r="J26" s="8" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="n">
-        <v>81</v>
-      </c>
-      <c r="B27" s="19" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>764</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>577</v>
-      </c>
-      <c r="G27" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I27" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=832569969546","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="n">
-        <v>82</v>
-      </c>
-      <c r="B28" s="19" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>764</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>572</v>
-      </c>
-      <c r="G28" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I28" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=832569969546","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="n">
-        <v>83</v>
-      </c>
-      <c r="B29" s="19" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>764</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>582</v>
-      </c>
-      <c r="G29" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I29" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=832569969546","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="n">
-        <v>91</v>
-      </c>
-      <c r="B30" s="19" t="n">
-        <v>46276</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>729</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="G30" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H30" s="20" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="I30" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=640391703111","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="B31" s="19" t="n">
-        <v>46276</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>599</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>765</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>600</v>
-      </c>
-      <c r="G31" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="20" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="I31" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=737603917521","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="n">
-        <v>93</v>
-      </c>
-      <c r="B32" s="19" t="n">
-        <v>46276</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>766</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="G32" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="I32" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=909264246006","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="B33" s="19" t="n">
-        <v>46276</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>767</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="G33" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I33" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=793455311175","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="B34" s="19" t="n">
-        <v>46276</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>768</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="G34" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H34" s="20" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I34" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=582129955778","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="n">
-        <v>96</v>
-      </c>
-      <c r="B35" s="19" t="n">
-        <v>46276</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>770</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G35" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I35" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=993202872551","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="B36" s="19" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>606</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>771</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>607</v>
-      </c>
-      <c r="G36" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="20" t="n">
-        <v>309</v>
-      </c>
-      <c r="I36" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=763812025816","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="n">
-        <v>103</v>
-      </c>
-      <c r="B37" s="19" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>772</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>594</v>
-      </c>
-      <c r="G37" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" s="20" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="I37" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=683920556900","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J37" s="8" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="n">
-        <v>105</v>
-      </c>
-      <c r="B38" s="19" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>773</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>774</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>775</v>
-      </c>
-      <c r="G38" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="20" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="I38" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=979077591318","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J38" s="8" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="n">
-        <v>106</v>
-      </c>
-      <c r="B39" s="19" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>777</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>778</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>779</v>
-      </c>
-      <c r="G39" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="20" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I39" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=19606507546","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J39" s="8" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="n">
-        <v>107</v>
-      </c>
-      <c r="B40" s="19" t="n">
-        <v>46274</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>781</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>782</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>783</v>
-      </c>
-      <c r="G40" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="I40" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=851008959999","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J40" s="8" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="n">
-        <v>117</v>
-      </c>
-      <c r="B41" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>764</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="G41" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="I41" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=832569969546","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J41" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="n">
-        <v>118</v>
-      </c>
-      <c r="B42" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>764</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="G42" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" s="20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I42" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=832569969546","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J42" s="8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="n">
-        <v>119</v>
-      </c>
-      <c r="B43" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>785</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="G43" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I43" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=762173333947","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J43" s="8" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="n">
-        <v>121</v>
-      </c>
-      <c r="B44" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>786</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="G44" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="20" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="I44" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=944306254140","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J44" s="8" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="n">
-        <v>122</v>
-      </c>
-      <c r="B45" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>787</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="G45" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" s="20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="I45" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=943185002457","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J45" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="n">
-        <v>124</v>
-      </c>
-      <c r="B46" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>788</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G46" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I46" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=610558214623","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J46" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="n">
-        <v>125</v>
-      </c>
-      <c r="B47" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>789</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="G47" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="I47" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=931081429973","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J47" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="n">
-        <v>126</v>
-      </c>
-      <c r="B48" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>789</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="G48" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" s="20" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="I48" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=931081429973","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J48" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="n">
-        <v>127</v>
-      </c>
-      <c r="B49" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>790</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="G49" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I49" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=598174251748","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J49" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="n">
-        <v>128</v>
-      </c>
-      <c r="B50" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>791</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="G50" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" s="20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I50" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=902117985110","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J50" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="n">
-        <v>129</v>
-      </c>
-      <c r="B51" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>791</v>
-      </c>
-      <c r="F51" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="G51" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51" s="20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I51" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=902117985110","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J51" s="8" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="n">
-        <v>130</v>
-      </c>
-      <c r="B52" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>791</v>
-      </c>
-      <c r="F52" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="G52" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H52" s="20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I52" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=902117985110","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J52" s="8" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="n">
-        <v>131</v>
-      </c>
-      <c r="B53" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>792</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="G53" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H53" s="20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="I53" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=944053669860","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J53" s="8" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="n">
-        <v>132</v>
-      </c>
-      <c r="B54" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>793</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="G54" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H54" s="20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="I54" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=808484505787","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J54" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="n">
-        <v>133</v>
-      </c>
-      <c r="B55" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>794</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>795</v>
-      </c>
-      <c r="F55" s="8" t="s">
-        <v>796</v>
-      </c>
-      <c r="G55" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="I55" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=857961351344","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J55" s="8" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="n">
-        <v>134</v>
-      </c>
-      <c r="B56" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>754</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="G56" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H56" s="20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="I56" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J56" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="n">
-        <v>135</v>
-      </c>
-      <c r="B57" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>754</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="G57" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H57" s="20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="I57" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J57" s="8" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="n">
-        <v>136</v>
-      </c>
-      <c r="B58" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>754</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>797</v>
-      </c>
-      <c r="G58" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H58" s="20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="I58" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J58" s="8" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="n">
-        <v>137</v>
-      </c>
-      <c r="B59" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D59" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>799</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="G59" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H59" s="20" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="I59" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1013388982214","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J59" s="8" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="n">
-        <v>139</v>
-      </c>
-      <c r="B60" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D60" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>800</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="G60" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H60" s="20" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="I60" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=920058690376","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J60" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="n">
-        <v>140</v>
-      </c>
-      <c r="B61" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D61" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>801</v>
-      </c>
-      <c r="F61" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="G61" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H61" s="20" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="I61" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=533725557959","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J61" s="8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="n">
-        <v>141</v>
-      </c>
-      <c r="B62" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>802</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="G62" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H62" s="20" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="I62" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=996702312391","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J62" s="8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="n">
-        <v>142</v>
-      </c>
-      <c r="B63" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>803</v>
-      </c>
-      <c r="F63" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G63" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H63" s="20" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="I63" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1005108810412","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J63" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="n">
-        <v>143</v>
-      </c>
-      <c r="B64" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D64" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>804</v>
-      </c>
-      <c r="F64" s="8" t="s">
-        <v>735</v>
-      </c>
-      <c r="G64" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H64" s="20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="I64" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=908248360601","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J64" s="8" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="n">
-        <v>144</v>
-      </c>
-      <c r="B65" s="19" t="n">
-        <v>46272</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>806</v>
-      </c>
-      <c r="F65" s="8" t="s">
-        <v>735</v>
-      </c>
-      <c r="G65" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H65" s="20" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="I65" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=708737648760","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J65" s="8" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="n">
-        <v>147</v>
-      </c>
-      <c r="B66" s="19" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D66" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>729</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="G66" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H66" s="20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I66" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=640391703111","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J66" s="8" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="n">
-        <v>148</v>
-      </c>
-      <c r="B67" s="19" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="F67" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="G67" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H67" s="20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I67" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1062189210190","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J67" s="8" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="n">
-        <v>149</v>
-      </c>
-      <c r="B68" s="19" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="G68" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H68" s="20" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="I68" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1028742717053","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J68" s="8" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="n">
-        <v>150</v>
-      </c>
-      <c r="B69" s="19" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D69" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="G69" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H69" s="20" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="I69" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=726808419708","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J69" s="8" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="n">
-        <v>151</v>
-      </c>
-      <c r="B70" s="19" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D70" s="8" t="s">
-        <v>810</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>811</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>812</v>
-      </c>
-      <c r="G70" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H70" s="20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="I70" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=602152415662","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J70" s="8" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="n">
-        <v>152</v>
-      </c>
-      <c r="B71" s="19" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D71" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>813</v>
-      </c>
-      <c r="F71" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="G71" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H71" s="20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="I71" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=606816197525","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J71" s="8" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="n">
-        <v>153</v>
-      </c>
-      <c r="B72" s="19" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D72" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>814</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="G72" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="H72" s="20" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I72" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=977236759812","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J72" s="8" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="n">
-        <v>154</v>
-      </c>
-      <c r="B73" s="19" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D73" s="8" t="s">
-        <v>815</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>816</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>817</v>
-      </c>
-      <c r="G73" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H73" s="20" t="n">
-        <v>9.84</v>
-      </c>
-      <c r="I73" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=581798084270","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J73" s="8" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="n">
-        <v>155</v>
-      </c>
-      <c r="B74" s="19" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>754</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="G74" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H74" s="20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="I74" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J74" s="8" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="n">
-        <v>156</v>
-      </c>
-      <c r="B75" s="19" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D75" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>754</v>
-      </c>
-      <c r="F75" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="G75" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" s="20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="I75" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J75" s="8" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="n">
-        <v>157</v>
-      </c>
-      <c r="B76" s="19" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>754</v>
-      </c>
-      <c r="F76" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="G76" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H76" s="20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="I76" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J76" s="8" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="n">
-        <v>158</v>
-      </c>
-      <c r="B77" s="19" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D77" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>819</v>
-      </c>
-      <c r="F77" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="G77" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H77" s="20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I77" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1025817117811","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J77" s="8" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="n">
-        <v>159</v>
-      </c>
-      <c r="B78" s="19" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>819</v>
-      </c>
-      <c r="F78" s="8" t="s">
-        <v>820</v>
-      </c>
-      <c r="G78" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H78" s="20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I78" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1025817117811","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J78" s="8" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="n">
-        <v>160</v>
-      </c>
-      <c r="B79" s="19" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D79" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>821</v>
-      </c>
-      <c r="F79" s="8" t="s">
-        <v>735</v>
-      </c>
-      <c r="G79" s="9" t="n">
-        <v>50</v>
-      </c>
-      <c r="H79" s="20" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I79" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=891785167202","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J79" s="8" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="n">
-        <v>161</v>
-      </c>
-      <c r="B80" s="19" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D80" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>822</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>735</v>
-      </c>
-      <c r="G80" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H80" s="20" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="I80" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=705642638300","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J80" s="8" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="n">
-        <v>162</v>
-      </c>
-      <c r="B81" s="19" t="n">
-        <v>46269</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D81" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>823</v>
-      </c>
-      <c r="F81" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="G81" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H81" s="20" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="I81" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=747094785928","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J81" s="8" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="n">
-        <v>178</v>
-      </c>
-      <c r="B82" s="19" t="n">
-        <v>46266</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D82" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="E82" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="F82" s="8" t="s">
-        <v>735</v>
-      </c>
-      <c r="G82" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H82" s="20" t="n">
-        <v>21.17</v>
-      </c>
-      <c r="I82" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1027587805193","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J82" s="8" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="n">
-        <v>196</v>
-      </c>
-      <c r="B83" s="19" t="n">
-        <v>46258</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D83" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E83" s="8" t="s">
-        <v>753</v>
-      </c>
-      <c r="F83" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G83" s="9" t="n">
-        <v>50</v>
-      </c>
-      <c r="H83" s="20" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I83" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=630712731066","打开商品")</f>
-        <v>打开商品</v>
-      </c>
-      <c r="J83" s="8" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="n">
-        <v>203</v>
-      </c>
-      <c r="B84" s="19" t="n">
-        <v>46258</v>
-      </c>
-      <c r="C84" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D84" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="E84" s="8" t="s">
-        <v>824</v>
-      </c>
-      <c r="F84" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="G84" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H84" s="20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="I84" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=969642590399","打开商品")</f>
-        <v>打开商品</v>
-      </c>
       <c r="J84" s="8" t="s">
-        <v>199</v>
+        <v>252</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="n">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="B85" s="19" t="n">
-        <v>46258</v>
+        <v>46253</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>27</v>
+        <v>806</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>762</v>
+        <v>807</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>43</v>
+        <v>808</v>
       </c>
       <c r="G85" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H85" s="20" t="n">
-        <v>1.98</v>
+        <v>3.28</v>
       </c>
       <c r="I85" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=731471380840","打开商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=744370287305","打开商品")</f>
         <v>打开商品</v>
       </c>
       <c r="J85" s="8" t="s">
-        <v>730</v>
+        <v>809</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="n">
-        <v>206</v>
+        <v>12</v>
       </c>
       <c r="B86" s="19" t="n">
-        <v>46258</v>
+        <v>46300.4844444444</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>736</v>
+        <v>706</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>27</v>
+        <v>675</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>48</v>
+        <v>680</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H86" s="20" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="I86" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=730407108775","打开商品")</f>
-        <v>打开商品</v>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
+        <v>打开订单商品</v>
       </c>
       <c r="J86" s="8" t="s">
-        <v>45</v>
+        <v>811</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="n">
-        <v>209</v>
+        <v>22</v>
       </c>
       <c r="B87" s="19" t="n">
-        <v>46256</v>
+        <v>46294.9525925926</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>826</v>
+        <v>711</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>827</v>
+        <v>625</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>828</v>
+        <v>812</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>829</v>
+        <v>626</v>
       </c>
       <c r="G87" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H87" s="20" t="n">
-        <v>169</v>
+        <v>84.59</v>
       </c>
       <c r="I87" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=956985590887","打开商品")</f>
-        <v>打开商品</v>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=585415365001","打开订单商品")</f>
+        <v>打开订单商品</v>
       </c>
       <c r="J87" s="8" t="s">
-        <v>830</v>
+        <v>813</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="n">
-        <v>213</v>
+        <v>29</v>
       </c>
       <c r="B88" s="19" t="n">
-        <v>46254</v>
+        <v>46291.7980902778</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>141</v>
+        <v>643</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>754</v>
+        <v>814</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>255</v>
+        <v>644</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H88" s="20" t="n">
-        <v>1.44</v>
+        <v>3.63</v>
       </c>
       <c r="I88" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=947267344247","打开商品")</f>
-        <v>打开商品</v>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=781764816472","打开订单商品")</f>
+        <v>打开订单商品</v>
       </c>
       <c r="J88" s="8" t="s">
-        <v>252</v>
+        <v>815</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="n">
-        <v>220</v>
+        <v>30</v>
       </c>
       <c r="B89" s="19" t="n">
-        <v>46253</v>
+        <v>46291.7979166667</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>831</v>
+        <v>643</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>832</v>
+        <v>814</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>833</v>
+        <v>644</v>
       </c>
       <c r="G89" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H89" s="20" t="n">
-        <v>3.28</v>
+        <v>3.52</v>
       </c>
       <c r="I89" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=744370287305","打开商品")</f>
-        <v>打开商品</v>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=781764816472","打开订单商品")</f>
+        <v>打开订单商品</v>
       </c>
       <c r="J89" s="8" t="s">
-        <v>834</v>
+        <v>816</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="64" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B90" s="19" t="n">
-        <v>46300.4844444444</v>
+        <v>46291.0479398148</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>728</v>
+        <v>711</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>697</v>
+        <v>649</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>835</v>
+        <v>817</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>702</v>
+        <v>650</v>
       </c>
       <c r="G90" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H90" s="20" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="I90" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=736162720327","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J90" s="8" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B91" s="19" t="n">
-        <v>46294.9525925926</v>
+        <v>46289.0137384259</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>625</v>
+        <v>656</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>837</v>
+        <v>819</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>626</v>
+        <v>657</v>
       </c>
       <c r="G91" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H91" s="20" t="n">
-        <v>84.59</v>
+        <v>0.99</v>
       </c>
       <c r="I91" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=585415365001","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=945215173380","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J91" s="8" t="s">
-        <v>838</v>
+        <v>820</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B92" s="19" t="n">
-        <v>46291.7980902778</v>
+        <v>46286.4381134259</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>665</v>
+        <v>821</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>839</v>
+        <v>822</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>666</v>
+        <v>823</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H92" s="20" t="n">
         <v>3.63</v>
       </c>
       <c r="I92" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=781764816472","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=567201709691","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J92" s="8" t="s">
-        <v>840</v>
+        <v>824</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B93" s="19" t="n">
-        <v>46291.7979166667</v>
+        <v>46286.4381134259</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>665</v>
+        <v>821</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>839</v>
+        <v>822</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>666</v>
+        <v>825</v>
       </c>
       <c r="G93" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H93" s="20" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="I93" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=781764816472","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=567201709691","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J93" s="8" t="s">
-        <v>841</v>
+        <v>826</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="B94" s="19" t="n">
-        <v>46291.0479398148</v>
+        <v>46277.8198726852</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>842</v>
+        <v>810</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>672</v>
+        <v>690</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H94" s="20" t="n">
-        <v>3.42</v>
+        <v>3.88</v>
       </c>
       <c r="I94" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=736162720327","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J94" s="8" t="s">
-        <v>843</v>
+        <v>827</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="n">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="B95" s="19" t="n">
-        <v>46289.0137384259</v>
+        <v>46277.8198726852</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>844</v>
+        <v>810</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="G95" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H95" s="20" t="n">
-        <v>0.99</v>
+        <v>3.59</v>
       </c>
       <c r="I95" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=945215173380","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J95" s="8" t="s">
-        <v>845</v>
+        <v>828</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="n">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="B96" s="19" t="n">
-        <v>46286.4381134259</v>
+        <v>46277.8198726852</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>846</v>
+        <v>675</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>847</v>
+        <v>810</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>848</v>
+        <v>684</v>
       </c>
       <c r="G96" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>3.63</v>
+        <v>3.31</v>
       </c>
       <c r="I96" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=567201709691","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J96" s="8" t="s">
-        <v>849</v>
+        <v>829</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="B97" s="19" t="n">
-        <v>46286.4381134259</v>
+        <v>46277.8198726852</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>846</v>
+        <v>675</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>847</v>
+        <v>810</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>850</v>
+        <v>676</v>
       </c>
       <c r="G97" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H97" s="20" t="n">
-        <v>3.3</v>
+        <v>3.03</v>
       </c>
       <c r="I97" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=567201709691","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J97" s="8" t="s">
-        <v>851</v>
+        <v>830</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B98" s="19" t="n">
         <v>46277.8198726852</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>697</v>
+        <v>675</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>835</v>
+        <v>810</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>712</v>
+        <v>693</v>
       </c>
       <c r="G98" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H98" s="20" t="n">
-        <v>3.88</v>
+        <v>3.59</v>
       </c>
       <c r="I98" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J98" s="8" t="s">
-        <v>852</v>
+        <v>831</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="n">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="B99" s="19" t="n">
-        <v>46277.8198726852</v>
+        <v>46274.8817939815</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>697</v>
+        <v>613</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>709</v>
+        <v>611</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H99" s="20" t="n">
-        <v>3.59</v>
+        <v>99</v>
       </c>
       <c r="I99" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1078248851201","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J99" s="8" t="s">
-        <v>853</v>
+        <v>833</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="n">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="B100" s="19" t="n">
-        <v>46277.8198726852</v>
+        <v>46272.8961458333</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>697</v>
+        <v>663</v>
       </c>
       <c r="E100" s="8" t="s">
+        <v>834</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>664</v>
+      </c>
+      <c r="G100" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H100" s="20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I100" s="10" t="str">
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=625390659071","打开订单商品")</f>
+        <v>打开订单商品</v>
+      </c>
+      <c r="J100" s="8" t="s">
         <v>835</v>
-      </c>
-      <c r="F100" s="8" t="s">
-        <v>706</v>
-      </c>
-      <c r="G100" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H100" s="20" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="I100" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="J100" s="8" t="s">
-        <v>854</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="n">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="B101" s="19" t="n">
-        <v>46277.8198726852</v>
+        <v>46272.8961458333</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>697</v>
+        <v>663</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>698</v>
+        <v>669</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H101" s="20" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="I101" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=733598659967","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J101" s="8" t="s">
-        <v>855</v>
+        <v>837</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="n">
-        <v>89</v>
+        <v>168</v>
       </c>
       <c r="B102" s="19" t="n">
-        <v>46277.8198726852</v>
+        <v>46266.8829513889</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>697</v>
+        <v>613</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>715</v>
+        <v>611</v>
       </c>
       <c r="G102" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H102" s="20" t="n">
-        <v>3.59</v>
+        <v>99</v>
       </c>
       <c r="I102" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1078248851201","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J102" s="8" t="s">
-        <v>856</v>
+        <v>838</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="B103" s="19" t="n">
-        <v>46274.8817939815</v>
+        <v>46266.8829513889</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D103" s="8" t="s">
         <v>613</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>857</v>
+        <v>832</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>611</v>
+        <v>839</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H103" s="20" t="n">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="I103" s="10" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1078248851201","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J103" s="8" t="s">
-        <v>858</v>
+        <v>840</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="n">
-        <v>111</v>
+        <v>172</v>
       </c>
       <c r="B104" s="19" t="n">
-        <v>46272.8961458333</v>
+        <v>46266.6967476852</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>685</v>
+        <v>663</v>
       </c>
       <c r="E104" s="8" t="s">
-        <v>859</v>
+        <v>836</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>686</v>
+        <v>669</v>
       </c>
       <c r="G104" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H104" s="20" t="n">
-        <v>1.94</v>
+        <v>2.91</v>
       </c>
       <c r="I104" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=625390659071","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=733598659967","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J104" s="8" t="s">
-        <v>860</v>
+        <v>841</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="n">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="B105" s="19" t="n">
-        <v>46272.8961458333</v>
+        <v>46266.6967476852</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>685</v>
+        <v>663</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>861</v>
+        <v>834</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>691</v>
+        <v>664</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H105" s="20" t="n">
-        <v>2.91</v>
+        <v>1.94</v>
       </c>
       <c r="I105" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=733598659967","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=625390659071","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J105" s="8" t="s">
-        <v>862</v>
+        <v>842</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="B106" s="19" t="n">
-        <v>46266.8829513889</v>
+        <v>46265.3613773148</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>857</v>
+        <v>843</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="G106" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H106" s="20" t="n">
-        <v>99</v>
+        <v>129.99</v>
       </c>
       <c r="I106" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1078248851201","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=768918125679","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J106" s="8" t="s">
-        <v>863</v>
+        <v>844</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="n">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="B107" s="19" t="n">
-        <v>46266.8829513889</v>
+        <v>46259.9707407408</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>613</v>
+        <v>718</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>857</v>
+        <v>845</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>864</v>
+        <v>846</v>
       </c>
       <c r="G107" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H107" s="20" t="n">
-        <v>45</v>
+        <v>106.68</v>
       </c>
       <c r="I107" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1078248851201","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=588102758150","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J107" s="8" t="s">
-        <v>865</v>
+        <v>847</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="n">
-        <v>172</v>
+        <v>211</v>
       </c>
       <c r="B108" s="19" t="n">
-        <v>46266.6967476852</v>
+        <v>46254.6453587963</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>685</v>
+        <v>802</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>861</v>
+        <v>803</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>691</v>
+        <v>804</v>
       </c>
       <c r="G108" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H108" s="20" t="n">
-        <v>2.91</v>
+        <v>188</v>
       </c>
       <c r="I108" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=733598659967","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=956985590887","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J108" s="8" t="s">
-        <v>866</v>
+        <v>848</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="n">
-        <v>173</v>
+        <v>214</v>
       </c>
       <c r="B109" s="19" t="n">
-        <v>46266.6967476852</v>
+        <v>46254.0581481482</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>685</v>
+        <v>849</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>859</v>
+        <v>850</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>686</v>
+        <v>851</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H109" s="20" t="n">
-        <v>1.94</v>
+        <v>4.69</v>
       </c>
       <c r="I109" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=625390659071","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=621018369847","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="J109" s="8" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="1" t="n">
-        <v>180</v>
-      </c>
-      <c r="B110" s="19" t="n">
-        <v>46265.3613773148</v>
-      </c>
-      <c r="C110" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D110" s="8" t="s">
-        <v>606</v>
-      </c>
-      <c r="E110" s="8" t="s">
-        <v>868</v>
-      </c>
-      <c r="F110" s="8" t="s">
-        <v>619</v>
-      </c>
-      <c r="G110" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H110" s="20" t="n">
-        <v>129.99</v>
-      </c>
-      <c r="I110" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=768918125679","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="J110" s="8" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="1" t="n">
-        <v>189</v>
-      </c>
-      <c r="B111" s="19" t="n">
-        <v>46259.9707407408</v>
-      </c>
-      <c r="C111" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D111" s="8" t="s">
-        <v>744</v>
-      </c>
-      <c r="E111" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="F111" s="8" t="s">
-        <v>871</v>
-      </c>
-      <c r="G111" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H111" s="20" t="n">
-        <v>106.68</v>
-      </c>
-      <c r="I111" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=588102758150","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="J111" s="8" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="1" t="n">
-        <v>211</v>
-      </c>
-      <c r="B112" s="19" t="n">
-        <v>46254.6453587963</v>
-      </c>
-      <c r="C112" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D112" s="8" t="s">
-        <v>827</v>
-      </c>
-      <c r="E112" s="8" t="s">
-        <v>828</v>
-      </c>
-      <c r="F112" s="8" t="s">
-        <v>829</v>
-      </c>
-      <c r="G112" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H112" s="20" t="n">
-        <v>188</v>
-      </c>
-      <c r="I112" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=956985590887","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="J112" s="8" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="1" t="n">
-        <v>214</v>
-      </c>
-      <c r="B113" s="19" t="n">
-        <v>46254.0581481482</v>
-      </c>
-      <c r="C113" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="D113" s="8" t="s">
-        <v>874</v>
-      </c>
-      <c r="E113" s="8" t="s">
-        <v>875</v>
-      </c>
-      <c r="F113" s="8" t="s">
-        <v>876</v>
-      </c>
-      <c r="G113" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H113" s="20" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="I113" s="10" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=621018369847","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-      <c r="J113" s="8" t="s">
-        <v>877</v>
-      </c>
-    </row>
+        <v>852</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="111" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="112" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="113" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -16143,7 +15795,7 @@
     </row>
     <row r="2" customFormat="false" ht="27.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="22" t="s">
-        <v>878</v>
+        <v>853</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -16158,7 +15810,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>879</v>
+        <v>854</v>
       </c>
       <c r="B3" s="21"/>
       <c r="C3" s="21"/>
@@ -16173,7 +15825,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>880</v>
+        <v>855</v>
       </c>
       <c r="B4" s="21"/>
       <c r="C4" s="21"/>
@@ -16238,32 +15890,32 @@
     </row>
     <row r="7" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>881</v>
+        <v>856</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>818</v>
+        <v>793</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>882</v>
+        <v>857</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>883</v>
+        <v>858</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>815</v>
+        <v>790</v>
       </c>
       <c r="F7" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=581798084270","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>817</v>
+        <v>792</v>
       </c>
       <c r="H7" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>884</v>
+        <v>859</v>
       </c>
       <c r="J7" s="21" t="n">
         <v>154</v>
@@ -16274,32 +15926,32 @@
     </row>
     <row r="8" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>885</v>
+        <v>860</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>784</v>
+        <v>758</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>886</v>
+        <v>861</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>887</v>
+        <v>862</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>781</v>
+        <v>755</v>
       </c>
       <c r="F8" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=851008959999","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>783</v>
+        <v>757</v>
       </c>
       <c r="H8" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="21" t="s">
-        <v>888</v>
+        <v>863</v>
       </c>
       <c r="J8" s="21" t="n">
         <v>107</v>
@@ -16310,32 +15962,32 @@
     </row>
     <row r="9" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>885</v>
+        <v>860</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>780</v>
+        <v>754</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>889</v>
+        <v>864</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>883</v>
+        <v>858</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>777</v>
+        <v>751</v>
       </c>
       <c r="F9" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=19606507546","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>779</v>
+        <v>753</v>
       </c>
       <c r="H9" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I9" s="21" t="s">
-        <v>890</v>
+        <v>865</v>
       </c>
       <c r="J9" s="21" t="n">
         <v>106</v>
@@ -16346,32 +15998,32 @@
     </row>
     <row r="10" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>885</v>
+        <v>860</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>747</v>
+        <v>721</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>891</v>
+        <v>866</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>892</v>
+        <v>867</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>744</v>
+        <v>718</v>
       </c>
       <c r="F10" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=626569273184","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>746</v>
+        <v>720</v>
       </c>
       <c r="H10" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>893</v>
+        <v>868</v>
       </c>
       <c r="J10" s="21" t="n">
         <v>35</v>
@@ -16382,32 +16034,32 @@
     </row>
     <row r="11" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>894</v>
+        <v>869</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>776</v>
+        <v>750</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>895</v>
+        <v>870</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>883</v>
+        <v>858</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>773</v>
+        <v>747</v>
       </c>
       <c r="F11" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=979077591318","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>775</v>
+        <v>749</v>
       </c>
       <c r="H11" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I11" s="21" t="s">
-        <v>896</v>
+        <v>871</v>
       </c>
       <c r="J11" s="21" t="n">
         <v>105</v>
@@ -16418,32 +16070,32 @@
     </row>
     <row r="12" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>894</v>
+        <v>869</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>830</v>
+        <v>805</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>897</v>
+        <v>872</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>883</v>
+        <v>858</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>827</v>
+        <v>802</v>
       </c>
       <c r="F12" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=956985590887","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>829</v>
+        <v>804</v>
       </c>
       <c r="H12" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>898</v>
+        <v>873</v>
       </c>
       <c r="J12" s="21" t="n">
         <v>211</v>
@@ -16454,32 +16106,32 @@
     </row>
     <row r="13" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>899</v>
+        <v>874</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>752</v>
+        <v>726</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>900</v>
+        <v>875</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>901</v>
+        <v>876</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>749</v>
+        <v>723</v>
       </c>
       <c r="F13" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=566089419587","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>751</v>
+        <v>725</v>
       </c>
       <c r="H13" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I13" s="21" t="s">
-        <v>902</v>
+        <v>877</v>
       </c>
       <c r="J13" s="21" t="n">
         <v>43</v>
@@ -16490,32 +16142,32 @@
     </row>
     <row r="14" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>903</v>
+        <v>878</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>759</v>
+        <v>733</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>904</v>
+        <v>879</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>901</v>
+        <v>876</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>739</v>
+        <v>714</v>
       </c>
       <c r="F14" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=972313702890","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>758</v>
+        <v>732</v>
       </c>
       <c r="H14" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>905</v>
+        <v>880</v>
       </c>
       <c r="J14" s="21" t="n">
         <v>76</v>
@@ -16526,32 +16178,32 @@
     </row>
     <row r="15" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>885</v>
+        <v>860</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>834</v>
+        <v>809</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>906</v>
+        <v>881</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>883</v>
+        <v>858</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>831</v>
+        <v>806</v>
       </c>
       <c r="F15" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=744370287305","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>833</v>
+        <v>808</v>
       </c>
       <c r="H15" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I15" s="21" t="s">
-        <v>907</v>
+        <v>882</v>
       </c>
       <c r="J15" s="21" t="n">
         <v>220</v>
@@ -16562,32 +16214,32 @@
     </row>
     <row r="16" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>908</v>
+        <v>883</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>742</v>
+        <v>717</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>909</v>
+        <v>884</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>883</v>
+        <v>858</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>739</v>
+        <v>714</v>
       </c>
       <c r="F16" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=1049340097483","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G16" s="21" t="s">
-        <v>741</v>
+        <v>716</v>
       </c>
       <c r="H16" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I16" s="21" t="s">
-        <v>910</v>
+        <v>885</v>
       </c>
       <c r="J16" s="21" t="n">
         <v>24</v>
@@ -16598,16 +16250,16 @@
     </row>
     <row r="17" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>911</v>
+        <v>886</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>912</v>
+        <v>887</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>864</v>
+        <v>839</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>913</v>
+        <v>888</v>
       </c>
       <c r="E17" s="21" t="s">
         <v>613</v>
@@ -16617,13 +16269,13 @@
         <v>打开订单商品</v>
       </c>
       <c r="G17" s="21" t="s">
-        <v>864</v>
+        <v>839</v>
       </c>
       <c r="H17" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I17" s="21" t="s">
-        <v>914</v>
+        <v>889</v>
       </c>
       <c r="J17" s="21" t="n">
         <v>169</v>
@@ -16634,32 +16286,32 @@
     </row>
     <row r="18" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>915</v>
+        <v>890</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>916</v>
+        <v>891</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>917</v>
+        <v>892</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>918</v>
+        <v>893</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>744</v>
+        <v>718</v>
       </c>
       <c r="F18" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=588102758150","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G18" s="21" t="s">
-        <v>871</v>
+        <v>846</v>
       </c>
       <c r="H18" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I18" s="21" t="s">
-        <v>919</v>
+        <v>894</v>
       </c>
       <c r="J18" s="21" t="n">
         <v>189</v>
@@ -16670,32 +16322,32 @@
     </row>
     <row r="19" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>920</v>
+        <v>895</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>921</v>
+        <v>896</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>922</v>
+        <v>897</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>923</v>
+        <v>898</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>846</v>
+        <v>821</v>
       </c>
       <c r="F19" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=567201709691","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G19" s="21" t="s">
-        <v>848</v>
+        <v>823</v>
       </c>
       <c r="H19" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>924</v>
+        <v>899</v>
       </c>
       <c r="J19" s="21" t="n">
         <v>39</v>
@@ -16706,32 +16358,32 @@
     </row>
     <row r="20" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>920</v>
+        <v>895</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>925</v>
+        <v>900</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>926</v>
+        <v>901</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>923</v>
+        <v>898</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>846</v>
+        <v>821</v>
       </c>
       <c r="F20" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=567201709691","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G20" s="21" t="s">
-        <v>850</v>
+        <v>825</v>
       </c>
       <c r="H20" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I20" s="21" t="s">
-        <v>927</v>
+        <v>902</v>
       </c>
       <c r="J20" s="21" t="n">
         <v>40</v>
@@ -16742,32 +16394,32 @@
     </row>
     <row r="21" customFormat="false" ht="80" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>885</v>
+        <v>860</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>928</v>
+        <v>903</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>929</v>
+        <v>904</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>930</v>
+        <v>905</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>874</v>
+        <v>849</v>
       </c>
       <c r="F21" s="24" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=621018369847","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
       <c r="G21" s="21" t="s">
-        <v>876</v>
+        <v>851</v>
       </c>
       <c r="H21" s="21" t="n">
         <v>1</v>
       </c>
       <c r="I21" s="21" t="s">
-        <v>931</v>
+        <v>906</v>
       </c>
       <c r="J21" s="21" t="n">
         <v>214</v>
@@ -16835,7 +16487,7 @@
     </row>
     <row r="2" customFormat="false" ht="27.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="22" t="s">
-        <v>932</v>
+        <v>907</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -16854,7 +16506,7 @@
     </row>
     <row r="3" customFormat="false" ht="40" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>933</v>
+        <v>908</v>
       </c>
       <c r="B3" s="21"/>
       <c r="C3" s="21"/>
@@ -16900,19 +16552,19 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>934</v>
+        <v>909</v>
       </c>
       <c r="B5" s="27" t="n">
         <v>20</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>935</v>
+        <v>910</v>
       </c>
       <c r="D5" s="27" t="n">
         <v>5</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>936</v>
+        <v>911</v>
       </c>
       <c r="F5" s="27" t="n">
         <v>12</v>
@@ -16946,16 +16598,16 @@
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>937</v>
+        <v>912</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>938</v>
+        <v>913</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>939</v>
+        <v>914</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>940</v>
+        <v>915</v>
       </c>
       <c r="E7" s="21"/>
       <c r="F7" s="21"/>
@@ -16971,7 +16623,7 @@
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>941</v>
+        <v>916</v>
       </c>
       <c r="B8" s="25" t="n">
         <f aca="false">SUM(I29:I72)</f>
@@ -16999,7 +16651,7 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>942</v>
+        <v>917</v>
       </c>
       <c r="B9" s="25" t="n">
         <v>0</v>
@@ -17025,7 +16677,7 @@
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="29" t="s">
-        <v>943</v>
+        <v>918</v>
       </c>
       <c r="B10" s="30" t="n">
         <f aca="false">B8+B9</f>
@@ -17053,7 +16705,7 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>944</v>
+        <v>919</v>
       </c>
       <c r="B11" s="25" t="n">
         <f aca="false">$B$5/$D$5*$B$4</f>
@@ -17081,7 +16733,7 @@
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="29" t="s">
-        <v>945</v>
+        <v>920</v>
       </c>
       <c r="B12" s="30" t="n">
         <f aca="false">B8+B11</f>
@@ -17126,7 +16778,7 @@
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>946</v>
+        <v>921</v>
       </c>
       <c r="B14" s="25"/>
       <c r="C14" s="25"/>
@@ -17145,16 +16797,16 @@
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="s">
-        <v>947</v>
+        <v>922</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>948</v>
+        <v>923</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>949</v>
+        <v>924</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>950</v>
+        <v>925</v>
       </c>
       <c r="E15" s="21"/>
       <c r="F15" s="21"/>
@@ -17170,7 +16822,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>951</v>
+        <v>926</v>
       </c>
       <c r="B16" s="25" t="n">
         <f aca="false">SUM(L29:L72)</f>
@@ -17198,7 +16850,7 @@
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="29" t="s">
-        <v>952</v>
+        <v>927</v>
       </c>
       <c r="B17" s="30" t="n">
         <f aca="false">B16</f>
@@ -17226,7 +16878,7 @@
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>953</v>
+        <v>928</v>
       </c>
       <c r="B18" s="25" t="n">
         <f aca="false">ROUNDUP($B$4/$D$5,0)*$B$5</f>
@@ -17254,7 +16906,7 @@
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="29" t="s">
-        <v>954</v>
+        <v>929</v>
       </c>
       <c r="B19" s="30" t="n">
         <f aca="false">B16+B18</f>
@@ -17299,7 +16951,7 @@
     </row>
     <row r="21" customFormat="false" ht="40" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>955</v>
+        <v>930</v>
       </c>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
@@ -17318,7 +16970,7 @@
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>956</v>
+        <v>931</v>
       </c>
       <c r="B22" s="25" t="n">
         <f aca="false">配件与耗材!K18</f>
@@ -17340,7 +16992,7 @@
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="29" t="s">
-        <v>957</v>
+        <v>932</v>
       </c>
       <c r="B23" s="30" t="n">
         <f aca="false">D10+B22</f>
@@ -17362,7 +17014,7 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="29" t="s">
-        <v>958</v>
+        <v>933</v>
       </c>
       <c r="B24" s="30" t="n">
         <f aca="false">D12+B22</f>
@@ -17401,7 +17053,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>959</v>
+        <v>934</v>
       </c>
       <c r="B26" s="21"/>
       <c r="C26" s="21"/>
@@ -17437,43 +17089,43 @@
     </row>
     <row r="28" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="23" t="s">
-        <v>960</v>
+        <v>935</v>
       </c>
       <c r="B28" s="23" t="s">
         <v>554</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>961</v>
+        <v>936</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>962</v>
+        <v>937</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>963</v>
+        <v>938</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>964</v>
+        <v>939</v>
       </c>
       <c r="G28" s="23" t="s">
-        <v>965</v>
+        <v>940</v>
       </c>
       <c r="H28" s="23" t="s">
-        <v>966</v>
+        <v>941</v>
       </c>
       <c r="I28" s="23" t="s">
-        <v>967</v>
+        <v>942</v>
       </c>
       <c r="J28" s="23" t="s">
-        <v>968</v>
+        <v>943</v>
       </c>
       <c r="K28" s="23" t="s">
-        <v>969</v>
+        <v>944</v>
       </c>
       <c r="L28" s="23" t="s">
-        <v>970</v>
+        <v>945</v>
       </c>
       <c r="M28" s="23" t="s">
-        <v>971</v>
+        <v>946</v>
       </c>
       <c r="N28" s="23" t="s">
         <v>552</v>
@@ -17484,7 +17136,7 @@
     </row>
     <row r="29" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>972</v>
+        <v>947</v>
       </c>
       <c r="B29" s="21" t="n">
         <v>1</v>
@@ -17540,7 +17192,7 @@
     </row>
     <row r="30" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>973</v>
+        <v>948</v>
       </c>
       <c r="B30" s="21" t="n">
         <v>1</v>
@@ -17596,7 +17248,7 @@
     </row>
     <row r="31" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>974</v>
+        <v>949</v>
       </c>
       <c r="B31" s="21" t="n">
         <v>100</v>
@@ -17652,7 +17304,7 @@
     </row>
     <row r="32" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>975</v>
+        <v>950</v>
       </c>
       <c r="B32" s="21" t="n">
         <v>100</v>
@@ -17708,7 +17360,7 @@
     </row>
     <row r="33" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>976</v>
+        <v>951</v>
       </c>
       <c r="B33" s="21" t="n">
         <v>1</v>
@@ -17764,7 +17416,7 @@
     </row>
     <row r="34" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
-        <v>977</v>
+        <v>952</v>
       </c>
       <c r="B34" s="21" t="n">
         <v>100</v>
@@ -17820,7 +17472,7 @@
     </row>
     <row r="35" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
-        <v>978</v>
+        <v>953</v>
       </c>
       <c r="B35" s="21" t="n">
         <v>100</v>
@@ -17876,7 +17528,7 @@
     </row>
     <row r="36" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>979</v>
+        <v>954</v>
       </c>
       <c r="B36" s="21" t="n">
         <v>20</v>
@@ -17932,7 +17584,7 @@
     </row>
     <row r="37" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
-        <v>980</v>
+        <v>955</v>
       </c>
       <c r="B37" s="21" t="n">
         <v>50</v>
@@ -17988,7 +17640,7 @@
     </row>
     <row r="38" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="21" t="s">
-        <v>981</v>
+        <v>956</v>
       </c>
       <c r="B38" s="21" t="n">
         <v>100</v>
@@ -18044,7 +17696,7 @@
     </row>
     <row r="39" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="21" t="s">
-        <v>982</v>
+        <v>957</v>
       </c>
       <c r="B39" s="21" t="n">
         <v>100</v>
@@ -18100,7 +17752,7 @@
     </row>
     <row r="40" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="21" t="s">
-        <v>983</v>
+        <v>958</v>
       </c>
       <c r="B40" s="21" t="n">
         <v>50</v>
@@ -18156,7 +17808,7 @@
     </row>
     <row r="41" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="21" t="s">
-        <v>984</v>
+        <v>959</v>
       </c>
       <c r="B41" s="21" t="n">
         <v>2</v>
@@ -18212,7 +17864,7 @@
     </row>
     <row r="42" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="21" t="s">
-        <v>985</v>
+        <v>960</v>
       </c>
       <c r="B42" s="21" t="n">
         <v>15</v>
@@ -18268,7 +17920,7 @@
     </row>
     <row r="43" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="21" t="s">
-        <v>986</v>
+        <v>961</v>
       </c>
       <c r="B43" s="21" t="n">
         <v>50</v>
@@ -18324,7 +17976,7 @@
     </row>
     <row r="44" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="21" t="s">
-        <v>987</v>
+        <v>962</v>
       </c>
       <c r="B44" s="21" t="n">
         <v>10</v>
@@ -18380,7 +18032,7 @@
     </row>
     <row r="45" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="21" t="s">
-        <v>988</v>
+        <v>963</v>
       </c>
       <c r="B45" s="21" t="n">
         <v>2</v>
@@ -18436,7 +18088,7 @@
     </row>
     <row r="46" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="21" t="s">
-        <v>989</v>
+        <v>964</v>
       </c>
       <c r="B46" s="21" t="n">
         <v>50</v>
@@ -18492,7 +18144,7 @@
     </row>
     <row r="47" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="21" t="s">
-        <v>990</v>
+        <v>965</v>
       </c>
       <c r="B47" s="21" t="n">
         <v>20</v>
@@ -18548,7 +18200,7 @@
     </row>
     <row r="48" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="21" t="s">
-        <v>991</v>
+        <v>966</v>
       </c>
       <c r="B48" s="21" t="n">
         <v>100</v>
@@ -18604,7 +18256,7 @@
     </row>
     <row r="49" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="21" t="s">
-        <v>992</v>
+        <v>967</v>
       </c>
       <c r="B49" s="21" t="n">
         <v>100</v>
@@ -18660,7 +18312,7 @@
     </row>
     <row r="50" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="21" t="s">
-        <v>993</v>
+        <v>968</v>
       </c>
       <c r="B50" s="21" t="n">
         <v>100</v>
@@ -18716,7 +18368,7 @@
     </row>
     <row r="51" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="21" t="s">
-        <v>994</v>
+        <v>969</v>
       </c>
       <c r="B51" s="21" t="n">
         <v>100</v>
@@ -18772,7 +18424,7 @@
     </row>
     <row r="52" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="21" t="s">
-        <v>995</v>
+        <v>970</v>
       </c>
       <c r="B52" s="21" t="n">
         <v>1</v>
@@ -18828,7 +18480,7 @@
     </row>
     <row r="53" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="21" t="s">
-        <v>996</v>
+        <v>971</v>
       </c>
       <c r="B53" s="21" t="n">
         <v>1</v>
@@ -18884,7 +18536,7 @@
     </row>
     <row r="54" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="21" t="s">
-        <v>997</v>
+        <v>972</v>
       </c>
       <c r="B54" s="21" t="n">
         <v>1</v>
@@ -18940,7 +18592,7 @@
     </row>
     <row r="55" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="21" t="s">
-        <v>998</v>
+        <v>973</v>
       </c>
       <c r="B55" s="21" t="n">
         <v>20</v>
@@ -18996,7 +18648,7 @@
     </row>
     <row r="56" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="21" t="s">
-        <v>999</v>
+        <v>974</v>
       </c>
       <c r="B56" s="21" t="n">
         <v>5</v>
@@ -19052,7 +18704,7 @@
     </row>
     <row r="57" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="21" t="s">
-        <v>1000</v>
+        <v>975</v>
       </c>
       <c r="B57" s="21" t="n">
         <v>5</v>
@@ -19108,7 +18760,7 @@
     </row>
     <row r="58" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="21" t="s">
-        <v>1001</v>
+        <v>976</v>
       </c>
       <c r="B58" s="21" t="n">
         <v>5</v>
@@ -19164,7 +18816,7 @@
     </row>
     <row r="59" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="21" t="s">
-        <v>1002</v>
+        <v>977</v>
       </c>
       <c r="B59" s="21" t="n">
         <v>1</v>
@@ -19220,7 +18872,7 @@
     </row>
     <row r="60" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="21" t="s">
-        <v>1003</v>
+        <v>978</v>
       </c>
       <c r="B60" s="21" t="n">
         <v>1</v>
@@ -19276,7 +18928,7 @@
     </row>
     <row r="61" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="21" t="s">
-        <v>1004</v>
+        <v>979</v>
       </c>
       <c r="B61" s="21" t="n">
         <v>1</v>
@@ -19332,7 +18984,7 @@
     </row>
     <row r="62" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="21" t="s">
-        <v>1005</v>
+        <v>980</v>
       </c>
       <c r="B62" s="21" t="n">
         <v>1</v>
@@ -19388,7 +19040,7 @@
     </row>
     <row r="63" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="21" t="s">
-        <v>1006</v>
+        <v>981</v>
       </c>
       <c r="B63" s="21" t="n">
         <v>1</v>
@@ -19444,7 +19096,7 @@
     </row>
     <row r="64" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="21" t="s">
-        <v>1007</v>
+        <v>982</v>
       </c>
       <c r="B64" s="21" t="n">
         <v>100</v>
@@ -19500,7 +19152,7 @@
     </row>
     <row r="65" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="21" t="s">
-        <v>1008</v>
+        <v>983</v>
       </c>
       <c r="B65" s="21" t="n">
         <v>30</v>
@@ -19556,7 +19208,7 @@
     </row>
     <row r="66" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="21" t="s">
-        <v>1009</v>
+        <v>984</v>
       </c>
       <c r="B66" s="21" t="n">
         <v>100</v>
@@ -19612,7 +19264,7 @@
     </row>
     <row r="67" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="21" t="s">
-        <v>1010</v>
+        <v>985</v>
       </c>
       <c r="B67" s="21" t="n">
         <v>100</v>
@@ -19668,7 +19320,7 @@
     </row>
     <row r="68" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="21" t="s">
-        <v>1011</v>
+        <v>986</v>
       </c>
       <c r="B68" s="21" t="n">
         <v>100</v>
@@ -19724,7 +19376,7 @@
     </row>
     <row r="69" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="21" t="s">
-        <v>1012</v>
+        <v>987</v>
       </c>
       <c r="B69" s="21" t="n">
         <v>1</v>
@@ -19780,7 +19432,7 @@
     </row>
     <row r="70" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="21" t="s">
-        <v>1013</v>
+        <v>988</v>
       </c>
       <c r="B70" s="21" t="n">
         <v>1</v>
@@ -19836,7 +19488,7 @@
     </row>
     <row r="71" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="21" t="s">
-        <v>1014</v>
+        <v>989</v>
       </c>
       <c r="B71" s="21" t="n">
         <v>1</v>
@@ -19892,7 +19544,7 @@
     </row>
     <row r="72" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="21" t="s">
-        <v>1015</v>
+        <v>990</v>
       </c>
       <c r="B72" s="21" t="n">
         <v>1</v>
@@ -19997,7 +19649,7 @@
     </row>
     <row r="2" customFormat="false" ht="27.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="34" t="s">
-        <v>1016</v>
+        <v>991</v>
       </c>
       <c r="B2" s="34"/>
       <c r="C2" s="34"/>
@@ -20009,7 +19661,7 @@
     </row>
     <row r="3" customFormat="false" ht="40" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="33" t="s">
-        <v>1017</v>
+        <v>992</v>
       </c>
       <c r="B3" s="33"/>
       <c r="C3" s="33"/>
@@ -20021,11 +19673,11 @@
     </row>
     <row r="4" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="35" t="s">
-        <v>1018</v>
+        <v>993</v>
       </c>
       <c r="B4" s="36" t="n">
-        <f aca="false">SUM(F11:F39)</f>
-        <v>2244.86853676336</v>
+        <f aca="false">SUM(F11:F35)</f>
+        <v>2234.48853676336</v>
       </c>
       <c r="C4" s="33"/>
       <c r="D4" s="33"/>
@@ -20036,11 +19688,11 @@
     </row>
     <row r="5" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="35" t="s">
-        <v>1019</v>
+        <v>994</v>
       </c>
       <c r="B5" s="36" t="n">
         <f aca="false">B4+(D11+D12)*制作成本!$B$5/制作成本!$D$5</f>
-        <v>2252.86853676336</v>
+        <v>2242.48853676336</v>
       </c>
       <c r="C5" s="33"/>
       <c r="D5" s="33"/>
@@ -20051,11 +19703,11 @@
     </row>
     <row r="6" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="35" t="s">
-        <v>1020</v>
+        <v>995</v>
       </c>
       <c r="B6" s="36" t="n">
         <f aca="false">B4-F11-F12+制作成本!D16</f>
-        <v>2301.98</v>
+        <v>2291.6</v>
       </c>
       <c r="C6" s="33"/>
       <c r="D6" s="33"/>
@@ -20066,11 +19718,11 @@
     </row>
     <row r="7" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="35" t="s">
-        <v>1021</v>
+        <v>996</v>
       </c>
       <c r="B7" s="36" t="n">
         <f aca="false">B6+ROUNDUP(D11/制作成本!$D$5,0)*制作成本!$B$5+ROUNDUP(D12/制作成本!$D$5,0)*制作成本!$B$5</f>
-        <v>2341.98</v>
+        <v>2331.6</v>
       </c>
       <c r="C7" s="33"/>
       <c r="D7" s="33"/>
@@ -20091,7 +19743,7 @@
     </row>
     <row r="9" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>1022</v>
+        <v>997</v>
       </c>
       <c r="B9" s="33"/>
       <c r="C9" s="33"/>
@@ -20103,39 +19755,39 @@
     </row>
     <row r="10" customFormat="false" ht="40" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="37" t="s">
-        <v>1023</v>
+        <v>998</v>
       </c>
       <c r="B10" s="37" t="s">
-        <v>960</v>
+        <v>935</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>1024</v>
+        <v>999</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>1025</v>
+        <v>1000</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>1026</v>
+        <v>1001</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>1027</v>
+        <v>1002</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>1028</v>
+        <v>1003</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>1029</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>1030</v>
+        <v>1005</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>1031</v>
+        <v>1006</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>1032</v>
+        <v>1007</v>
       </c>
       <c r="D11" s="38" t="n">
         <f aca="false">合并采购清单!B4</f>
@@ -20150,7 +19802,7 @@
         <v>16.7249050849176</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>1033</v>
+        <v>1008</v>
       </c>
       <c r="H11" s="41" t="str">
         <f aca="false">HYPERLINK("https://github.com/kissqy/Microduck-kissqy/blob/main/hardware/README.md#完整位号bom","查看完整BOM")</f>
@@ -20159,13 +19811,13 @@
     </row>
     <row r="12" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="s">
-        <v>1034</v>
+        <v>1009</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>1035</v>
+        <v>1010</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>1032</v>
+        <v>1007</v>
       </c>
       <c r="D12" s="38" t="n">
         <f aca="false">合并采购清单!D4</f>
@@ -20180,7 +19832,7 @@
         <v>12.3336316784379</v>
       </c>
       <c r="G12" s="33" t="s">
-        <v>1033</v>
+        <v>1008</v>
       </c>
       <c r="H12" s="41" t="str">
         <f aca="false">HYPERLINK("https://github.com/kissqy/Microduck-kissqy/blob/main/hardware/README.md#完整位号bom","查看完整BOM")</f>
@@ -20192,10 +19844,10 @@
         <v>610</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>1036</v>
+        <v>1011</v>
       </c>
       <c r="C13" s="33" t="s">
-        <v>1037</v>
+        <v>1012</v>
       </c>
       <c r="D13" s="42" t="n">
         <v>15</v>
@@ -20221,10 +19873,10 @@
         <v>603</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>1038</v>
+        <v>1013</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>1039</v>
+        <v>1014</v>
       </c>
       <c r="D14" s="42" t="n">
         <v>1</v>
@@ -20250,10 +19902,10 @@
         <v>622</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>1040</v>
+        <v>1015</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>1041</v>
+        <v>1016</v>
       </c>
       <c r="D15" s="42" t="n">
         <v>1</v>
@@ -20279,10 +19931,10 @@
         <v>616</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>1042</v>
+        <v>1017</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>1039</v>
+        <v>1014</v>
       </c>
       <c r="D16" s="42" t="n">
         <v>1</v>
@@ -20308,10 +19960,10 @@
         <v>596</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>1043</v>
+        <v>1018</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>1039</v>
+        <v>1014</v>
       </c>
       <c r="D17" s="42" t="n">
         <v>1</v>
@@ -20337,10 +19989,10 @@
         <v>591</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>1044</v>
+        <v>1019</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>1039</v>
+        <v>1014</v>
       </c>
       <c r="D18" s="42" t="n">
         <v>1</v>
@@ -20363,19 +20015,19 @@
     </row>
     <row r="19" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="33" t="s">
-        <v>682</v>
+        <v>660</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>1045</v>
+        <v>1020</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>1037</v>
+        <v>1012</v>
       </c>
       <c r="D19" s="42" t="n">
         <v>5</v>
       </c>
       <c r="E19" s="39" t="n">
-        <f aca="false">配件与耗材!K28</f>
+        <f aca="false">配件与耗材!K24</f>
         <v>1.94</v>
       </c>
       <c r="F19" s="40" t="n">
@@ -20383,7 +20035,7 @@
         <v>9.7</v>
       </c>
       <c r="G19" s="33" t="s">
-        <v>1046</v>
+        <v>1021</v>
       </c>
       <c r="H19" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=625390659071","打开订单商品")</f>
@@ -20392,19 +20044,19 @@
     </row>
     <row r="20" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="33" t="s">
-        <v>688</v>
+        <v>666</v>
       </c>
       <c r="B20" s="33" t="s">
-        <v>1047</v>
+        <v>1022</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>1037</v>
+        <v>1012</v>
       </c>
       <c r="D20" s="42" t="n">
         <v>12</v>
       </c>
       <c r="E20" s="39" t="n">
-        <f aca="false">配件与耗材!K29</f>
+        <f aca="false">配件与耗材!K25</f>
         <v>2.91</v>
       </c>
       <c r="F20" s="40" t="n">
@@ -20412,7 +20064,7 @@
         <v>34.92</v>
       </c>
       <c r="G20" s="33" t="s">
-        <v>1048</v>
+        <v>1023</v>
       </c>
       <c r="H20" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=733598659967","打开订单商品")</f>
@@ -20421,19 +20073,19 @@
     </row>
     <row r="21" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="33" t="s">
-        <v>694</v>
+        <v>672</v>
       </c>
       <c r="B21" s="33" t="s">
-        <v>1049</v>
+        <v>1024</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>1050</v>
+        <v>1025</v>
       </c>
       <c r="D21" s="42" t="n">
         <v>1</v>
       </c>
       <c r="E21" s="39" t="n">
-        <f aca="false">配件与耗材!K30</f>
+        <f aca="false">配件与耗材!K26</f>
         <v>3.03</v>
       </c>
       <c r="F21" s="40" t="n">
@@ -20441,7 +20093,7 @@
         <v>3.03</v>
       </c>
       <c r="G21" s="33" t="s">
-        <v>1051</v>
+        <v>1026</v>
       </c>
       <c r="H21" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
@@ -20450,19 +20102,19 @@
     </row>
     <row r="22" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="33" t="s">
-        <v>700</v>
+        <v>678</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>1052</v>
+        <v>1027</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>1050</v>
+        <v>1025</v>
       </c>
       <c r="D22" s="42" t="n">
         <v>1</v>
       </c>
       <c r="E22" s="39" t="n">
-        <f aca="false">配件与耗材!K31</f>
+        <f aca="false">配件与耗材!K27</f>
         <v>0</v>
       </c>
       <c r="F22" s="40" t="n">
@@ -20470,7 +20122,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="33" t="s">
-        <v>1053</v>
+        <v>1028</v>
       </c>
       <c r="H22" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
@@ -20479,19 +20131,19 @@
     </row>
     <row r="23" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="33" t="s">
-        <v>704</v>
+        <v>682</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>1054</v>
+        <v>1029</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>1050</v>
+        <v>1025</v>
       </c>
       <c r="D23" s="42" t="n">
         <v>1</v>
       </c>
       <c r="E23" s="39" t="n">
-        <f aca="false">配件与耗材!K32</f>
+        <f aca="false">配件与耗材!K28</f>
         <v>3.31</v>
       </c>
       <c r="F23" s="40" t="n">
@@ -20499,7 +20151,7 @@
         <v>3.31</v>
       </c>
       <c r="G23" s="33" t="s">
-        <v>1051</v>
+        <v>1026</v>
       </c>
       <c r="H23" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
@@ -20508,19 +20160,19 @@
     </row>
     <row r="24" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="33" t="s">
-        <v>707</v>
+        <v>685</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>1055</v>
+        <v>1030</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>1050</v>
+        <v>1025</v>
       </c>
       <c r="D24" s="42" t="n">
         <v>1</v>
       </c>
       <c r="E24" s="39" t="n">
-        <f aca="false">配件与耗材!K33</f>
+        <f aca="false">配件与耗材!K29</f>
         <v>3.59</v>
       </c>
       <c r="F24" s="40" t="n">
@@ -20528,7 +20180,7 @@
         <v>3.59</v>
       </c>
       <c r="G24" s="33" t="s">
-        <v>1051</v>
+        <v>1026</v>
       </c>
       <c r="H24" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
@@ -20537,19 +20189,19 @@
     </row>
     <row r="25" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="33" t="s">
-        <v>710</v>
+        <v>688</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>1056</v>
+        <v>1031</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>1050</v>
+        <v>1025</v>
       </c>
       <c r="D25" s="42" t="n">
         <v>1</v>
       </c>
       <c r="E25" s="39" t="n">
-        <f aca="false">配件与耗材!K34</f>
+        <f aca="false">配件与耗材!K30</f>
         <v>3.88</v>
       </c>
       <c r="F25" s="40" t="n">
@@ -20557,7 +20209,7 @@
         <v>3.88</v>
       </c>
       <c r="G25" s="33" t="s">
-        <v>1051</v>
+        <v>1026</v>
       </c>
       <c r="H25" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
@@ -20566,19 +20218,19 @@
     </row>
     <row r="26" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="33" t="s">
-        <v>713</v>
+        <v>691</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>1057</v>
+        <v>1032</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>1050</v>
+        <v>1025</v>
       </c>
       <c r="D26" s="42" t="n">
         <v>1</v>
       </c>
       <c r="E26" s="39" t="n">
-        <f aca="false">配件与耗材!K35</f>
+        <f aca="false">配件与耗材!K31</f>
         <v>3.59</v>
       </c>
       <c r="F26" s="40" t="n">
@@ -20586,7 +20238,7 @@
         <v>3.59</v>
       </c>
       <c r="G26" s="33" t="s">
-        <v>1051</v>
+        <v>1026</v>
       </c>
       <c r="H26" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=534923831046","打开订单商品")</f>
@@ -20598,10 +20250,10 @@
         <v>569</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>1058</v>
+        <v>1033</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>1059</v>
+        <v>1034</v>
       </c>
       <c r="D27" s="42" t="n">
         <v>1</v>
@@ -20627,10 +20279,10 @@
         <v>574</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>1060</v>
+        <v>1035</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>1059</v>
+        <v>1034</v>
       </c>
       <c r="D28" s="42" t="n">
         <v>1</v>
@@ -20656,10 +20308,10 @@
         <v>579</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>1061</v>
+        <v>1036</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>1062</v>
+        <v>1037</v>
       </c>
       <c r="D29" s="42" t="n">
         <v>1</v>
@@ -20685,10 +20337,10 @@
         <v>585</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>1063</v>
+        <v>1038</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>1064</v>
+        <v>1039</v>
       </c>
       <c r="D30" s="42" t="n">
         <v>1</v>
@@ -20714,10 +20366,10 @@
         <v>629</v>
       </c>
       <c r="B31" s="33" t="s">
-        <v>1065</v>
+        <v>1040</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>1066</v>
+        <v>1041</v>
       </c>
       <c r="D31" s="42" t="n">
         <v>30</v>
@@ -20731,7 +20383,7 @@
         <v>27</v>
       </c>
       <c r="G31" s="33" t="s">
-        <v>1067</v>
+        <v>1042</v>
       </c>
       <c r="H31" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=825340808235","打开订单商品")</f>
@@ -20743,10 +20395,10 @@
         <v>635</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>1068</v>
+        <v>1043</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>1066</v>
+        <v>1041</v>
       </c>
       <c r="D32" s="42" t="n">
         <v>30</v>
@@ -20760,7 +20412,7 @@
         <v>27</v>
       </c>
       <c r="G32" s="33" t="s">
-        <v>1069</v>
+        <v>1044</v>
       </c>
       <c r="H32" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=825340808235","打开订单商品")</f>
@@ -20772,27 +20424,27 @@
         <v>640</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>1070</v>
+        <v>1045</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>1039</v>
+        <v>1046</v>
       </c>
       <c r="D33" s="42" t="n">
-        <v>50</v>
-      </c>
-      <c r="E33" s="39" t="n">
-        <f aca="false">配件与耗材!K21</f>
-        <v>0.04</v>
+        <v>3</v>
+      </c>
+      <c r="E33" s="43" t="n">
+        <f aca="false">(订单匹配依据!G88*订单匹配依据!H88+订单匹配依据!G89*订单匹配依据!H89)/(订单匹配依据!G88+订单匹配依据!G89)</f>
+        <v>3.59333333333333</v>
       </c>
       <c r="F33" s="40" t="n">
         <f aca="false">D33*E33</f>
-        <v>2</v>
+        <v>10.78</v>
       </c>
       <c r="G33" s="33" t="s">
-        <v>1071</v>
+        <v>1047</v>
       </c>
       <c r="H33" s="41" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=891600917698","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=781764816472","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
     </row>
@@ -20801,175 +20453,63 @@
         <v>646</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>1072</v>
+        <v>1048</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>1062</v>
+        <v>1014</v>
       </c>
       <c r="D34" s="42" t="n">
         <v>1</v>
       </c>
       <c r="E34" s="39" t="n">
         <f aca="false">配件与耗材!K22</f>
-        <v>2.68</v>
+        <v>3.42</v>
       </c>
       <c r="F34" s="40" t="n">
         <f aca="false">D34*E34</f>
-        <v>2.68</v>
+        <v>3.42</v>
       </c>
       <c r="G34" s="33" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H34" s="41" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=891600917698","打开订单商品")</f>
+        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=736162720327","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="33" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B35" s="33" t="s">
-        <v>1073</v>
+        <v>1049</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>1039</v>
+        <v>1014</v>
       </c>
       <c r="D35" s="42" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E35" s="39" t="n">
         <f aca="false">配件与耗材!K23</f>
-        <v>0.3</v>
+        <v>0.99</v>
       </c>
       <c r="F35" s="40" t="n">
         <f aca="false">D35*E35</f>
-        <v>3</v>
+        <v>0.99</v>
       </c>
       <c r="G35" s="33" t="s">
-        <v>1074</v>
+        <v>658</v>
       </c>
       <c r="H35" s="41" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=598425041338","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="33" t="s">
-        <v>657</v>
-      </c>
-      <c r="B36" s="33" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C36" s="33" t="s">
-        <v>1039</v>
-      </c>
-      <c r="D36" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" s="39" t="n">
-        <f aca="false">配件与耗材!K24</f>
-        <v>0.27</v>
-      </c>
-      <c r="F36" s="40" t="n">
-        <f aca="false">D36*E36</f>
-        <v>2.7</v>
-      </c>
-      <c r="G36" s="33" t="s">
-        <v>1076</v>
-      </c>
-      <c r="H36" s="41" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=595594145847","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="33" t="s">
-        <v>662</v>
-      </c>
-      <c r="B37" s="33" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C37" s="33" t="s">
-        <v>1078</v>
-      </c>
-      <c r="D37" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="E37" s="43" t="n">
-        <f aca="false">(订单匹配依据!G92*订单匹配依据!H92+订单匹配依据!G93*订单匹配依据!H93)/(订单匹配依据!G92+订单匹配依据!G93)</f>
-        <v>3.59333333333333</v>
-      </c>
-      <c r="F37" s="40" t="n">
-        <f aca="false">D37*E37</f>
-        <v>10.78</v>
-      </c>
-      <c r="G37" s="33" t="s">
-        <v>1079</v>
-      </c>
-      <c r="H37" s="41" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=781764816472","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="33" t="s">
-        <v>668</v>
-      </c>
-      <c r="B38" s="33" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C38" s="33" t="s">
-        <v>1039</v>
-      </c>
-      <c r="D38" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="39" t="n">
-        <f aca="false">配件与耗材!K26</f>
-        <v>3.42</v>
-      </c>
-      <c r="F38" s="40" t="n">
-        <f aca="false">D38*E38</f>
-        <v>3.42</v>
-      </c>
-      <c r="G38" s="33" t="s">
-        <v>673</v>
-      </c>
-      <c r="H38" s="41" t="str">
-        <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=736162720327","打开订单商品")</f>
-        <v>打开订单商品</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="33" t="s">
-        <v>675</v>
-      </c>
-      <c r="B39" s="33" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C39" s="33" t="s">
-        <v>1039</v>
-      </c>
-      <c r="D39" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="39" t="n">
-        <f aca="false">配件与耗材!K27</f>
-        <v>0.99</v>
-      </c>
-      <c r="F39" s="40" t="n">
-        <f aca="false">D39*E39</f>
-        <v>0.99</v>
-      </c>
-      <c r="G39" s="33" t="s">
-        <v>680</v>
-      </c>
-      <c r="H39" s="41" t="str">
         <f aca="false">HYPERLINK("https://item.taobao.com/item.htm?id=945215173380","打开订单商品")</f>
         <v>打开订单商品</v>
       </c>
     </row>
+    <row r="36" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="40" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="41" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="42" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
